--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,12 +29,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -479,411 +486,2106 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>CTI Imobiliária</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar no Cordeiro</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Cordeiro</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/706</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento de 90 m² com 3 dormitórios, 1 vaga e varanda disponível para locação em</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Rio Doce</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-rio-doce-olinda-com-garagem-90m2-aluguel-RS1700-id-2892631476/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 3 quartos, 1 banheiro, 1 vaga na garagem, área de 90 m², varanda e ar-condicionado em</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Rio Doce</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-ar-condicionado-rio-doce-olinda-90m2-id-2892631476/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 60 m², 2 quartos, 2 banheiros, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Boa Viagem</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-viagem-recife-com-garagem-60m2-aluguel-RS1800-id-2902680499/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento de 74 m² com 3 dormitórios, 2 banheiros e 1 vaga disponível para compra em</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Rio Doce</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-rio-doce-olinda-com-garagem-74m2-aluguel-RS1800-id-2884604076/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Zap Imóveis</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 60 m², 2 quartos, 2 banheiros, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Boa Viagem</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-boa-viagem-recife-60m2-id-2902680499/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento à venda com 3 quartos, 2 banheiros e 1 vaga na garagem de 74 m² em</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Rio Doce</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-cozinha-rio-doce-olinda-74m2-id-2884604076/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 79 m², 3 quartos, 1 banheiro, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Jardim Atlântico</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1842</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-jardim-atlantico-olinda-79m2-id-2899186475/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Zap Imóveis</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 2 quartos, 1 banheiro, 1 vaga na garagem e 60 m² próximo ao Metrô Shopping em</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Boa Viagem</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1896</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-area-de-servico-boa-viagem-recife-60m2-id-2893138519/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 90 m², 3 quartos, 3 banheiros, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Jardim Atlântico</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-com-garagem-90m2-aluguel-RS1900-id-2902068413/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 90 m², 3 quartos, 3 banheiros, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Jardim Atlântico</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-jardim-atlantico-olinda-90m2-id-2902068413/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>REMAX Recife</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Boa Viagem</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/1826-rua-almirante-saldanha-da-gama-clube-das-aguias/850501240-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento disponível para locação com 70 m², 2 dormitórios e 2 banheiros em</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Cordeiro</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-cordeiro-recife-com-garagem-70m2-aluguel-RS2100-id-2869283216/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 70 m², 3 quartos, 1 banheiro, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>2140</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-70m2-aluguel-RS2140-id-2896700211/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 70 m², 3 quartos, 1 banheiro, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>2140</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-cozinha-casa-caiada-olinda-70m2-id-2896700211/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento com portaria 24h, 2 quartos, 1 suíte e disponível para aluguel em</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Várzea</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>2199</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-varzea-recife-com-garagem-70m2-aluguel-RS2199-id-2894160875/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>REMAX Recife</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Arruda</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/1029-estrada-velha-de-agua-fria-a-160-m-da-sede-do-dnocs/850191023-82</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Abasol Imóveis</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>ExclusivoAP0535-DD4ApartamentoSetúbal - Recife - PE56.8 m²2 Quartos1 Suíte2 Banheiros1 VagaAluguelR$ 2.300/mês</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>568</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.abasol.com.br/imovel/apartamento-recife-2-quartos-57-m/AP0535-DD4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Rede Imóveis Pernambuco</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>R$ 2.300/mêsBoa ViagemApartamento em RecifeApartamento para Locação  Edifício Aline Maria | Boa Viagem
+More com conforto e praticidade em um dos bairros mais desejados do Recife!
+Este excelente apartamento possui 85 m² de área, com uma distribuição funcional dos ambientes. São 2 quartos, sendo 1 suíte, 1 banheiro social, sala ampla, cozinha e ótima iluminação natural.
+O imóvel conta com móveis planejados nos quartos, na cozinha e nos banheiros, oferecendo mais organização e comodidade. Além disso, dispõe de 1 vaga de garagem e o edifício possui elevador proporcionando mais conforto no dia a dia.
+Sua localização em Boa Viagem é um grande diferencial, estando próximo a parada de ônibus, além de supermercados, farmácias, escolas, restaurantes e diversos outros serviços essenciais, facilitando a rotina dos moradores.
+Valor da locação: R$ 2.300,00.
+Entre em contato com a Rocha Imóveis e agende sua visita!2quartos2banheiros1vaga85m²DetalhesContatoAP2432-DDZ</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Boa Viagem</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.redeimoveispe.com.br/imovel/apartamento-recife-2-quartos-85-m/AP2432-DDZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>OLX Imóveis</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>ALUGUEL APT CASA CAIADA</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/aluguel-apt-casa-caiada-1523400339</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento disponível para locação com 72 m², 3 dormitórios, varanda e 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 3 quartos, 1 banheiro, 1 vaga na garagem, varanda e elevador no condomínio em</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-ar-condicionado-casa-caiada-olinda-72m2-id-2866390830/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Rede Imóveis Pernambuco</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>R$ 2.400/mêsBoa VistaApartamento em RecifeExcelente oportunidade de moradia no Edifício Mandacaru, ideal para quem busca praticidade e conforto no centro do Recife. O apartamento 203 possui uma planta funcional com 2 dormitórios (sendo 1 suíte) e 2 banheiros totais. 
+Localizado em rua asfaltada com iluminação pública e saneamento.
+Localização:
+Endereço: Rua Sete de Setembro, 105 - Boa Vista, Recife/PE. Localização central privilegiada, próxima a polos educacionais, médicos e comerciais, garantindo facilidade de deslocamento para todas as regiões da cidade.2quartos2banheiros1vaga80m²DetalhesContatoAP1125-CZA</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.redeimoveispe.com.br/imovel/apartamento-recife-2-quartos-80-m/AP1125-CZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento com varanda, 3 dormitórios e 1 suíte disponível para locação em</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-120m2-aluguel-RS2200-id-2886278592/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 3 quartos, 1 suíte, 120 m², 1 banheiro e 1 vaga na garagem em</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-jardim-casa-caiada-olinda-120m2-id-2886278592/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>REMAX Recife</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Boa Viagem</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/2970-avenida-conselheiro-aguiar-edif-paris-ao-lado-da-loja-feminina-sirena-l/850251121-58</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 107 m², 3 quartos, 3 banheiros, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 107 m², 3 quartos, 3 banheiros, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-sala-de-jantar-bairro-novo-olinda-107m2-id-2902349299/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CTI Imobiliária</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>Apartamento para alugar no Iputinga</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Iputinga</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E30" t="n">
         <v>1500</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F30" t="n">
         <v>2</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G30" t="n">
         <v>85</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-iputinga-recife-pe/4347</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 70 m², 3 quartos, 2 banheiros, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Jardim Atlântico</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" t="n">
+        <v>70</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-com-garagem-70m2-aluguel-RS1500-id-2900988225/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 78 m², 3 quartos, 2 banheiros em</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Jardim Atlântico</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" t="n">
+        <v>78</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-78m2-aluguel-RS1500-id-2879884309/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 70 m², 3 quartos, 2 banheiros, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Jardim Atlântico</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>70</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-jardim-atlantico-olinda-70m2-id-2900988225/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 78 m², 3 quartos, 2 banheiros em</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Jardim Atlântico</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>78</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-jardim-atlantico-olinda-78m2-id-2879884309/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Apartamento disponível para locação com 3 dormitórios, 1 suíte e 110 m² em</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Fragoso</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3</v>
+      </c>
+      <c r="G35" t="n">
+        <v>110</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-fragoso-olinda-com-garagem-110m2-aluguel-RS1500-id-2886093996/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 3 quartos, 1 suíte, 2 banheiros e 1 vaga na garagem em</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Fragoso</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>110</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-fragoso-olinda-110m2-id-2886093996/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CTI Imobiliária</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar no Cordeiro no condomínio Edifício Morais</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Cordeiro</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>70</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/1006</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>REMAX Olinda</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Apartamento</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pernambuco</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/olinda/184-rua-cel-francisco-figueiroa/850471077-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 79 m², 3 quartos, 1 banheiro, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Jardim Atlântico</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1842</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" t="n">
+        <v>79</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-com-garagem-79m2-aluguel-RS1500-id-2899186475/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CTI Imobiliária</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar no Graças</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Graças</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1850</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>80</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Moradasol Imobiliária</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ExclusivoAP1233-MOSAApartamentoBoa Viagem - Recife - PEEd. Bouganvile60 m²2 Quartos1 Banheiro1 VagaAluguelR$ 1.896/mês</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1896</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" t="n">
+        <v>60</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://www.moradasol.com.br/imovel/apartamento-recife-2-quartos-60-m/AP1233-MOSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Viva Real</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Apartamento de 60 m² com 2 dormitórios, 1 banheiro e 1 vaga disponível para aluguel em</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Boa Viagem</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1896</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>60</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-viagem-recife-com-garagem-60m2-aluguel-RS1896-id-2893138519/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Moradasol Imobiliária</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ExclusivoAP3590-MOSAApartamentoBoa Viagem - Recife - PEEd. Nerfetite60 m²2 Quartos1 Banheiro1 VagaAluguelR$ 1.985,42/mês</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1985.42</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" t="n">
+        <v>60</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://www.moradasol.com.br/imovel/apartamento-recife-2-quartos-60-m/AP3590-MOSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Viva Real</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Apartamento com 2 quartos, 1 suíte e 70 m² disponível para aluguel em</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Iputinga</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2068</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" t="n">
+        <v>70</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-iputinga-recife-com-garagem-70m2-aluguel-RS2068-id-2893614874/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Zap Imóveis</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 2 quartos, 1 suíte, 2 banheiros, 1 vaga na garagem e 70 m² em</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Iputinga</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2068</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>70</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-area-de-servico-iputinga-recife-70m2-id-2893614874/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Rogério Corretor</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Pronto chevron_left chevron_right Apartamento para locação bairro Cordeiro, 2 qu</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Cordeiro</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" t="n">
+        <v>70</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-cordeiro-recife-1-vaga-70m2-code-673</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Zap Imóveis</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 2 quartos, 1 suíte, 2 banheiros, 1 vaga na garagem e portaria 24h em</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Várzea</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2199</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" t="n">
+        <v>70</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-acesso-24-horas-varzea-recife-70m2-id-2894160875/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Viva Real</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 66 m², 2 quartos, 1 banheiro, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Água Fria</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" t="n">
+        <v>66</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-agua-fria-recife-com-garagem-66m2-aluguel-RS2200-id-2899660583/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Apartamento disponível para locação com 3 dormitórios, aceita animais e 72 m² em</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" t="n">
+        <v>72</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2200-id-2876313979/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Zap Imóveis</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 66 m², 2 quartos, 1 banheiro, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Água Fria</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>66</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-churrasqueira-agua-fria-recife-66m2-id-2899660583/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 3 quartos, 2 banheiros, 1 vaga na garagem e varanda em</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3</v>
+      </c>
+      <c r="G51" t="n">
+        <v>72</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-interfone-casa-caiada-olinda-72m2-id-2876313979/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CTI Imobiliária</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar no Cordeiro</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Cordeiro</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" t="n">
+        <v>60</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/181</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Viva Real</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 85 m², 2 quartos, 2 banheiros, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Boa Viagem</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" t="n">
+        <v>85</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-viagem-recife-com-garagem-85m2-aluguel-RS2300-id-2900737397/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Zap Imóveis</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 85 m², 2 quartos, 2 banheiros, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Boa Viagem</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" t="n">
+        <v>85</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-cozinha-boa-viagem-recife-85m2-id-2900737397/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Âncora Imobiliária</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apartamento 3 Quartos Boa Viagem 120m² Rua Barão De Souza Leão, 367, Boa Viagem </t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Boa Viagem</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2341.42</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>120</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://ancoraimobiliaria.com.br/imovel/4504/apartamento-3-quartos-diva-boa-viagem-recife/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
         <is>
           <t>Rede Imóveis Pernambuco</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>R$ 1.500/mêsAfogadosApartamento em RecifeAPARTAMENTO PARA LOCAÇÃO EM AFOGADOS
-Sala ampla
-3 quartos com armários sendo 1 suíte
-Cozinha com armários
-1 banheiro social com armário
-Varanda
-1 vaga de garagem coberta
-Agende sua visita!3quartos1suíte1banheiro102m²DetalhesContatoAP0956-ARRE</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Afogados</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" t="n">
-        <v>102</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>https://www.redeimoveispe.com.br/imovel/apartamento-recife-3-quartos-102-m/AP0956-ARRE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CTI Imobiliária</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Apartamento para alugar no Cordeiro no condomínio Edifício Morais</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Cordeiro</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1700</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>70</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/1006</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>REMAX Olinda</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Apartamento</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Pernambuco</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1800</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/olinda/184-rua-cel-francisco-figueiroa/850471077-9</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Moradasol Imobiliária</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ExclusivoAP1233-MOSAApartamentoBoa Viagem - Recife - PEEd. Bouganvile60 m²2 Quartos1 Banheiro1 VagaAluguelR$ 1.896/mês</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1896</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>60</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>https://www.moradasol.com.br/imovel/apartamento-recife-2-quartos-60-m/AP1233-MOSA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Moradasol Imobiliária</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ExclusivoAP3590-MOSAApartamentoBoa Viagem - Recife - PEEd. Nerfetite60 m²2 Quartos1 Banheiro1 VagaAluguelR$ 1.985,42/mês</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1985.42</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>https://www.moradasol.com.br/imovel/apartamento-recife-2-quartos-60-m/AP3590-MOSA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CTI Imobiliária</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Apartamento para alugar no Santana</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Santana</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>75</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-santana-recife-pe/7770</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Rogério Corretor</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Pronto chevron_left chevron_right Apartamento para locação bairro Cordeiro, 2 qu</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Cordeiro</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>2100</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>70</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-cordeiro-recife-1-vaga-70m2-code-673</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>REMAX Recife</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Apartamento</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Arruda</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>2200</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>66</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/1029-estrada-velha-de-agua-fria-proximo-ao-dnocs-avenida-norte/850191120-4</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CTI Imobiliária</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Apartamento para alugar no Cordeiro</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Cordeiro</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>2300</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>60</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/181</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Âncora Imobiliária</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Apartamento 3 Quartos Boa Viagem 120m² Rua Barão De Souza Leão, 367, Boa Viagem </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Boa Viagem</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>2341.42</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" t="n">
-        <v>120</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/4504/apartamento-3-quartos-diva-boa-viagem-recife/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Rede Imóveis Pernambuco</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>R$ 2.048,59/mêsCondomínio R$ 200IPTU R$ 145/mêsCasa AmarelaApartamento em RecifeEdf Antonio de Sá - numa excelente localização em Casa Amarela !
 Próximo ao comercio, escolas, supermercados, etc.
@@ -892,65 +2594,139 @@
 Agende sua visita conosco!3quartos1suíte1banheiro1vaga80m²DetalhesContatoAP2232-DDZ</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Casa Amarela</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E56" t="n">
         <v>2393.59</v>
       </c>
-      <c r="F13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="F56" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" t="n">
         <v>80</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>https://www.redeimoveispe.com.br/imovel/apartamento-recife-3-quartos-80-m/AP2232-DDZ</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
         <is>
           <t>REMAX Recife</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Apartamento</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Boa Viagem</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E57" t="n">
         <v>2500</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F57" t="n">
         <v>2</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G57" t="n">
         <v>60</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/1222-avenida-fernando-simoes-barbosa-ao-lado-do-restaurante-parraxaxa/850191105-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 80 m², 3 quartos, 2 banheiros, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3</v>
+      </c>
+      <c r="G58" t="n">
+        <v>80</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2897542450/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 80 m², 3 quartos, 2 banheiros, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3</v>
+      </c>
+      <c r="G59" t="n">
+        <v>80</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-casa-caiada-olinda-80m2-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -493,36 +493,36 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento para alugar no Cordeiro</t>
+          <t>Apartamento para alugar com 70 m², 2 quartos, 2 banheiros em</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Cordeiro</t>
+          <t>São José</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/7802</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-sao-jose-recife-70m2-aluguel-RS1600-id-2903759599/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -534,36 +534,36 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Casa 3 Quartos Engenho Do Meio 150m² Rua Francisco Bezerra Monteiro, 119, Engenh</t>
+          <t>Apartamento para alugar com 75 m², 3 quartos, 1 banheiro em</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Engenho Do Meio</t>
+          <t>Jardim Atlântico</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1700</v>
+        <v>1672</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/2234/casa-3-quartos-engenho-do-meio-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-75m2-aluguel-RS1500-id-2904783799/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -575,36 +575,36 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 70 m², 2 quartos, 2 banheiros em</t>
+          <t>Apartamento para alugar com 75 m², 3 quartos, 1 banheiro em</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>São José</t>
+          <t>Jardim Atlântico</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1700</v>
+        <v>1672</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-sao-jose-recife-70m2-aluguel-RS1700-id-2903759599/?source=ranking%2Crp</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-jardim-atlantico-olinda-75m2-id-2904783799/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -616,17 +616,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 70 m², 2 quartos, 2 banheiros em</t>
+          <t>Apartamento para alugar no Cordeiro no condomínio Edifício Morais</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>São José</t>
+          <t>Cordeiro</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -640,12 +640,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-sao-jose-recife-70m2-id-2903759599/?source=ranking%2Crp</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/2947</t>
         </is>
       </c>
     </row>
@@ -657,12 +657,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 3 quartos, 1 banheiro, 1 vaga na garagem, área de 90 m², varanda e ar-condicionado em</t>
+          <t>Apartamento de 74 m² com 3 dormitórios, 2 banheiros e 1 vaga disponível para compra em</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -677,16 +677,16 @@
         <v>3</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-interfone-rio-doce-olinda-90m2-id-2892631476/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-rio-doce-olinda-com-garagem-74m2-aluguel-RS1700-id-2884604076/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -698,36 +698,30 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Zap Imóveis Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Apartamento à venda com 3 quartos, 2 banheiros e 1 vaga na garagem de 74 m² em</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Rio Doce</t>
-        </is>
-      </c>
+          <t>ApartamentoRecife - PE</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n">
         <v>1800</v>
       </c>
-      <c r="F7" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n">
         <v>74</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-rio-doce-olinda-74m2-id-2884604076/?source=ranking%2Crp</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -739,36 +733,30 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Zap Imóveis Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 79 m², 3 quartos, 1 banheiro, 1 vaga em</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Jardim Atlântico</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Boa Vista Apartamento Semi-mobiliado para locação na Boa Vista no Edf. Basbel 2 </t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="n">
-        <v>1842</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>3</v>
-      </c>
+        <v>1800</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-area-de-servico-jardim-atlantico-olinda-79m2-id-2899186475/?source=ranking%2Crp</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -780,36 +768,36 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Zap Imóveis Olinda</t>
+          <t>Zap Imóveis</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 90 m², 3 quartos, 3 banheiros, 1 vaga em</t>
+          <t>Apartamento para alugar com 2 quartos, 1 suíte, 2 banheiros, 1 vaga na garagem e 70 m² em</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Jardim Atlântico</t>
+          <t>Iputinga</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1900</v>
+        <v>2068</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-jardim-jardim-atlantico-olinda-90m2-id-2902068413/?source=ranking%2Crp</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-cozinha-iputinga-recife-70m2-id-2893614874/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -821,36 +809,36 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>REMAX Recife</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 60 m², 2 quartos, 1 banheiro, 1 vaga em</t>
+          <t>Apartamento</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Imbiribeira</t>
+          <t>Cordeiro</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1985</v>
+        <v>2100</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-imbiribeira-recife-com-garagem-60m2-aluguel-RS1985-id-2903214422/?source=ranking%2Crp</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/126-rua-taio-proximo-avenida-do-forte/850191024-518</t>
         </is>
       </c>
     </row>
@@ -862,36 +850,36 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 60 m², 2 quartos, 1 banheiro, 1 vaga em</t>
+          <t>Apartamento para alugar com 3 quartos, 1 banheiro, 1 vaga na garagem, varanda e elevador no condomínio em</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Imbiribeira</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1985</v>
+        <v>2300</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-ar-condicionado-imbiribeira-recife-60m2-id-2903214422/?source=ranking%2Crp</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-varanda-casa-caiada-olinda-72m2-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -903,36 +891,36 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Zap Imóveis Olinda</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 70 m², 3 quartos, 1 banheiro, 1 vaga em</t>
+          <t>Apartamento para alugar com 110 m², 2 quartos, 1 banheiro, 1 vaga em</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Cordeiro</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2140</v>
+        <v>2400</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-interfone-casa-caiada-olinda-70m2-id-2896700211/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-cordeiro-recife-com-garagem-110m2-aluguel-RS2400-id-2903630297/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -944,12 +932,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>REMAX Recife</t>
+          <t>Zap Imóveis</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Apartamento</t>
+          <t>Apartamento para alugar com 110 m², 2 quartos, 1 banheiro, 1 vaga em</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -958,18 +946,22 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
+        <v>2400</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>110</v>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/em-frente-ao-terminal-getulio-vagas/850251121-36</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-cordeiro-recife-110m2-id-2903630297/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -981,36 +973,36 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 62 m², 2 quartos, 2 banheiros, 1 vaga em</t>
+          <t>Apartamento para alugar com 3 quartos, 1 suíte, 120 m², 1 banheiro e 1 vaga na garagem em</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Boa Viagem</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-viagem-recife-com-garagem-62m2-aluguel-RS2200-id-2904384993/?source=ranking%2Crp</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-casa-caiada-olinda-120m2-id-2886278592/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1014,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 62 m², 2 quartos, 2 banheiros, 1 vaga em</t>
+          <t>Apartamento para alugar com 75 m², 2 quartos, 2 banheiros, 1 vaga em</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1036,22 +1028,22 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-playground-boa-viagem-recife-62m2-id-2904384993/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-viagem-recife-com-garagem-75m2-aluguel-RS2500-id-2904540305/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1055,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 3 quartos, 1 banheiro, 1 vaga na garagem, varanda e elevador no condomínio em</t>
+          <t>Apartamento para alugar com 80 m², 3 quartos, 1 banheiro, 1 vaga em</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1077,22 +1069,22 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2300</v>
+        <v>2500</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-casa-caiada-olinda-72m2-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1104,36 +1096,36 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Zap Imóveis</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 60 m², 2 quartos, 2 banheiros, 1 vaga em</t>
+          <t>Apartamento para alugar com 2 quartos, 2 suítes, 80 m², 2 banheiros e 1 vaga na garagem em</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Iputinga</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2350</v>
+        <v>2500</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-iputinga-recife-com-garagem-60m2-aluguel-RS2350-id-2904017640/?source=ranking%2Crp</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-jardim-arruda-recife-80m2-id-2882143782/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1150,31 +1142,31 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 60 m², 2 quartos, 2 banheiros, 1 vaga em</t>
+          <t>Apartamento para alugar com 75 m², 2 quartos, 2 banheiros, 1 vaga em</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Iputinga</t>
+          <t>Boa Viagem</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2350</v>
+        <v>2500</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-infraestrutura-internet-iputinga-recife-60m2-id-2904017640/?source=ranking%2Crp</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-boa-viagem-recife-75m2-id-2904540305/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1178,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 80 m², 3 quartos, 2 banheiros, 1 vaga em</t>
+          <t>Apartamento para alugar com 80 m², 3 quartos, 1 banheiro, 1 vaga em</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1200,7 +1192,7 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>3</v>
@@ -1210,220 +1202,197 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-mobiliado-casa-caiada-olinda-80m2-id-2904821162/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CTI Imobiliária</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar no Iputinga</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Iputinga</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>85</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-iputinga-recife-pe/4347</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 78 m², 3 quartos, 2 banheiros em</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Jardim Atlântico</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>78</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-78m2-aluguel-RS1500-id-2879884309/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
         <is>
           <t>Zap Imóveis Olinda</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento para alugar com 3 quartos, 1 suíte, 120 m², 1 banheiro e 1 vaga na garagem em</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>2400</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-interfone-casa-caiada-olinda-120m2-id-2886278592/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Rede Imóveis Pernambuco</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>R$ 1.600/mêsCondomínio R$ 690IPTU R$ 180/mêsCordeiroApartamento em RecifeÓtimo apartamento para locação no Cordeiro, com 3 quartos, 2 Wcs, sala para 2 ambientes, cozinha, varanda, área de serviço.
-Bombeiro 2026 - R$ 44,04
-OBS: SERÁ OBRIGATÓRIO A CONTRATAÇÃO DE SEGURO INCENDIO NO CONTRATO DE LOCAÇÃO
-A SEGURADORA FICA A ESCOLHA DO CLIENTE.3quartos2banheiros1vaga70m²DetalhesContatoAP0381-PRP3</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Cordeiro</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>2470</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.redeimoveispe.com.br/imovel/apartamento-recife-3-quartos-70-m/AP0381-PRP3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Viva Real</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento disponível para locação com 2 dormitórios, 2 suítes e 1 vaga em</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Arruda</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 78 m², 3 quartos, 2 banheiros em</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Jardim Atlântico</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>78</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-jardim-atlantico-olinda-78m2-id-2879884309/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento para alugar com 2 quartos, 2 suítes, 80 m², 2 banheiros e 1 vaga na garagem em</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Arruda</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-area-de-servico-arruda-recife-80m2-id-2882143782/?source=ranking%2Crp</t>
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apartamento disponível para locação com 3 dormitórios, 1 suíte e 110 m² em</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Fragoso</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>110</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-fragoso-olinda-com-garagem-110m2-aluguel-RS1500-id-2886093996/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
         <is>
           <t>Zap Imóveis Olinda</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento para alugar com 107 m², 3 quartos, 3 banheiros, 1 vaga em</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-area-de-servico-bairro-novo-olinda-107m2-id-2902349299/?source=ranking%2Crp</t>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 3 quartos, 1 suíte, 2 banheiros e 1 vaga na garagem em</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Fragoso</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="n">
+        <v>110</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-fragoso-olinda-110m2-id-2886093996/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1436,22 +1405,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Apartamento para alugar no Iputinga</t>
+          <t>Apartamento para alugar no Cordeiro no condomínio Edifício Morais</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Iputinga</t>
+          <t>Cordeiro</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="F25" t="n">
         <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1460,7 +1429,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-iputinga-recife-pe/4347</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/1006</t>
         </is>
       </c>
     </row>
@@ -1473,31 +1442,31 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 78 m², 3 quartos, 2 banheiros em</t>
+          <t>Apartamento de 90 m² com 3 dormitórios, 1 vaga e varanda disponível para locação em</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Jardim Atlântico</t>
+          <t>Rio Doce</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-78m2-aluguel-RS1500-id-2879884309/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-rio-doce-olinda-com-garagem-90m2-aluguel-RS1700-id-2892631476/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1510,31 +1479,31 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 78 m², 3 quartos, 2 banheiros em</t>
+          <t>Apartamento para alugar com 3 quartos, 1 banheiro, 1 vaga na garagem, área de 90 m², varanda e ar-condicionado em</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Jardim Atlântico</t>
+          <t>Rio Doce</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="F27" t="n">
         <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-jardim-atlantico-olinda-78m2-id-2879884309/?source=ranking%2Crp</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-ar-condicionado-rio-doce-olinda-90m2-id-2892631476/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1542,36 +1511,36 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Apartamento disponível para locação com 3 dormitórios, 1 suíte e 110 m² em</t>
+          <t>Apartamento à venda com 3 quartos, 2 banheiros e 1 vaga na garagem de 74 m² em</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fragoso</t>
+          <t>Rio Doce</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="F28" t="n">
         <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-fragoso-olinda-com-garagem-110m2-aluguel-RS1500-id-2886093996/?source=ranking%2Crp</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-cozinha-rio-doce-olinda-74m2-id-2884604076/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1579,36 +1548,36 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Zap Imóveis Olinda</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 3 quartos, 1 suíte, 2 banheiros e 1 vaga na garagem em</t>
+          <t>Apartamento para alugar com 60 m², 2 quartos, 2 banheiros, 1 vaga em</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fragoso</t>
+          <t>Boa Viagem</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1650</v>
+        <v>1800</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-fragoso-olinda-110m2-id-2886093996/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-viagem-recife-com-garagem-60m2-aluguel-RS1800-id-2902680499/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1616,36 +1585,36 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Zap Imóveis</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Apartamento para alugar no Cordeiro no condomínio Edifício Morais</t>
+          <t>Apartamento para alugar com 60 m², 2 quartos, 2 banheiros, 1 vaga em</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cordeiro</t>
+          <t>Boa Viagem</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="F30" t="n">
         <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/1006</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-boa-viagem-recife-60m2-id-2902680499/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1658,31 +1627,31 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Apartamento de 90 m² com 3 dormitórios, 1 vaga e varanda disponível para locação em</t>
+          <t>Apartamento para alugar com 79 m², 3 quartos, 1 banheiro, 1 vaga em</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Rio Doce</t>
+          <t>Jardim Atlântico</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1700</v>
+        <v>1842</v>
       </c>
       <c r="F31" t="n">
         <v>3</v>
       </c>
       <c r="G31" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-rio-doce-olinda-com-garagem-90m2-aluguel-RS1700-id-2892631476/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-com-garagem-79m2-aluguel-RS1500-id-2899186475/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1690,21 +1659,27 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>REMAX Olinda</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Apartamento</t>
+          <t>Apartamento para alugar com 79 m², 3 quartos, 1 banheiro, 1 vaga em</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pernambuco</t>
+          <t>Jardim Atlântico</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1800</v>
+        <v>1842</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" t="n">
+        <v>79</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1713,7 +1688,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/olinda/184-rua-cel-francisco-figueiroa/850471077-9</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-jardim-jardim-atlantico-olinda-79m2-id-2899186475/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1721,36 +1696,36 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 60 m², 2 quartos, 2 banheiros, 1 vaga em</t>
+          <t>Apartamento para alugar no Graças</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Boa Viagem</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1800</v>
+        <v>1850</v>
       </c>
       <c r="F33" t="n">
         <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-viagem-recife-com-garagem-60m2-aluguel-RS1800-id-2902680499/?source=ranking%2Crp</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
         </is>
       </c>
     </row>
@@ -1758,36 +1733,31 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>Moradasol Imobiliária</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Apartamento de 74 m² com 3 dormitórios, 2 banheiros e 1 vaga disponível para compra em</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Rio Doce</t>
+          <t>ExclusivoAP1233-MOSAApartamentoBoa Viagem - Recife - PEEd. Bouganvile60 m²2 Quartos1 Banheiro1 VagaAluguelR$ 1.896/mês</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1800</v>
+        <v>1896</v>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-rio-doce-olinda-com-garagem-74m2-aluguel-RS1800-id-2884604076/?source=ranking%2Crp</t>
+          <t>https://www.moradasol.com.br/imovel/apartamento-recife-2-quartos-60-m/AP1233-MOSA</t>
         </is>
       </c>
     </row>
@@ -1795,12 +1765,12 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 60 m², 2 quartos, 2 banheiros, 1 vaga em</t>
+          <t>Apartamento de 60 m² com 2 dormitórios, 1 banheiro e 1 vaga disponível para aluguel em</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1809,7 +1779,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1800</v>
+        <v>1896</v>
       </c>
       <c r="F35" t="n">
         <v>2</v>
@@ -1819,12 +1789,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-boa-viagem-recife-60m2-id-2902680499/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-viagem-recife-com-garagem-60m2-aluguel-RS1896-id-2893138519/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1832,36 +1802,36 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>Zap Imóveis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 79 m², 3 quartos, 1 banheiro, 1 vaga em</t>
+          <t>Apartamento para alugar com 2 quartos, 1 banheiro, 1 vaga na garagem e 60 m² próximo ao Metrô Shopping em</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Jardim Atlântico</t>
+          <t>Boa Viagem</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1842</v>
+        <v>1896</v>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-com-garagem-79m2-aluguel-RS1500-id-2899186475/?source=ranking%2Crp</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-area-de-servico-boa-viagem-recife-60m2-id-2893138519/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1869,36 +1839,36 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Apartamento para alugar no Graças</t>
+          <t>Apartamento para alugar com 90 m², 3 quartos, 3 banheiros, 1 vaga em</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Jardim Atlântico</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1850</v>
+        <v>1900</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-com-garagem-90m2-aluguel-RS1900-id-2902068413/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1906,36 +1876,36 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Apartamento de 60 m² com 2 dormitórios, 1 banheiro e 1 vaga disponível para aluguel em</t>
+          <t>Apartamento para alugar com 90 m², 3 quartos, 3 banheiros, 1 vaga em</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Boa Viagem</t>
+          <t>Jardim Atlântico</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1896</v>
+        <v>1900</v>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-viagem-recife-com-garagem-60m2-aluguel-RS1896-id-2893138519/?source=ranking%2Crp</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-jardim-jardim-atlantico-olinda-90m2-id-2902068413/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1943,36 +1913,31 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>Moradasol Imobiliária</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 90 m², 3 quartos, 3 banheiros, 1 vaga em</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Jardim Atlântico</t>
+          <t>AP3946-MOSAApartamentoBoa Viagem - Recife - PE70 m²2 Quartos1 Suíte2 BanheirosAluguelR$ 1.977,52/mês</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1900</v>
+        <v>1977.52</v>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-com-garagem-90m2-aluguel-RS1900-id-2902068413/?source=ranking%2Crp</t>
+          <t>https://www.moradasol.com.br/imovel/apartamento-recife-2-quartos-70-m/AP3946-MOSA</t>
         </is>
       </c>
     </row>
@@ -1980,31 +1945,36 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Moradasol Imobiliária</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AP3946-MOSAApartamentoBoa Viagem - Recife - PE70 m²2 Quartos1 Suíte2 BanheirosAluguelR$ 1.977,52/mês</t>
+          <t>Apartamento para alugar com 60 m², 2 quartos, 1 banheiro, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Imbiribeira</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1977.52</v>
+        <v>1985</v>
       </c>
       <c r="F40" t="n">
         <v>2</v>
       </c>
       <c r="G40" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://www.moradasol.com.br/imovel/apartamento-recife-2-quartos-70-m/AP3946-MOSA</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-imbiribeira-recife-com-garagem-60m2-aluguel-RS1985-id-2903214422/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2012,31 +1982,36 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Moradasol Imobiliária</t>
+          <t>Zap Imóveis</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AP2607-MOSAApartamentoIputinga - Recife - PE70 m²2 Quartos1 Suíte2 Banheiros1 VagaAluguelR$ 2.068,30/mês</t>
+          <t>Apartamento para alugar com 60 m², 2 quartos, 1 banheiro, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Imbiribeira</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1977.52</v>
+        <v>1985</v>
       </c>
       <c r="F41" t="n">
         <v>2</v>
       </c>
       <c r="G41" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://www.moradasol.com.br/imovel/apartamento-recife-2-quartos-70-m/AP2607-MOSA</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-ar-condicionado-imbiribeira-recife-60m2-id-2903214422/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2044,27 +2019,22 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Moradasol Imobiliária</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Apartamento com 2 quartos, 1 suíte e 70 m² disponível para aluguel em</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Iputinga</t>
+          <t>ExclusivoAP3590-MOSAApartamentoBoa Viagem - Recife - PEEd. Nerfetite60 m²2 Quartos1 Banheiro1 VagaAluguelR$ 1.985,42/mês</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2068</v>
+        <v>1985.42</v>
       </c>
       <c r="F42" t="n">
         <v>2</v>
       </c>
       <c r="G42" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2073,7 +2043,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-iputinga-recife-com-garagem-70m2-aluguel-RS2068-id-2893614874/?source=ranking%2Crp</t>
+          <t>https://www.moradasol.com.br/imovel/apartamento-recife-2-quartos-60-m/AP3590-MOSA</t>
         </is>
       </c>
     </row>
@@ -2081,12 +2051,12 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 2 quartos, 1 suíte, 2 banheiros, 1 vaga na garagem e 70 m² em</t>
+          <t>Apartamento com 2 quartos, 1 suíte e 70 m² disponível para aluguel em</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2110,7 +2080,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-area-de-servico-iputinga-recife-70m2-id-2893614874/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-iputinga-recife-com-garagem-70m2-aluguel-RS2068-id-2893614874/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2118,21 +2088,16 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>Moradasol Imobiliária</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pronto chevron_left chevron_right Apartamento para locação bairro Cordeiro, 2 qu</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Cordeiro</t>
+          <t>AP2607-MOSAApartamentoIputinga - Recife - PE70 m²2 Quartos1 Suíte2 Banheiros1 VagaAluguelR$ 2.068,30/mês</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2100</v>
+        <v>2068.3</v>
       </c>
       <c r="F44" t="n">
         <v>2</v>
@@ -2147,7 +2112,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-cordeiro-recife-1-vaga-70m2-code-673</t>
+          <t>https://www.moradasol.com.br/imovel/apartamento-recife-2-quartos-70-m/AP2607-MOSA</t>
         </is>
       </c>
     </row>
@@ -2155,24 +2120,24 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Apartamento disponível para locação com 70 m², 2 dormitórios e 2 banheiros em</t>
+          <t>Apartamento para alugar com 70 m², 3 quartos, 1 banheiro, 1 vaga em</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cordeiro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2100</v>
+        <v>2140</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45" t="n">
         <v>70</v>
@@ -2184,7 +2149,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-cordeiro-recife-com-garagem-70m2-aluguel-RS2100-id-2869283216/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-70m2-aluguel-RS2140-id-2896700211/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2192,36 +2157,36 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Apartamento para alugar com 2 quartos, 2 banheiros e 1 vaga na garagem em</t>
+          <t>Apartamento para alugar com 70 m², 3 quartos, 1 banheiro, 1 vaga em</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cordeiro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2100</v>
+        <v>2140</v>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46" t="n">
         <v>70</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-cordeiro-recife-70m2-id-2869283216/?source=ranking%2Crp</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-interfone-casa-caiada-olinda-70m2-id-2896700211/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2229,47 +2194,10 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>Rede Imóveis Pernambuco</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
-        <is>
-          <t>Apartamento para alugar com 70 m², 3 quartos, 1 banheiro, 1 vaga em</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>2140</v>
-      </c>
-      <c r="F47" t="n">
-        <v>3</v>
-      </c>
-      <c r="G47" t="n">
-        <v>70</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-70m2-aluguel-RS2140-id-2896700211/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Rede Imóveis Pernambuco</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
         <is>
           <t>R$ 2.300/mêsBoa ViagemApartamento em RecifeApartamento para Locação  Edifício Aline Maria | Boa Viagem
 More com conforto e praticidade em um dos bairros mais desejados do Recife!
@@ -2280,6 +2208,43 @@
 Entre em contato com a Rocha Imóveis e agende sua visita!2quartos2banheiros1vaga85m²DetalhesContatoAP2432-DDZ</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Boa Viagem</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" t="n">
+        <v>85</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://www.redeimoveispe.com.br/imovel/apartamento-recife-2-quartos-85-m/AP2432-DDZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Viva Real</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 85 m², 2 quartos, 2 banheiros, 1 vaga em</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>Boa Viagem</t>
@@ -2296,12 +2261,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://www.redeimoveispe.com.br/imovel/apartamento-recife-2-quartos-85-m/AP2432-DDZ</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-viagem-recife-com-garagem-85m2-aluguel-RS2300-id-2900737397/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2346,12 +2311,12 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Zap Imóveis</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apartamento 3 Quartos Boa Viagem 120m² Rua Barão De Souza Leão, 367, Boa Viagem </t>
+          <t>Apartamento para alugar com 85 m², 2 quartos, 2 banheiros, 1 vaga em</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2360,22 +2325,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2341.42</v>
+        <v>2300</v>
       </c>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/4504/apartamento-3-quartos-diva-boa-viagem-recife/</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-cozinha-boa-viagem-recife-85m2-id-2900737397/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2383,10 +2348,47 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
+          <t>Âncora Imobiliária</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apartamento 3 Quartos Boa Viagem 120m² Rua Barão De Souza Leão, 367, Boa Viagem </t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Boa Viagem</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2341.42</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3</v>
+      </c>
+      <c r="G51" t="n">
+        <v>120</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://ancoraimobiliaria.com.br/imovel/4504/apartamento-3-quartos-diva-boa-viagem-recife/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>Rede Imóveis Pernambuco</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>R$ 2.048,59/mêsCondomínio R$ 200IPTU R$ 145/mêsCasa AmarelaApartamento em RecifeEdf Antonio de Sá - numa excelente localização em Casa Amarela !
 Próximo ao comercio, escolas, supermercados, etc.
@@ -2395,65 +2397,28 @@
 Agende sua visita conosco!3quartos1suíte1banheiro1vaga80m²DetalhesContatoAP2232-DDZ</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Casa Amarela</t>
         </is>
       </c>
-      <c r="E51" t="n">
+      <c r="E52" t="n">
         <v>2393.59</v>
       </c>
-      <c r="F51" t="n">
-        <v>3</v>
-      </c>
-      <c r="G51" t="n">
+      <c r="F52" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" t="n">
         <v>80</v>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>https://www.redeimoveispe.com.br/imovel/apartamento-recife-3-quartos-80-m/AP2232-DDZ</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>CTI Imobiliária</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Apartamento para alugar no Cordeiro</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Cordeiro</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>2400</v>
-      </c>
-      <c r="F52" t="n">
-        <v>2</v>
-      </c>
-      <c r="G52" t="n">
-        <v>60</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/181</t>
         </is>
       </c>
     </row>
@@ -2501,36 +2466,30 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>REMAX Recife</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Apartamento com varanda, 3 dormitórios e 1 suíte disponível para locação em</t>
+          <t>Apartamento</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Cordeiro</t>
         </is>
       </c>
       <c r="E54" t="n">
         <v>2400</v>
       </c>
-      <c r="F54" t="n">
-        <v>3</v>
-      </c>
-      <c r="G54" t="n">
-        <v>120</v>
-      </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-120m2-aluguel-RS2200-id-2886278592/?source=ranking%2Crp</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/em-frente-ao-terminal-getulio-vagas/850251121-36</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2497,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2562,12 +2521,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-casa-caiada-olinda-80m2-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2575,36 +2534,36 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>REMAX Recife</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Apartamento</t>
+          <t>Apartamento com varanda, 3 dormitórios e 1 suíte disponível para locação em</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Boa Viagem</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="F56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G56" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/1222-avenida-fernando-simoes-barbosa-ao-lado-do-restaurante-parraxaxa/850191105-5</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-120m2-aluguel-RS2200-id-2886278592/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2612,36 +2571,147 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
+          <t>Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 80 m², 3 quartos, 2 banheiros, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" t="n">
+        <v>80</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-casa-caiada-olinda-80m2-id-2897542450/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Viva Real</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Apartamento disponível para locação com 2 dormitórios, 2 suítes e 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Arruda</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" t="n">
+        <v>80</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>Viva Real Olinda</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Apartamento para alugar com 107 m², 3 quartos, 3 banheiros, 1 vaga em</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Bairro Novo</t>
         </is>
       </c>
-      <c r="E57" t="n">
+      <c r="E59" t="n">
         <v>2500</v>
       </c>
-      <c r="F57" t="n">
-        <v>3</v>
-      </c>
-      <c r="G57" t="n">
+      <c r="F59" t="n">
+        <v>3</v>
+      </c>
+      <c r="G59" t="n">
         <v>107</v>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Apartamento para alugar com 107 m², 3 quartos, 3 banheiros, 1 vaga em</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3</v>
+      </c>
+      <c r="G60" t="n">
+        <v>107</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-sala-de-jantar-bairro-novo-olinda-107m2-id-2902349299/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,18 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -546,1712 +539,1640 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CTI Imobiliária</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 80 m² · 2 vagas · Candeias</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Candeias</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 85 m² · Iputinga</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Iputinga</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>1500.0</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>1500.0</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-terreo-1527561087</t>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>17.65</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-iputinga-recife-pe/4347</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>OLX Imóveis</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 60 m² · Candeias</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 80 m² · 2 vagas · Candeias</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Candeias</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>1500.0</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>1500.0</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-tem-60-metros-quadrados-com-2-quartos-em-candeias-jaboatao-dos-guara-1527459633</t>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-terreo-1527561087</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
         <is>
           <t>OLX Imóveis</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · Boa Viagem</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Boa Viagem</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1600.0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1600.0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 60 m² · Candeias</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Candeias</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-com-3-quartos-e-garagem-conjunto-europa-1527426100</t>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-tem-60-metros-quadrados-com-2-quartos-em-candeias-jaboatao-dos-guara-1527459633</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 100 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1600.0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1600.0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 78 m² · Jardim Atlântico</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Rua Olavo Bilac</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jardim Atlântico</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-100m-reformado-ventilado-semi-mobiliado-no-centro-da-boa-vista-9-andar-1507545093</t>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>19.23</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-78m2-aluguel-RS1500-id-2879884309/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
         <is>
           <t>OLX Imóveis</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 70 m² · Candeias</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Candeias</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · Boa Viagem</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Boa Viagem</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>1600.0</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>1600.0</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>22.86</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-candeias-2-quartos-excelente-localizacao-por-1600-reais-taxas-inclusas-1527355763</t>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-com-3-quartos-e-garagem-conjunto-europa-1527426100</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Viva Real, Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 70 m² · São José</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Avenida Sul Governador Cid Sampaio</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>São José</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OLX Imóveis</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Apartamento · 100 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1600.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1600.0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1600.0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>22.86</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-sao-jose-recife-70m2-aluguel-RS1500-id-2903759599/?source=ranking%2Crp</t>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-100m-reformado-ventilado-semi-mobiliado-no-centro-da-boa-vista-9-andar-1507545093</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Viva Real, Zap Imóveis</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 70 m² · São José</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Avenida Sul Governador Cid Sampaio</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>São José</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1600.0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Iputinga</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Iputinga</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1700.0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1700.0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>28.33</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>22.86</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/perto-da-ufpe-1526627062</t>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-sao-jose-recife-70m2-aluguel-RS1500-id-2903759599/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 110 m² · Fragoso</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Rua Marim dos Caetés</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fragoso</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1650.0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Portal CRECI Brasil</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · Várzea</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Várzea</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-varzea-recife--pe_33349791</t>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-fragoso-olinda-com-garagem-110m2-aluguel-RS1500-id-2886093996/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Rua Joana Noberto Pessoa</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CTI Imobiliária</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 70 m² · Cordeiro</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Cordeiro</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1700.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1700.0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>21.18</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>24.29</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/2947</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CTI Imobiliária</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 1355 m² · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1925.0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1925.0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 70 m² · Cordeiro</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Cordeiro</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1700.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1700.0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>1355.0</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/studio-mobiliado-100m-da-fmo-e-40m-da-orla-melhor-local-ligue-hoje-mesmo-1527546954</t>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>24.29</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/1006</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>REMAX Recife e Olinda</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>OLX Imóveis</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 73 m² · Afogados</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Afogados</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1950.0</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1950.0</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Iputinga</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Iputinga</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1700.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1700.0</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>26.71</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>28.33</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850191067-75</t>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/perto-da-ufpe-1526627062</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Viva Real, Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 60 m² · Iputinga</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Rua João Sales de Menezes</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Iputinga</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2000.0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2000.0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 90 m² · Rio Doce</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Travessa Coronel Frederico Lundgren</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rio Doce</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1700.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1700.0</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-iputinga-recife-com-garagem-60m2-aluguel-RS2000-id-2904017640/?source=ranking%2Crp</t>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>18.89</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-rio-doce-olinda-com-garagem-90m2-aluguel-RS1700-id-2892631476/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Aldeia dos Camarás</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Aldeia dos Camarás</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2000.0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2002.0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>33.37</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 74 m² · Rio Doce</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Rua Maria da Conceição Viana</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rio Doce</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1700.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1700.0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>22.97</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-para-locacao-em-aldeia-so-100m-do-centro-comercial-terreo-1451601323</t>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-rio-doce-olinda-com-garagem-74m2-aluguel-RS1700-id-2884604076/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis, Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 120 m² · Jardim Atlântico</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Rua José Maurício Viana</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Jardim Atlântico</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Camila Melo Imóveis</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Apartamento · 74 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>1800.0</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>250.0</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>2050.0</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>17.08</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>120.0</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-com-3-quartos-em-jardim-atlantico-olinda-pe-1527601271</t>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 70 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Rua Antônio Silva Guimarães</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2140.0</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2140.0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Camila Melo Imóveis</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Apartamento · 74 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>30.57</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-70m2-aluguel-RS2140-id-2896700211/?source=ranking%2Crp</t>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis, REMAX Recife e Olinda</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 60 m² · Boa Viagem</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Boa Viagem</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2400.0</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2400.0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Portal CRECI Brasil</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · Várzea</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Várzea</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-possui-60-metros-quadrados-com-2-quartos-em-boa-viagem-recife-pe-1527394922</t>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-varzea-recife--pe_33349791</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C18" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 120 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2200.0</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>200.0</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2400.0</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Rua Joana Noberto Pessoa</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>21.18</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>120.0</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-120m2-aluguel-RS2200-id-2886278592/?source=ranking%2Crp</t>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 79 m² · Jardim Atlântico</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Rua Eurípedes Lavor Paes Barreto</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Jardim Atlântico</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>170.0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>172.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1842.0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Portal CRECI Brasil</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Santo Amaro</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>20.83</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>23.32</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>120.0</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-com-garagem-79m2-aluguel-RS1500-id-2899186475/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2188,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 85 m² · Iputinga</t>
+          <t>Apartamento · 2 quartos · 80 m² · Graças</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2277,12 +2198,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Iputinga</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1500.0</t>
+          <t>1850.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2297,7 +2218,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1500.0</t>
+          <t>1850.0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2307,7 +2228,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2327,7 +2248,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2342,7 +2263,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-iputinga-recife-pe/4347</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
         </is>
       </c>
     </row>
@@ -2358,12 +2279,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 78 m² · Jardim Atlântico</t>
+          <t>Apartamento · 3 quartos · 90 m² · Jardim Atlântico</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rua Olavo Bilac</t>
+          <t>Rua Jornalista Edson Regis</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2373,7 +2294,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1500.0</t>
+          <t>1900.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2388,7 +2309,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1500.0</t>
+          <t>1900.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2398,7 +2319,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2408,7 +2329,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2418,22 +2339,22 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-78m2-aluguel-RS1500-id-2879884309/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-com-garagem-90m2-aluguel-RS1900-id-2902068413/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2441,35 +2362,35 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 110 m² · Fragoso</t>
+          <t>Apartamento · 1355 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rua Marim dos Caetés</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fragoso</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1500.0</t>
+          <t>1925.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2479,27 +2400,27 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1650.0</t>
+          <t>1925.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2509,22 +2430,22 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>1355.0</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-fragoso-olinda-com-garagem-110m2-aluguel-RS1500-id-2886093996/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/studio-mobiliado-100m-da-fmo-e-40m-da-orla-melhor-local-ligue-hoje-mesmo-1527546954</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2453,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2540,7 +2461,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Cordeiro</t>
+          <t>Apartamento · 3 quartos · 73 m² · Afogados</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2550,12 +2471,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cordeiro</t>
+          <t>Afogados</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1950.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2570,7 +2491,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1950.0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2580,12 +2501,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2600,22 +2521,22 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/2947</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850191067-75</t>
         </is>
       </c>
     </row>
@@ -2623,30 +2544,30 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Cordeiro</t>
+          <t>Apartamento · 2 quartos · 60 m² · Imbiribeira</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Eládio Ramos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cordeiro</t>
+          <t>Imbiribeira</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1985.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2661,7 +2582,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1985.0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2671,7 +2592,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>33.08</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2681,7 +2602,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2691,22 +2612,22 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/1006</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-imbiribeira-recife-com-garagem-60m2-aluguel-RS1985-id-2903214422/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2635,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2722,22 +2643,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 90 m² · Rio Doce</t>
+          <t>Apartamento · 2 quartos · 60 m² · Iputinga</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Travessa Coronel Frederico Lundgren</t>
+          <t>Rua João Sales de Menezes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rio Doce</t>
+          <t>Iputinga</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2752,7 +2673,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2762,42 +2683,42 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-rio-doce-olinda-com-garagem-90m2-aluguel-RS1700-id-2892631476/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-iputinga-recife-com-garagem-60m2-aluguel-RS2000-id-2904017640/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2805,90 +2726,90 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 74 m² · Rio Doce</t>
+          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Aldeia dos Camarás</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rua Maria da Conceição Viana</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rio Doce</t>
+          <t>Aldeia dos Camarás</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2002.0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>22.97</t>
+          <t>33.37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-rio-doce-olinda-com-garagem-74m2-aluguel-RS1700-id-2884604076/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-para-locacao-em-aldeia-so-100m-do-centro-comercial-terreo-1451601323</t>
         </is>
       </c>
     </row>
@@ -2896,25 +2817,25 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>OLX Imóveis, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 120 m² · Jardim Atlântico</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua José Maurício Viana</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Jardim Atlântico</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2924,7 +2845,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2934,52 +2855,52 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2050.0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-com-3-quartos-em-jardim-atlantico-olinda-pe-1527601271</t>
         </is>
       </c>
     </row>
@@ -2987,30 +2908,30 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 70 m² · Iputinga</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Gaspar Perez</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Iputinga</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2068.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3025,7 +2946,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2068.0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3035,42 +2956,42 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>29.54</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-iputinga-recife-com-garagem-70m2-aluguel-RS2068-id-2893614874/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3086,47 +3007,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 79 m² · Jardim Atlântico</t>
+          <t>Apartamento · 3 quartos · 70 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rua Eurípedes Lavor Paes Barreto</t>
+          <t>Rua Antônio Silva Guimarães</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jardim Atlântico</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1500.0</t>
+          <t>2140.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1842.0</t>
+          <t>2140.0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3141,27 +3062,27 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-com-garagem-79m2-aluguel-RS1500-id-2899186475/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-70m2-aluguel-RS2140-id-2896700211/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3169,30 +3090,30 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Graças</t>
+          <t>Apartamento · 2 quartos · 85 m² · Boa Viagem</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua José Domingues da Silva</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Boa Viagem</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1850.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3207,7 +3128,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1850.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3217,7 +3138,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>27.06</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3227,7 +3148,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3237,7 +3158,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3252,7 +3173,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-viagem-recife-com-garagem-85m2-aluguel-RS2300-id-2900737397/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3268,22 +3189,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 90 m² · Jardim Atlântico</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rua Jornalista Edson Regis</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jardim Atlântico</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1900.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3298,7 +3219,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1900.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3308,7 +3229,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3318,7 +3239,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3328,7 +3249,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3343,7 +3264,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-com-garagem-90m2-aluguel-RS1900-id-2902068413/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3351,65 +3272,65 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Imbiribeira</t>
+          <t>Apartamento · 3 quartos · 120 m² · Boa Viagem</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rua Eládio Ramos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Imbiribeira</t>
+          <t>Boa Viagem</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1985.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>241.42</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1985.0</t>
+          <t>2341.42</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>33.08</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3419,22 +3340,22 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-imbiribeira-recife-com-garagem-60m2-aluguel-RS1985-id-2903214422/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/4504/apartamento-3-quartos-diva-boa-viagem-recife/</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3363,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>OLX Imóveis, REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3450,22 +3371,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Iputinga</t>
+          <t>Apartamento · 2 quartos · 60 m² · Boa Viagem</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rua Gaspar Perez</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Iputinga</t>
+          <t>Boa Viagem</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2068.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3480,7 +3401,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2068.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3490,7 +3411,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>29.54</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3500,32 +3421,32 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-iputinga-recife-com-garagem-70m2-aluguel-RS2068-id-2893614874/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-possui-60-metros-quadrados-com-2-quartos-em-boa-viagem-recife-pe-1527394922</t>
         </is>
       </c>
     </row>
@@ -3541,22 +3462,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 85 m² · Boa Viagem</t>
+          <t>Apartamento · 2 quartos · 110 m² · Cordeiro</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rua José Domingues da Silva</t>
+          <t>Avenida Caxangá</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Boa Viagem</t>
+          <t>Cordeiro</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3571,7 +3492,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3581,7 +3502,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>27.06</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3591,32 +3512,32 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-viagem-recife-com-garagem-85m2-aluguel-RS2300-id-2900737397/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-cordeiro-recife-com-garagem-110m2-aluguel-RS2400-id-2903630297/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3553,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3647,7 +3568,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3662,7 +3583,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3672,7 +3593,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3682,7 +3603,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3692,22 +3613,22 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3715,45 +3636,45 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Boa Viagem</t>
+          <t>Apartamento · 3 quartos · 120 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Boa Viagem</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>241.42</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2341.42</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3763,7 +3684,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3773,7 +3694,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3788,17 +3709,17 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/4504/apartamento-3-quartos-diva-boa-viagem-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-120m2-aluguel-RS2200-id-2886278592/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3806,30 +3727,30 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 110 m² · Cordeiro</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Avenida Caxangá</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cordeiro</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3844,7 +3765,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3854,17 +3775,17 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3874,22 +3795,22 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-cordeiro-recife-com-garagem-110m2-aluguel-RS2400-id-2903630297/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3818,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3905,22 +3826,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Zeferino Agra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3935,7 +3856,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3945,12 +3866,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3970,17 +3891,17 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3996,17 +3917,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+          <t>Apartamento · 2 quartos · 75 m² · Boa Viagem</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rua Zeferino Agra</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Boa Viagem</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4036,7 +3957,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4056,22 +3977,22 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-viagem-recife-com-garagem-75m2-aluguel-RS2500-id-2904540305/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4000,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -4087,17 +4008,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 75 m² · Boa Viagem</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Boa Viagem</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4127,17 +4048,17 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4147,22 +4068,22 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-viagem-recife-com-garagem-75m2-aluguel-RS2500-id-2904540305/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4178,17 +4099,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4218,7 +4139,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4228,121 +4149,30 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>2</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S41"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1088,7 +1088,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1096,17 +1096,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · São José</t>
+          <t>Apartamento · 3 quartos · 110 m² · Fragoso</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Avenida Sul Governador Cid Sampaio</t>
+          <t>Rua Marim dos Caetés</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>São José</t>
+          <t>Fragoso</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>1650.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1136,19 +1136,19 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -1156,22 +1156,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-sao-jose-recife-70m2-aluguel-RS1500-id-2903759599/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-fragoso-olinda-com-garagem-110m2-aluguel-RS1500-id-2886093996/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1179,35 +1179,35 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 110 m² · Fragoso</t>
+          <t>Apartamento · 2 quartos · 70 m² · Cordeiro</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua Marim dos Caetés</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fragoso</t>
+          <t>Cordeiro</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1500.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1217,52 +1217,52 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1650.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-fragoso-olinda-com-garagem-110m2-aluguel-RS1500-id-2886093996/?source=ranking%2Crp</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/2947</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/2947</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/1006</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Cordeiro</t>
+          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Iputinga</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cordeiro</t>
+          <t>Iputinga</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1429,22 +1429,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/1006</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/perto-da-ufpe-1526627062</t>
         </is>
       </c>
     </row>
@@ -1452,25 +1452,25 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Iputinga</t>
+          <t>Apartamento · 3 quartos · 90 m² · Rio Doce</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Travessa Coronel Frederico Lundgren</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Iputinga</t>
+          <t>Rio Doce</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1520,22 +1520,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/perto-da-ufpe-1526627062</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-rio-doce-olinda-com-garagem-90m2-aluguel-RS1700-id-2892631476/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 90 m² · Rio Doce</t>
+          <t>Apartamento · 3 quartos · 74 m² · Rio Doce</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Travessa Coronel Frederico Lundgren</t>
+          <t>Rua Maria da Conceição Viana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>22.97</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1601,17 +1601,17 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-rio-doce-olinda-com-garagem-90m2-aluguel-RS1700-id-2892631476/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-rio-doce-olinda-com-garagem-74m2-aluguel-RS1700-id-2884604076/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1634,30 +1634,30 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 74 m² · Rio Doce</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rua Maria da Conceição Viana</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rio Doce</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1682,42 +1682,42 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>22.97</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-rio-doce-olinda-com-garagem-74m2-aluguel-RS1700-id-2884604076/?source=ranking%2Crp</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · Várzea</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Várzea</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1884,22 +1884,22 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-varzea-recife--pe_33349791</t>
         </is>
       </c>
     </row>
@@ -1907,25 +1907,25 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · Várzea</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Várzea</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-varzea-recife--pe_33349791</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2006,47 +2006,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 79 m² · Jardim Atlântico</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Rua Eurípedes Lavor Paes Barreto</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Jardim Atlântico</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1842.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2061,27 +2061,27 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-com-garagem-79m2-aluguel-RS1500-id-2899186475/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2089,75 +2089,75 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 79 m² · Jardim Atlântico</t>
+          <t>Apartamento · 2 quartos · 80 m² · Graças</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rua Eurípedes Lavor Paes Barreto</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jardim Atlântico</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1500.0</t>
+          <t>1850.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1842.0</t>
+          <t>1850.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-com-garagem-79m2-aluguel-RS1500-id-2899186475/?source=ranking%2Crp</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
         </is>
       </c>
     </row>
@@ -2180,30 +2180,30 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Graças</t>
+          <t>Apartamento · 2 quartos · 60 m² · Boa Viagem</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Coronel Anízio Rodrigues Coelho</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Boa Viagem</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1850.0</t>
+          <t>1896.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1850.0</t>
+          <t>1896.0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-viagem-recife-com-garagem-60m2-aluguel-RS1896-id-2893138519/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3917,17 +3917,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 75 m² · Boa Viagem</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Boa Viagem</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3957,17 +3957,17 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3977,22 +3977,22 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-viagem-recife-com-garagem-75m2-aluguel-RS2500-id-2904540305/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4008,17 +4008,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4058,121 +4058,30 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>2</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,12 +29,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -539,1458 +546,1522 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>CTI Imobiliária</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 85 m² · Iputinga</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 60 m² · Iputinga</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Iputinga</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1750.0</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>1750.0</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>17.65</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>29.17</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-iputinga-recife-pe/4347</t>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-iputinga-recife-pe/116</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>OLX Imóveis</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 80 m² · 2 vagas · Candeias</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Candeias</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 100 m² · 2 vagas · Aldeia dos Camarás</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Aldeia dos Camarás</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-terreo-1527561087</t>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/aldeia-aluguel-apartamento-1513926197</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>OLX Imóveis</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 60 m² · Candeias</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Candeias</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 4 quartos · 95 m² · 1 vaga · Torrões</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Torrões</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-tem-60-metros-quadrados-com-2-quartos-em-candeias-jaboatao-dos-guara-1527459633</t>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-em-torroes-recife-pe-1527769769</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 78 m² · Jardim Atlântico</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Rua Olavo Bilac</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Jardim Atlântico</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Rua Joana Noberto Pessoa</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>19.23</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>21.18</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-78m2-aluguel-RS1500-id-2879884309/?source=ranking%2Crp</t>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>OLX Imóveis</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · Boa Viagem</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Boa Viagem</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1600.0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>1600.0</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 80 m² · Espinheiro</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Espinheiro</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-com-3-quartos-e-garagem-conjunto-europa-1527426100</t>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-possui-80-metros-quadrados-com-3-quartos-em-espinheiro-recife-pe-1527706131</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Apartamento · 100 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1600.0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>1600.0</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 120 m² · Jardim Atlântico</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Rua José Maurício Viana</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Jardim Atlântico</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>250.0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2050.0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>17.08</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-100m-reformado-ventilado-semi-mobiliado-no-centro-da-boa-vista-9-andar-1507545093</t>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-com-garagem-120m2-aluguel-RS1800-id-2906445220/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 110 m² · Fragoso</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Rua Marim dos Caetés</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Fragoso</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>1650.0</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>OLX Imóveis</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 85 m² · Derby</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Derby</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1700.0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>250.0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2056.0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>24.19</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-fragoso-olinda-com-garagem-110m2-aluguel-RS1500-id-2886093996/?source=ranking%2Crp</t>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-aluguel-3-quartos-derby-recife-pe-1527909868</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CTI Imobiliária</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 70 m² · Cordeiro</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Cordeiro</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>1700.0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>1700.0</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>24.29</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/2947</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>OLX Imóveis, Âncora Imobiliária</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 109 m² · Prado</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Prado</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1900.0</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>126.945</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2126.9449999999997</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>19.51</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-aluguel-3-quartos-1-vaga-prado-recife-pe-1527742370</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CTI Imobiliária</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 70 m² · Cordeiro</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Cordeiro</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1700.0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1700.0</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 70 m² · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Rua Antônio Silva Guimarães</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2140.0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2140.0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>24.29</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>30.57</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/1006</t>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-70m2-aluguel-RS2140-id-2896700211/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>OLX Imóveis</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Iputinga</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Iputinga</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1700.0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1700.0</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 100 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2300.0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2300.0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>28.33</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/perto-da-ufpe-1526627062</t>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-3-quartos-na-boa-vista-1-vaga-1527718836</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 90 m² · Rio Doce</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Travessa Coronel Frederico Lundgren</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Rio Doce</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1700.0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1700.0</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Rua João Clementino Montarroyos</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2300.0</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2300.0</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>18.89</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>31.94</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-rio-doce-olinda-com-garagem-90m2-aluguel-RS1700-id-2892631476/?source=ranking%2Crp</t>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 74 m² · Rio Doce</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Rua Maria da Conceição Viana</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Rio Doce</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>1700.0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>1700.0</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>22.97</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>OLX Imóveis</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 79 m² · 2 vagas · Encruzilhada</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Encruzilhada</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>521.0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2388.0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>30.23</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-rio-doce-olinda-com-garagem-74m2-aluguel-RS1700-id-2884604076/?source=ranking%2Crp</t>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-amplo-no-bairro-da-encruzilhada-1525389412</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Camila Melo Imóveis</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>OLX Imóveis</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 75 m² · 1 vaga · Boa Viagem</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Boa Viagem</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>24.32</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/aluguel-apartamento-3qts-mobiliado-boa-viagem-1527921083</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Camila Melo Imóveis</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>OLX Imóveis</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 100 m² · Casa Amarela</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Casa Amarela</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>24.32</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-em-casa-amarela-refomado-e-bem-localizado-para-alugar-1523968605</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Portal CRECI Brasil</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>OLX Imóveis</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · Várzea</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Várzea</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 100 m² · Casa Amarela</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Casa Amarela</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-varzea-recife--pe_33349791</t>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-refomado-e-bem-localizado-em-casa-amarela-para-alugar-1524274300</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Rua Joana Noberto Pessoa</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Rua Maria Ramos</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Bairro Novo</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>21.18</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>23.36</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1998,25 +2069,25 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 79 m² · Jardim Atlântico</t>
+          <t>Apartamento · 2 quartos · 85 m² · Iputinga</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rua Eurípedes Lavor Paes Barreto</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jardim Atlântico</t>
+          <t>Iputinga</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2026,52 +2097,52 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1842.0</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2081,7 +2152,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-com-garagem-79m2-aluguel-RS1500-id-2899186475/?source=ranking%2Crp</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-iputinga-recife-pe/4347</t>
         </is>
       </c>
     </row>
@@ -2089,30 +2160,30 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Graças</t>
+          <t>Apartamento · 3 quartos · 78 m² · Jardim Atlântico</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Olavo Bilac</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Jardim Atlântico</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1850.0</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2127,7 +2198,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1850.0</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2137,19 +2208,19 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -2157,12 +2228,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2172,7 +2243,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-78m2-aluguel-RS1500-id-2879884309/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2188,27 +2259,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Boa Viagem</t>
+          <t>Apartamento · 2 quartos · 70 m² · São José</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rua Coronel Anízio Rodrigues Coelho</t>
+          <t>Avenida Sul Governador Cid Sampaio</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Boa Viagem</t>
+          <t>São José</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1896.0</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2218,17 +2289,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1896.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>22.86</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2238,32 +2309,32 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-viagem-recife-com-garagem-60m2-aluguel-RS1896-id-2893138519/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-sao-jose-recife-70m2-aluguel-RS1500-id-2903759599/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2279,27 +2350,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 90 m² · Jardim Atlântico</t>
+          <t>Apartamento · 3 quartos · 110 m² · Fragoso</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rua Jornalista Edson Regis</t>
+          <t>Rua Marim dos Caetés</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jardim Atlântico</t>
+          <t>Fragoso</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1900.0</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2309,17 +2380,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1900.0</t>
+          <t>1650.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2329,7 +2400,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2339,22 +2410,22 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-com-garagem-90m2-aluguel-RS1900-id-2902068413/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-fragoso-olinda-com-garagem-110m2-aluguel-RS1500-id-2886093996/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2433,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2370,7 +2441,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Apartamento · 1355 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 70 m² · Cordeiro</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2380,12 +2451,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Cordeiro</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1925.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2400,7 +2471,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1925.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2410,12 +2481,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2430,22 +2501,22 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1355.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/studio-mobiliado-100m-da-fmo-e-40m-da-orla-melhor-local-ligue-hoje-mesmo-1527546954</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/2947</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2524,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2461,7 +2532,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 73 m² · Afogados</t>
+          <t>Apartamento · 2 quartos · 70 m² · Cordeiro</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2471,12 +2542,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Afogados</t>
+          <t>Cordeiro</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1950.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2491,7 +2562,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1950.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2501,12 +2572,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>26.71</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2521,22 +2592,22 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850191067-75</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-cordeiro-recife-pe/1006</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2615,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2552,22 +2623,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Imbiribeira</t>
+          <t>Apartamento · 3 quartos · 90 m² · Rio Doce</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rua Eládio Ramos</t>
+          <t>Travessa Coronel Frederico Lundgren</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Imbiribeira</t>
+          <t>Rio Doce</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1985.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2582,7 +2653,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1985.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2592,12 +2663,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>33.08</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2612,22 +2683,22 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-imbiribeira-recife-com-garagem-60m2-aluguel-RS1985-id-2903214422/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-rio-doce-olinda-com-garagem-90m2-aluguel-RS1700-id-2892631476/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2706,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2643,22 +2714,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Iputinga</t>
+          <t>Apartamento · 3 quartos · 74 m² · Rio Doce</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rua João Sales de Menezes</t>
+          <t>Rua Maria da Conceição Viana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Iputinga</t>
+          <t>Rio Doce</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2673,7 +2744,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2683,42 +2754,42 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>22.97</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-iputinga-recife-com-garagem-60m2-aluguel-RS2000-id-2904017640/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-rio-doce-olinda-com-garagem-74m2-aluguel-RS1700-id-2884604076/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2797,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2734,7 +2805,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Aldeia dos Camarás</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2744,42 +2815,42 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aldeia dos Camarás</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2002.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>33.37</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2794,22 +2865,22 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-para-locacao-em-aldeia-so-100m-do-centro-comercial-terreo-1451601323</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -2817,25 +2888,25 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OLX Imóveis, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Jardim Atlântico</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rua José Maurício Viana</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jardim Atlântico</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2845,7 +2916,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2855,52 +2926,52 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2050.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>120.0</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-com-3-quartos-em-jardim-atlantico-olinda-pe-1527601271</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -2908,30 +2979,30 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Iputinga</t>
+          <t>Apartamento · 2 quartos · Várzea</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rua Gaspar Perez</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Iputinga</t>
+          <t>Várzea</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2068.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2946,7 +3017,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2068.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2956,7 +3027,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>29.54</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2966,32 +3037,32 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-iputinga-recife-com-garagem-70m2-aluguel-RS2068-id-2893614874/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-varzea-recife--pe_33349791</t>
         </is>
       </c>
     </row>
@@ -3007,47 +3078,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 79 m² · Jardim Atlântico</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rua Antônio Silva Guimarães</t>
+          <t>Rua Eurípedes Lavor Paes Barreto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Jardim Atlântico</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2140.0</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2140.0</t>
+          <t>1842.0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3062,27 +3133,27 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-70m2-aluguel-RS2140-id-2896700211/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-jardim-atlantico-olinda-com-garagem-79m2-aluguel-RS1500-id-2899186475/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3090,30 +3161,30 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 85 m² · Boa Viagem</t>
+          <t>Apartamento · 2 quartos · 80 m² · Graças</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rua José Domingues da Silva</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Boa Viagem</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1850.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3128,7 +3199,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1850.0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3138,7 +3209,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>27.06</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3148,7 +3219,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3158,12 +3229,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3173,7 +3244,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-viagem-recife-com-garagem-85m2-aluguel-RS2300-id-2900737397/?source=ranking%2Crp</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3252,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -3189,22 +3260,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 60 m² · Boa Viagem</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Coronel Anízio Rodrigues Coelho</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Boa Viagem</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1896.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3219,7 +3290,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1896.0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3229,12 +3300,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3244,27 +3315,27 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-viagem-recife-com-garagem-60m2-aluguel-RS1896-id-2893138519/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3343,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -3280,7 +3351,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Boa Viagem</t>
+          <t>Apartamento · 3 quartos · 73 m² · Afogados</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3290,37 +3361,37 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Boa Viagem</t>
+          <t>Afogados</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1950.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>241.42</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2341.42</t>
+          <t>1950.0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>26.71</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3340,22 +3411,22 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/4504/apartamento-3-quartos-diva-boa-viagem-recife/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850191067-75</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3434,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OLX Imóveis, REMAX Recife e Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3371,22 +3442,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Boa Viagem</t>
+          <t>Apartamento · 2 quartos · 60 m² · Imbiribeira</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Eládio Ramos</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Boa Viagem</t>
+          <t>Imbiribeira</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>1985.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3401,7 +3472,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>1985.0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3411,7 +3482,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>33.08</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3421,7 +3492,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3436,17 +3507,17 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-possui-60-metros-quadrados-com-2-quartos-em-boa-viagem-recife-pe-1527394922</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-imbiribeira-recife-com-garagem-60m2-aluguel-RS1985-id-2903214422/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3462,22 +3533,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 110 m² · Cordeiro</t>
+          <t>Apartamento · 2 quartos · 70 m² · Iputinga</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Avenida Caxangá</t>
+          <t>Rua Gaspar Perez</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cordeiro</t>
+          <t>Iputinga</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2068.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3492,7 +3563,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2068.0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3502,7 +3573,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>29.54</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3512,32 +3583,32 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-cordeiro-recife-com-garagem-110m2-aluguel-RS2400-id-2903630297/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-iputinga-recife-com-garagem-70m2-aluguel-RS2068-id-2893614874/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3616,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3553,22 +3624,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 85 m² · Boa Viagem</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua José Domingues da Silva</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Boa Viagem</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3583,7 +3654,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3593,12 +3664,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>27.06</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3613,12 +3684,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3628,7 +3699,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-viagem-recife-com-garagem-85m2-aluguel-RS2300-id-2900737397/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3636,45 +3707,45 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 120 m² · Boa Viagem</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Boa Viagem</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>241.42</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2341.42</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3684,7 +3755,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3694,7 +3765,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3709,17 +3780,17 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-120m2-aluguel-RS2200-id-2886278592/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/4504/apartamento-3-quartos-diva-boa-viagem-recife/</t>
         </is>
       </c>
     </row>
@@ -3727,30 +3798,30 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 2 quartos · 110 m² · Cordeiro</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Caxangá</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Cordeiro</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3765,7 +3836,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3775,42 +3846,42 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>120.0</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-cordeiro-recife-com-garagem-110m2-aluguel-RS2400-id-2903630297/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3889,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3826,22 +3897,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rua Zeferino Agra</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3856,7 +3927,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3866,19 +3937,19 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="O38" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -3891,17 +3962,17 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3909,25 +3980,25 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3957,7 +4028,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3967,7 +4038,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3977,22 +4048,22 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -4000,88 +4071,270 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
+          <t>REMAX Recife e Olinda</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 60 m² · Boa Viagem</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Boa Viagem</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>41.67</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/1222-avenida-fernando-simoes-barbosa-ao-lado-do-restaurante-parraxaxa/850191105-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Viva Real, Zap Imóveis</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Rua Zeferino Agra</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Arruda</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C42" t="n">
         <v>2</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Casa Caiada</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>31.25</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,18 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -546,95 +539,91 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
         <is>
           <t>Âncora Imobiliária</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Arruda</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>1400.0</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>1450.0</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>19.33</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>75.0</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
         </is>
@@ -1372,7 +1361,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1380,7 +1369,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 100 m² · Casa Amarela</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1390,7 +1379,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1420,12 +1409,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1440,22 +1429,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-em-casa-amarela-refomado-e-bem-localizado-para-alugar-1523968605</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1463,25 +1452,25 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Zeferino Agra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1511,17 +1500,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1531,22 +1520,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1543,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1562,17 +1551,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua Zeferino Agra</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1602,17 +1591,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1622,22 +1611,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1653,17 +1642,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1693,7 +1682,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1703,121 +1692,30 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,12 +29,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -539,93 +546,97 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Âncora Imobiliária</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Arruda</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1450.0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Rua Otaviano Pessoa</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>19.33</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>25.71</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -633,7 +644,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -641,7 +652,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -651,12 +662,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1400.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,12 +677,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1450.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -681,12 +692,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -701,22 +712,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
         </is>
       </c>
     </row>
@@ -807,7 +818,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -815,25 +826,25 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -863,42 +874,42 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -906,55 +917,55 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Derby</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2056.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -964,7 +975,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -979,17 +990,17 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-aluguel-3-quartos-derby-recife-pe-1527909868</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -997,55 +1008,55 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 85 m² · Derby</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rua Antônio Silva Guimarães</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2140.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2140.0</t>
+          <t>2056.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>24.19</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1055,7 +1066,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1065,22 +1076,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-70m2-aluguel-RS2140-id-2896700211/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-aluguel-3-quartos-derby-recife-pe-1527909868</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1107,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 70 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Antônio Silva Guimarães</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1111,7 +1122,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2140.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1126,7 +1137,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2140.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1136,7 +1147,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1156,7 +1167,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1171,7 +1182,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-70m2-aluguel-RS2140-id-2896700211/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1179,55 +1190,55 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 79 m² · 2 vagas · Encruzilhada</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>521.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2388.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1237,7 +1248,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1247,22 +1258,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-amplo-no-bairro-da-encruzilhada-1525389412</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1270,55 +1281,55 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 79 m² · 2 vagas · Encruzilhada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>521.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2388.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1328,7 +1339,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1338,22 +1349,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-amplo-no-bairro-da-encruzilhada-1525389412</t>
         </is>
       </c>
     </row>
@@ -1361,30 +1372,30 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1399,7 +1410,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1409,7 +1420,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1419,7 +1430,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1429,22 +1440,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1452,25 +1463,25 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua Zeferino Agra</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1500,17 +1511,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1520,22 +1531,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1554,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1551,17 +1562,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Rua Zeferino Agra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1591,17 +1602,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1611,22 +1622,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1642,80 +1653,171 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Rua Maria Ramos</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>23.36</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Casa Caiada</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>31.25</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,18 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -546,97 +539,93 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Âncora Imobiliária</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Rua Otaviano Pessoa</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Arruda</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1450.0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>25.71</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>19.33</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
         </is>
       </c>
     </row>
@@ -644,7 +633,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -652,7 +641,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -662,12 +651,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -677,12 +666,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -692,42 +681,42 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -818,7 +807,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -826,7 +815,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -834,17 +823,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -874,17 +863,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -894,22 +883,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -917,11 +906,11 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,11 +1088,11 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1190,11 +1179,11 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1372,11 +1361,11 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1445,12 +1434,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1645,11 +1634,11 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1736,11 +1725,11 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,12 +29,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -539,93 +546,97 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Âncora Imobiliária</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>OLX Imóveis</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Arruda</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1450.0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2360.0</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2360.0</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>19.33</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>32.78</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
         </is>
       </c>
     </row>
@@ -633,7 +644,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -641,7 +652,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -651,12 +662,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1400.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,12 +677,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1450.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -681,12 +692,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -701,22 +712,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
         </is>
       </c>
     </row>
@@ -807,7 +818,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -815,7 +826,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -823,17 +834,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -863,42 +874,42 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -906,7 +917,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -914,12 +925,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -954,7 +965,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -964,7 +975,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -974,22 +985,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -997,55 +1008,55 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Derby</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2056.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1055,7 +1066,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1070,17 +1081,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-aluguel-3-quartos-derby-recife-pe-1527909868</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1099,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1096,47 +1107,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 85 m² · Derby</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua Antônio Silva Guimarães</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2140.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2140.0</t>
+          <t>2056.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>24.19</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1146,7 +1157,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1156,22 +1167,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-70m2-aluguel-RS2140-id-2896700211/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-aluguel-3-quartos-derby-recife-pe-1527909868</t>
         </is>
       </c>
     </row>
@@ -1179,11 +1190,11 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1361,11 +1372,11 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1434,12 +1445,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1634,11 +1645,11 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1725,11 +1736,11 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,18 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -546,97 +539,93 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Âncora Imobiliária</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2360.0</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>2360.0</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Arruda</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1450.0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>32.78</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>19.33</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
         </is>
       </c>
     </row>
@@ -644,7 +633,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -652,7 +641,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -662,12 +651,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -677,12 +666,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -692,42 +681,42 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -818,7 +807,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -826,7 +815,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -834,17 +823,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -874,17 +863,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -894,22 +883,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -917,20 +906,20 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -965,7 +954,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -975,7 +964,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -985,22 +974,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1008,55 +997,55 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 85 m² · Derby</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2056.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>24.19</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1066,7 +1055,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1081,17 +1070,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-aluguel-3-quartos-derby-recife-pe-1527909868</t>
         </is>
       </c>
     </row>
@@ -1099,55 +1088,55 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Derby</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2056.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1157,7 +1146,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1167,22 +1156,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-aluguel-3-quartos-derby-recife-pe-1527909868</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1190,20 +1179,20 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1213,7 +1202,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1228,7 +1217,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1238,7 +1227,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>32.78</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1248,7 +1237,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1263,17 +1252,17 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
         </is>
       </c>
     </row>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -997,55 +997,55 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Derby</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2056.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-aluguel-3-quartos-derby-recife-pe-1527909868</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1156,22 +1156,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>32.78</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1247,22 +1247,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1270,65 +1270,65 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 79 m² · 2 vagas · Encruzilhada</t>
+          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Zeferino Agra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>521.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2388.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-amplo-no-bairro-da-encruzilhada-1525389412</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1369,22 +1369,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1429,22 +1429,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1452,25 +1452,25 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1510,303 +1510,30 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
-        <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Viva Real, Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Rua Zeferino Agra</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Arruda</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Rua Maria Ramos</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>23.36</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,12 +29,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -539,184 +546,192 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Âncora Imobiliária</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Arruda</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1450.0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>OLX Imóveis, Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Rua João Clementino Montarroyos</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>19.33</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>32.47</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/edf-felix-conj-res-vaticano-1528244119</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Camila Melo Imóveis</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Rua Maria Ramos</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>24.32</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>23.36</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -724,7 +739,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -732,7 +747,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -742,12 +757,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1400.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -757,12 +772,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1450.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -772,12 +787,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -792,22 +807,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
         </is>
       </c>
     </row>
@@ -815,7 +830,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -823,17 +838,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -863,17 +878,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -883,22 +898,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -906,25 +921,25 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -954,17 +969,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -974,22 +989,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -997,30 +1012,30 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1035,7 +1050,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1045,7 +1060,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1055,32 +1070,32 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -1096,22 +1111,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1126,7 +1141,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1136,7 +1151,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1146,32 +1161,32 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1179,30 +1194,30 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1217,7 +1232,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1227,7 +1242,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1237,7 +1252,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1247,22 +1262,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1285,7 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1278,22 +1293,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rua Zeferino Agra</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1308,7 +1323,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1318,19 +1333,19 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -1343,17 +1358,17 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>29</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1361,25 +1376,25 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1409,7 +1424,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1419,7 +1434,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1429,22 +1444,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1467,7 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1460,80 +1475,171 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Rua Zeferino Agra</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Arruda</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Casa Caiada</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>31.25</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -553,11 +553,11 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>OLX Imóveis, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda, OLX Imóveis, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -636,102 +636,98 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/edf-felix-conj-res-vaticano-1528244119</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Rua Maria Ramos</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Âncora Imobiliária</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Arruda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1450.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>23.36</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>19.33</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
         </is>
       </c>
     </row>
@@ -739,7 +735,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -747,7 +743,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -757,12 +753,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -772,12 +768,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -787,12 +783,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -807,22 +803,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -913,7 +909,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -921,7 +917,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -929,17 +925,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -969,17 +965,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -989,22 +985,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -1012,20 +1008,20 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1060,7 +1056,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1070,32 +1066,32 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1107,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1141,7 +1137,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1151,7 +1147,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1171,22 +1167,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1198,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1217,7 +1213,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1232,7 +1228,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1242,7 +1238,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1252,7 +1248,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1262,22 +1258,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1285,30 +1281,30 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1323,7 +1319,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1333,7 +1329,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1343,32 +1339,32 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1372,25 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Zeferino Agra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1424,17 +1420,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1444,22 +1440,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>29</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1463,7 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1475,17 +1471,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua Zeferino Agra</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1515,17 +1511,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1535,22 +1531,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,18 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -546,97 +539,93 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda, OLX Imóveis, Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Rua João Clementino Montarroyos</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Âncora Imobiliária</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Arruda</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1450.0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>32.47</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>19.33</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
         </is>
       </c>
     </row>
@@ -644,7 +633,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -652,7 +641,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -662,12 +651,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -677,12 +666,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -692,12 +681,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,22 +701,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -818,7 +807,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -826,7 +815,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -834,17 +823,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -874,17 +863,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -894,22 +883,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -917,20 +906,20 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -965,7 +954,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -975,32 +964,32 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1016,22 +1005,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1046,7 +1035,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1056,7 +1045,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1076,22 +1065,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1096,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1122,7 +1111,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1137,7 +1126,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1147,7 +1136,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1157,7 +1146,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1167,22 +1156,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1190,15 +1179,15 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda, OLX Imóveis, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1213,7 +1202,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1228,7 +1217,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1238,7 +1227,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1248,7 +1237,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1258,22 +1247,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,12 +29,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -539,184 +546,192 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Âncora Imobiliária</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>OLX Imóveis</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Arruda</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1450.0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 20240 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2300.0</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2300.0</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>19.33</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>20240.0</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/studio-no-bairro-novo-em-frente-a-fmo-1528408505</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Camila Melo Imóveis</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>OLX Imóveis</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2300.0</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2300.0</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>24.32</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>32.86</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-apt-em-casa-caiada-proximo-a-caixa-economica-1528362969</t>
         </is>
       </c>
     </row>
@@ -724,7 +739,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -732,7 +747,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -742,12 +757,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1400.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -757,12 +772,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1450.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -772,12 +787,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -792,22 +807,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
         </is>
       </c>
     </row>
@@ -815,7 +830,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -823,22 +838,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 100 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -853,7 +868,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -863,42 +878,42 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-100m-reformado-ventilado-semi-mobiliado-no-centro-da-boa-vista-9-andar-1507545093</t>
         </is>
       </c>
     </row>
@@ -906,25 +921,25 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -954,17 +969,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -974,22 +989,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -997,30 +1012,30 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1035,7 +1050,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1045,17 +1060,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1065,22 +1080,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -1088,30 +1103,30 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1126,7 +1141,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1136,7 +1151,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1156,22 +1171,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -1179,30 +1194,30 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, OLX Imóveis, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1217,7 +1232,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1227,7 +1242,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1247,22 +1262,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1270,30 +1285,30 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1308,7 +1323,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1318,7 +1333,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1328,7 +1343,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1338,22 +1353,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1361,30 +1376,30 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rua Zeferino Agra</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1399,7 +1414,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1409,17 +1424,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>32.78</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1429,22 +1444,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
         </is>
       </c>
     </row>
@@ -1460,22 +1475,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1490,7 +1505,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1500,7 +1515,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1510,7 +1525,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1520,22 +1535,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1543,88 +1558,452 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Rua João Clementino Montarroyos</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>32.47</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Portal CRECI Brasil</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Santo Amaro</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>20.83</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Viva Real, Zap Imóveis</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Rua Zeferino Agra</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Arruda</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C16" t="n">
         <v>2</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Rua Maria Ramos</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>23.36</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Casa Caiada</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>31.25</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -553,20 +553,20 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 20240 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,17 +601,17 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -621,22 +621,22 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20240.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/studio-no-bairro-novo-em-frente-a-fmo-1528408505</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -656,7 +656,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -666,37 +666,37 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>105.95</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2055.95</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>32.86</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -726,103 +726,107 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-apt-em-casa-caiada-proximo-a-caixa-economica-1528362969</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Âncora Imobiliária</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Arruda</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>1450.0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Rua João Clementino Montarroyos</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>19.33</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>32.47</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -830,7 +834,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -838,7 +842,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 100 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -848,12 +852,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>1400.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -863,12 +867,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>1450.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -878,12 +882,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -898,7 +902,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -908,12 +912,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-100m-reformado-ventilado-semi-mobiliado-no-centro-da-boa-vista-9-andar-1507545093</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
         </is>
       </c>
     </row>
@@ -994,7 +998,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1085,7 +1089,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1176,7 +1180,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1202,22 +1206,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1232,7 +1236,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1242,7 +1246,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1262,22 +1266,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1297,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1308,7 +1312,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1323,7 +1327,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1333,7 +1337,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1343,7 +1347,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1353,22 +1357,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1380,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1384,7 +1388,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1394,12 +1398,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1414,7 +1418,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1424,7 +1428,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>32.78</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1444,22 +1448,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1471,7 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1475,22 +1479,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Zeferino Agra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1505,7 +1509,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1515,12 +1519,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1540,7 +1544,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1550,7 +1554,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1558,25 +1562,25 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1606,7 +1610,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1616,7 +1620,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1626,22 +1630,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1649,25 +1653,25 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1697,7 +1701,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1707,303 +1711,30 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
-        <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Viva Real, Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Rua Zeferino Agra</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Arruda</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Rua Maria Ramos</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>23.36</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,18 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -546,287 +539,275 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Rua Joana Noberto Pessoa</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Âncora Imobiliária</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Arruda</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1450.0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>21.18</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>19.33</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Âncora Imobiliária</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Camila Melo Imóveis</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Derby</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1700.0</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>250.0</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>105.95</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2055.95</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>24.48</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Apartamento · 74 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Rua João Clementino Montarroyos</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Camila Melo Imóveis</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Apartamento · 74 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>32.47</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -834,7 +815,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -842,22 +823,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -867,12 +848,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -882,7 +863,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -892,7 +873,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -902,7 +883,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -917,7 +898,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -925,25 +906,25 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -973,17 +954,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -993,22 +974,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1016,7 +997,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1024,7 +1005,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1034,42 +1015,42 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>105.95</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2055.95</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1084,22 +1065,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
         </is>
       </c>
     </row>
@@ -1107,30 +1088,30 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1145,7 +1126,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1155,7 +1136,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1165,7 +1146,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1175,22 +1156,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1187,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1221,7 +1202,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1236,7 +1217,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1246,7 +1227,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1256,7 +1237,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1266,22 +1247,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1289,15 +1270,15 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1312,7 +1293,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1327,7 +1308,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1337,7 +1318,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1347,7 +1328,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1357,22 +1338,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,12 +29,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -539,93 +546,97 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Âncora Imobiliária</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Arruda</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1450.0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Rua João Clementino Montarroyos</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2300.0</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2300.0</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>19.33</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>31.94</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -633,7 +644,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -641,7 +652,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -651,12 +662,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1400.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,12 +677,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1450.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -681,12 +692,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -701,22 +712,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
         </is>
       </c>
     </row>
@@ -807,7 +818,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -815,7 +826,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -823,17 +834,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -863,17 +874,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -883,22 +894,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -906,20 +917,20 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -954,7 +965,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -964,7 +975,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -974,22 +985,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -997,55 +1008,55 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>105.95</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2055.95</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1055,7 +1066,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1065,22 +1076,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1088,55 +1099,55 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>105.95</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2055.95</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1146,7 +1157,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1156,22 +1167,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
         </is>
       </c>
     </row>
@@ -1179,20 +1190,20 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1202,7 +1213,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1217,7 +1228,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1227,7 +1238,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>32.78</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1237,32 +1248,32 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
         </is>
       </c>
     </row>
@@ -1270,15 +1281,15 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1293,7 +1304,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1308,7 +1319,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1318,7 +1329,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1328,7 +1339,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1338,22 +1349,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1361,25 +1372,25 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1409,7 +1420,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1419,7 +1430,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1429,22 +1440,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1452,25 +1463,25 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+          <t>Apartamento · 100 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua Zeferino Agra</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1500,42 +1511,42 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-em-casa-amarela-refomado-e-bem-localizado-para-alugar-1523968605</t>
         </is>
       </c>
     </row>
@@ -1543,25 +1554,25 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+          <t>Apartamento · 100 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1591,17 +1602,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1611,22 +1622,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-refomado-e-bem-localizado-em-casa-amarela-para-alugar-1524274300</t>
         </is>
       </c>
     </row>
@@ -1634,88 +1645,361 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
+          <t>Portal CRECI Brasil</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Santo Amaro</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>20.83</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Viva Real, Zap Imóveis</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Rua Zeferino Agra</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Arruda</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C16" t="n">
         <v>2</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Rua Maria Ramos</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>23.36</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Casa Caiada</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>31.25</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -553,30 +553,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 70 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1850.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1850.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,17 +601,17 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -621,22 +621,22 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-casa-amarela-2-quartos-1528698567</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1190,20 +1190,20 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>32.78</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1263,17 +1263,17 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1281,55 +1281,55 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 79 m² · 2 vagas · Encruzilhada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>521.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2388.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1349,22 +1349,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-amplo-no-bairro-da-encruzilhada-1525389412</t>
         </is>
       </c>
     </row>
@@ -1372,15 +1372,15 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1440,22 +1440,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1463,25 +1463,25 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 100 m² · Casa Amarela</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-em-casa-amarela-refomado-e-bem-localizado-para-alugar-1523968605</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-refomado-e-bem-localizado-em-casa-amarela-para-alugar-1524274300</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-em-casa-amarela-refomado-e-bem-localizado-para-alugar-1523968605</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 100 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1693,42 +1693,42 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>120.0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-refomado-e-bem-localizado-em-casa-amarela-para-alugar-1524274300</t>
         </is>
       </c>
     </row>
@@ -1736,25 +1736,25 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rua Zeferino Agra</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1804,22 +1804,22 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1835,17 +1835,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Rua Zeferino Agra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1895,22 +1895,22 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1926,80 +1926,171 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Rua Maria Ramos</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>23.36</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Casa Caiada</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>31.25</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Casa Amarela</t>
+          <t>Apartamento · 4 quartos · 100 m² · 1 vaga · Arruda</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1850.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>1850.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -636,98 +636,102 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-casa-amarela-2-quartos-1528698567</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-no-arruda-1528830595</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Âncora Imobiliária</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Arruda</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1450.0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Rua João Clementino Montarroyos</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2300.0</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2300.0</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>19.33</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>31.94</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -735,7 +739,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -743,7 +747,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -753,12 +757,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1400.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -768,12 +772,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1450.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -783,12 +787,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -803,22 +807,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
         </is>
       </c>
     </row>
@@ -909,7 +913,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -917,7 +921,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -925,17 +929,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -965,17 +969,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -985,22 +989,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -1008,20 +1012,20 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1056,7 +1060,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1066,7 +1070,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1076,22 +1080,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -1099,55 +1103,55 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>105.95</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2055.95</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1157,7 +1161,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1167,22 +1171,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1190,55 +1194,55 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>105.95</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2055.95</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1248,32 +1252,32 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1293,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 79 m² · 2 vagas · Encruzilhada</t>
+          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1299,37 +1303,37 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>521.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2388.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>32.78</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1349,7 +1353,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1364,7 +1368,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-amplo-no-bairro-da-encruzilhada-1525389412</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
         </is>
       </c>
     </row>
@@ -1372,55 +1376,55 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 79 m² · 2 vagas · Encruzilhada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>521.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2388.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1430,7 +1434,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1440,22 +1444,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-amplo-no-bairro-da-encruzilhada-1525389412</t>
         </is>
       </c>
     </row>
@@ -1463,15 +1467,15 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1486,7 +1490,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1501,7 +1505,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1511,7 +1515,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1521,7 +1525,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1531,22 +1535,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1554,25 +1558,25 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 100 m² · Casa Amarela</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1602,17 +1606,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1622,22 +1626,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-em-casa-amarela-refomado-e-bem-localizado-para-alugar-1523968605</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1649,7 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1653,7 +1657,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 100 m² · Casa Amarela</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1663,7 +1667,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1693,12 +1697,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1713,22 +1717,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-refomado-e-bem-localizado-em-casa-amarela-para-alugar-1524274300</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1736,25 +1740,25 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Zeferino Agra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1784,17 +1788,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1804,22 +1808,22 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1831,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1835,17 +1839,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rua Zeferino Agra</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1875,17 +1879,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1895,22 +1899,22 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1926,17 +1930,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1966,7 +1970,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1976,121 +1980,30 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -553,30 +553,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 100 m² · 1 vaga · Arruda</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,17 +601,17 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -621,117 +621,113 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-no-arruda-1528830595</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Rua João Clementino Montarroyos</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>2300.0</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2300.0</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Âncora Imobiliária</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Arruda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1450.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>31.94</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>19.33</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
         </is>
       </c>
     </row>
@@ -739,7 +735,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -747,7 +743,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -757,12 +753,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -772,12 +768,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -787,12 +783,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -807,22 +803,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -903,7 +899,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -913,7 +909,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -921,7 +917,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -929,17 +925,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -969,17 +965,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -989,22 +985,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -1012,20 +1008,20 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1060,7 +1056,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1070,7 +1066,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1080,22 +1076,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1103,30 +1099,30 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 4 quartos · 100 m² · 1 vaga · Arruda</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1141,7 +1137,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1151,42 +1147,42 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-no-arruda-1528830595</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1263,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1285,20 +1281,20 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1308,7 +1304,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1323,7 +1319,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1333,7 +1329,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>32.78</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1343,7 +1339,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1358,17 +1354,17 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1376,55 +1372,55 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 79 m² · 2 vagas · Encruzilhada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>521.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2388.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1434,7 +1430,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1444,22 +1440,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>32</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-amplo-no-bairro-da-encruzilhada-1525389412</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1467,30 +1463,30 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1505,7 +1501,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1515,7 +1511,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1525,7 +1521,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1535,22 +1531,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1558,25 +1554,25 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Zeferino Agra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1606,17 +1602,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1626,22 +1622,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1649,25 +1645,25 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1697,7 +1693,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1707,7 +1703,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1717,22 +1713,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1736,7 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1748,17 +1744,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rua Zeferino Agra</t>
+          <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1793,17 +1789,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1813,197 +1809,15 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Rua Maria Ramos</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>23.36</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,18 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -546,97 +539,93 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Rua João Clementino Montarroyos</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Âncora Imobiliária</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Arruda</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1450.0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>32.47</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>19.33</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
         </is>
       </c>
     </row>
@@ -644,7 +633,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -652,7 +641,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
+          <t>Apartamento · 100 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -662,12 +651,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -677,12 +666,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -692,12 +681,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,22 +701,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-100m-reformado-ventilado-semi-mobiliado-no-centro-da-boa-vista-9-andar-1507545093</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1088,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1107,7 +1096,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 100 m² · 1 vaga · Arruda</t>
+          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1117,42 +1106,42 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>105.95</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2055.95</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1167,22 +1156,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-no-arruda-1528830595</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
         </is>
       </c>
     </row>
@@ -1190,55 +1179,55 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>105.95</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2055.95</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1248,7 +1237,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1258,22 +1247,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1281,20 +1270,20 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1304,7 +1293,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1319,7 +1308,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1329,7 +1318,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>32.78</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1339,7 +1328,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1354,17 +1343,17 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
         </is>
       </c>
     </row>
@@ -1463,25 +1452,25 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1511,7 +1500,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1521,7 +1510,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1531,22 +1520,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1554,25 +1543,25 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua Zeferino Agra</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1602,17 +1591,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1622,22 +1611,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1634,7 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1653,17 +1642,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Rua Zeferino Agra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1693,17 +1682,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1713,22 +1702,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1744,80 +1733,171 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Rua Maria Ramos</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>23.36</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Casa Caiada</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>31.25</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -615,7 +615,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -633,7 +633,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Apartamento · 100 m² · Boa Vista</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -701,22 +701,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-100m-reformado-ventilado-semi-mobiliado-no-centro-da-boa-vista-9-andar-1507545093</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -823,17 +823,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -863,17 +863,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -883,22 +883,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -906,20 +906,20 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -974,22 +974,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -997,55 +997,55 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>105.95</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2055.95</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
         </is>
       </c>
     </row>
@@ -1088,55 +1088,55 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>105.95</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2055.95</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1156,22 +1156,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1247,22 +1247,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>33</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1270,20 +1270,20 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>32.78</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1361,30 +1361,30 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1429,22 +1429,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1452,25 +1452,25 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Zeferino Agra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1520,22 +1520,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1543,25 +1543,25 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1611,22 +1611,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1642,17 +1642,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rua Zeferino Agra</t>
+          <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1687,17 +1687,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1707,197 +1707,15 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Rua Maria Ramos</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>23.36</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,12 +29,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -539,93 +546,97 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Âncora Imobiliária</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 60 m² · Arruda</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Avenida Beberibe</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Arruda</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1450.0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2315.0</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>174.0</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2489.0</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>19.33</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>41.48</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-60m2-aluguel-RS2315-id-2899617480/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -633,7 +644,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -641,7 +652,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -651,12 +662,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1400.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,12 +677,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1450.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -681,12 +692,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -701,22 +712,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
         </is>
       </c>
     </row>
@@ -807,7 +818,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -815,7 +826,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -823,17 +834,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -863,17 +874,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -883,22 +894,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -906,20 +917,20 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -954,7 +965,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -964,7 +975,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -974,22 +985,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -997,55 +1008,55 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>105.95</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2055.95</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1055,7 +1066,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1065,22 +1076,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1088,55 +1099,55 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>105.95</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2055.95</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1146,7 +1157,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1156,22 +1167,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1198,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1202,7 +1213,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1217,7 +1228,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1227,7 +1238,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1237,7 +1248,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1247,22 +1258,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1270,15 +1281,15 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1293,7 +1304,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1308,7 +1319,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1318,7 +1329,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1328,7 +1339,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1338,22 +1349,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>33</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1361,25 +1372,25 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1409,7 +1420,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1419,7 +1430,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1429,22 +1440,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1452,25 +1463,25 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua Zeferino Agra</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1500,17 +1511,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1520,22 +1531,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1554,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1551,17 +1562,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Rua Zeferino Agra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1591,17 +1602,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1611,22 +1622,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>33</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1642,80 +1653,171 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Rua Maria Ramos</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>23.36</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Casa Caiada</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>31.25</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -553,30 +553,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Avenida Beberibe</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2315.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2489.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>41.48</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -616,27 +616,27 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-60m2-aluguel-RS2315-id-2899617480/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1372,25 +1372,25 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1440,22 +1440,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1463,25 +1463,25 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Zeferino Agra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1531,22 +1531,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>34</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1562,17 +1562,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua Zeferino Agra</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1602,17 +1602,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1622,22 +1622,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1653,17 +1653,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1703,121 +1703,30 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,18 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -546,97 +539,93 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Rua João Clementino Montarroyos</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Âncora Imobiliária</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Arruda</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1450.0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>32.47</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>19.33</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
         </is>
       </c>
     </row>
@@ -644,7 +633,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -652,7 +641,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -662,12 +651,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -677,12 +666,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -692,12 +681,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,22 +701,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -808,7 +797,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -818,7 +807,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -826,7 +815,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -834,17 +823,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -874,17 +863,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -894,22 +883,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -917,20 +906,20 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -965,7 +954,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -975,7 +964,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -985,22 +974,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1008,55 +997,55 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>105.95</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2055.95</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1066,7 +1055,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1076,22 +1065,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
         </is>
       </c>
     </row>
@@ -1099,55 +1088,55 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>105.95</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2055.95</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1157,7 +1146,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1167,22 +1156,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1187,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1213,7 +1202,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1228,7 +1217,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1238,7 +1227,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1248,7 +1237,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1258,22 +1247,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1281,30 +1270,30 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 60 m² · Arruda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Avenida Beberibe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2315.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1314,12 +1303,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2489.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1329,42 +1318,42 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>41.48</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-60m2-aluguel-RS2315-id-2899617480/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1372,25 +1361,25 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1420,7 +1409,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1430,7 +1419,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1440,22 +1429,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1463,25 +1452,25 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua Zeferino Agra</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1511,17 +1500,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1531,22 +1520,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1543,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1562,17 +1551,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Rua Zeferino Agra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1602,17 +1591,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1622,22 +1611,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1653,80 +1642,171 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Rua Maria Ramos</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>23.36</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Casa Caiada</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>31.25</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,12 +29,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -539,366 +546,382 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Âncora Imobiliária</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Arruda</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1450.0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Rua Joana Noberto Pessoa</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>182.0</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>1982.0</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>19.33</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>23.32</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Camila Melo Imóveis</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>OLX Imóveis</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Arruda</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Arruda</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>24.32</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-arruda-1529925280</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Camila Melo Imóveis</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>24.32</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>OLX Imóveis, Âncora Imobiliária</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Derby</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1700.0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>250.0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>105.975</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2055.975</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>24.48</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-possui-84-metros-quadrados-com-3-quartos-em-derby-recife-pe-1530031414</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Rua Otaviano Pessoa</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real, Zap Imóveis</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 90 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Rua do Riachuelo</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2317.0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2317.0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>25.71</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>25.74</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-vista-recife-90m2-aluguel-RS2317-id-2904925102/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -906,30 +929,30 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 100 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -944,7 +967,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -954,17 +977,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -974,7 +997,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -989,7 +1012,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-100m-reformado-ventilado-semi-mobiliado-no-centro-da-boa-vista-9-andar-1507545093</t>
         </is>
       </c>
     </row>
@@ -997,7 +1020,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1005,7 +1028,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1015,42 +1038,42 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>105.95</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2055.95</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1065,22 +1088,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -1088,30 +1111,30 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1126,7 +1149,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1136,17 +1159,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1156,22 +1179,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -1179,30 +1202,30 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1217,7 +1240,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1227,7 +1250,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1247,22 +1270,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -1270,30 +1293,30 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Avenida Beberibe</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2315.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1303,12 +1326,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2489.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1318,12 +1341,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>41.48</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1333,27 +1356,27 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-60m2-aluguel-RS2315-id-2899617480/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1361,15 +1384,15 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1384,7 +1407,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1399,7 +1422,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1409,7 +1432,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1419,7 +1442,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1429,22 +1452,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1452,25 +1475,25 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1500,7 +1523,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1510,7 +1533,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1520,22 +1543,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1543,25 +1566,25 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua Zeferino Agra</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1591,17 +1614,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1611,22 +1634,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1642,17 +1665,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1682,7 +1705,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1692,32 +1715,32 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1733,17 +1756,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1773,7 +1796,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1783,32 +1806,32 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -553,20 +553,20 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 1251 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2199.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>1982.0</t>
+          <t>2199.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,17 +601,17 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -621,307 +621,295 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>1251.0</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apt-studio-c-mobilia-90m-da-fmo-e-30m-da-praia-reserve-agora-1530115997</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Camila Melo Imóveis</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Arruda</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Arruda</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>2000.0</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2000.0</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Apartamento · 74 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-arruda-1529925280</t>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis, Âncora Imobiliária</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Derby</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1700.0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>250.0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>105.975</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2055.975</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>24.48</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-possui-84-metros-quadrados-com-3-quartos-em-derby-recife-pe-1530031414</t>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Camila Melo Imóveis</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Apartamento · 74 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Viva Real, Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 90 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Rua do Riachuelo</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2317.0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2317.0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Rua Otaviano Pessoa</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>25.74</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>25.71</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-vista-recife-90m2-aluguel-RS2317-id-2904925102/?source=ranking%2Crp</t>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -929,30 +917,30 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 100 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -962,12 +950,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>1982.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -977,17 +965,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,12 +985,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1012,7 +1000,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-100m-reformado-ventilado-semi-mobiliado-no-centro-da-boa-vista-9-andar-1507545093</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1008,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1028,7 +1016,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1038,42 +1026,42 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>105.95</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2055.95</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1088,22 +1076,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
         </is>
       </c>
     </row>
@@ -1111,30 +1099,30 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1149,7 +1137,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1159,17 +1147,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1179,22 +1167,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1202,30 +1190,30 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1240,7 +1228,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1250,7 +1238,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1270,22 +1258,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>36</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1293,15 +1281,15 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1316,7 +1304,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1331,7 +1319,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1341,7 +1329,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1361,22 +1349,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1384,30 +1372,30 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1422,7 +1410,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1432,7 +1420,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1442,7 +1430,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1452,22 +1440,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1475,20 +1463,20 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1523,7 +1511,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1538,27 +1526,27 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1566,25 +1554,25 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1614,7 +1602,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1624,7 +1612,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1634,202 +1622,20 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
-        <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Rua Maria Ramos</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>23.36</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -553,20 +553,20 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 1251 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2199.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2199.0</t>
+          <t>1982.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,17 +601,17 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -621,295 +621,307 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>1251.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apt-studio-c-mobilia-90m-da-fmo-e-30m-da-praia-reserve-agora-1530115997</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Camila Melo Imóveis</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>OLX Imóveis</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Encruzilhada</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>24.32</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>28.57</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-otimo-apartamento-com-2-quartos-no-bairro-da-encruzilhada-recife-1530342968</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Camila Melo Imóveis</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real, Zap Imóveis</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 60 m² · Arruda</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Rua José de Barros Bezerra</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Arruda</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>24.32</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-60m2-aluguel-RS2000-id-2908173232/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>OLX Imóveis</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Rua Otaviano Pessoa</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 87 m² · Espinheiro</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Espinheiro</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2200.0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2200.0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>25.71</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>25.29</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-e-venda-com-87-metros-quadrados-com-3-quartos-em-espinheiro-recife-1530348025</t>
         </is>
       </c>
     </row>
@@ -917,25 +929,25 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -950,12 +962,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1982.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -965,17 +977,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -985,22 +997,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1020,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1016,7 +1028,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1026,42 +1038,42 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>105.95</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2055.95</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1076,22 +1088,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -1099,30 +1111,30 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1137,7 +1149,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1147,7 +1159,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1157,7 +1169,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1167,22 +1179,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -1190,55 +1202,55 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>105.95</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2055.95</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1248,7 +1260,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1258,22 +1270,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
         </is>
       </c>
     </row>
@@ -1281,15 +1293,15 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1304,7 +1316,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1319,7 +1331,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1329,7 +1341,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1349,22 +1361,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1372,30 +1384,30 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1410,7 +1422,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1420,7 +1432,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1430,7 +1442,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1440,22 +1452,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>36</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1463,20 +1475,20 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1511,7 +1523,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1526,27 +1538,27 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1554,88 +1566,270 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
+          <t>Portal CRECI Brasil</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Santo Amaro</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>20.83</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C14" t="n">
         <v>2</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Rua Alcina Coelho de Carvalho</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Rua Maria Ramos</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Bairro Novo</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>23.36</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>107.0</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,18 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -546,382 +539,366 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Rua Joana Noberto Pessoa</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Camila Melo Imóveis</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Apartamento · 74 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>1800.0</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>182.0</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>1982.0</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>23.32</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Camila Melo Imóveis</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Encruzilhada</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>2000.0</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2000.0</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Apartamento · 74 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>28.57</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-otimo-apartamento-com-2-quartos-no-bairro-da-encruzilhada-recife-1530342968</t>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Viva Real, Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 60 m² · Arruda</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Rua José de Barros Bezerra</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Arruda</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2000.0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2000.0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Rua Otaviano Pessoa</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>25.71</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-60m2-aluguel-RS2000-id-2908173232/?source=ranking%2Crp</t>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 87 m² · Espinheiro</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Espinheiro</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2200.0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2200.0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Rua Joana Noberto Pessoa</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>182.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1982.0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>25.29</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>23.32</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-e-venda-com-87-metros-quadrados-com-3-quartos-em-espinheiro-recife-1530348025</t>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -929,7 +906,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -937,7 +914,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -947,12 +924,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -967,7 +944,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -977,12 +954,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -997,22 +974,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-otimo-apartamento-com-2-quartos-no-bairro-da-encruzilhada-recife-1530342968</t>
         </is>
       </c>
     </row>
@@ -1020,30 +997,30 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 60 m² · Arruda</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua José de Barros Bezerra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1058,7 +1035,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1068,17 +1045,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1088,22 +1065,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-60m2-aluguel-RS2000-id-2908173232/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1088,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1119,47 +1096,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>105.95</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2055.95</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1169,7 +1146,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1179,22 +1156,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1179,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1210,7 +1187,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
+          <t>Apartamento · 3 quartos · 87 m² · Espinheiro</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1220,37 +1197,37 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>105.95</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2055.95</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>25.29</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1270,22 +1247,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-e-venda-com-87-metros-quadrados-com-3-quartos-em-espinheiro-recife-1530348025</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1343,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1457,7 +1434,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1548,7 +1525,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1639,7 +1616,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1730,7 +1707,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1821,7 +1798,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,12 +29,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -539,93 +546,97 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Camila Melo Imóveis</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real, Zap Imóveis</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Estrada de Belém</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Encruzilhada</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1800.0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>1800.0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>24.32</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>25.71</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-encruzilhada-recife-com-garagem-70m2-aluguel-RS1800-id-2826948890/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -716,7 +727,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -724,7 +735,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -732,17 +743,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -772,17 +783,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -792,22 +803,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -815,20 +826,20 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -848,12 +859,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1982.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -863,7 +874,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -873,7 +884,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -883,22 +894,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -906,30 +917,30 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -939,12 +950,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1982.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -954,17 +965,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -974,22 +985,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-otimo-apartamento-com-2-quartos-no-bairro-da-encruzilhada-recife-1530342968</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1179,30 +1190,30 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 87 m² · Espinheiro</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1217,7 +1228,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1227,7 +1238,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>25.29</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1237,7 +1248,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1247,22 +1258,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-e-venda-com-87-metros-quadrados-com-3-quartos-em-espinheiro-recife-1530348025</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1289,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1293,7 +1304,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1308,7 +1319,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1318,7 +1329,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1328,7 +1339,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1338,22 +1349,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>37</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1361,15 +1372,15 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1384,7 +1395,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1399,7 +1410,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1409,7 +1420,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1419,7 +1430,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1429,22 +1440,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1452,25 +1463,25 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1500,7 +1511,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1510,7 +1521,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1520,22 +1531,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1543,25 +1554,25 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1591,7 +1602,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1601,32 +1612,32 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1642,17 +1653,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1682,7 +1693,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1692,121 +1703,30 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Rua Maria Ramos</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>23.36</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,18 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -546,97 +539,93 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Viva Real, Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Estrada de Belém</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Encruzilhada</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Camila Melo Imóveis</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Apartamento · 74 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>1800.0</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>1800.0</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>25.71</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-encruzilhada-recife-com-garagem-70m2-aluguel-RS1800-id-2826948890/?source=ranking%2Crp</t>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -727,7 +716,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -735,7 +724,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -743,17 +732,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -783,17 +772,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -803,22 +792,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -826,20 +815,20 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -859,12 +848,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1982.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -874,7 +863,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -884,7 +873,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -894,22 +883,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -917,7 +906,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -925,22 +914,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 60 m² · Arruda</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Rua José de Barros Bezerra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -950,12 +939,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1982.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -965,12 +954,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -985,22 +974,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-60m2-aluguel-RS2000-id-2908173232/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1008,65 +997,65 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rua José de Barros Bezerra</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>105.95</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2055.95</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1076,22 +1065,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-60m2-aluguel-RS2000-id-2908173232/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
         </is>
       </c>
     </row>
@@ -1099,55 +1088,55 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>105.95</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2055.95</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1157,7 +1146,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1167,22 +1156,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1187,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1213,7 +1202,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1228,7 +1217,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1238,7 +1227,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1248,7 +1237,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1258,22 +1247,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>37</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1281,15 +1270,15 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1304,7 +1293,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1319,7 +1308,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1329,7 +1318,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1339,7 +1328,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1349,22 +1338,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1372,25 +1361,25 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1420,7 +1409,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1430,7 +1419,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1440,22 +1429,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1463,25 +1452,25 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1511,7 +1500,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1521,32 +1510,32 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1562,17 +1551,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1602,7 +1591,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1612,121 +1601,30 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Rua Maria Ramos</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>23.36</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -615,7 +615,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -906,15 +906,15 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>OLX Imóveis, Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Arruda</t>
+          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Arruda</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -979,17 +979,17 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-60m2-aluguel-RS2000-id-2908173232/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-arruda-1529925280</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1179,20 +1179,20 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>32.78</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1247,22 +1247,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
         </is>
       </c>
     </row>
@@ -1270,15 +1270,15 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>38</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1361,25 +1361,25 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1429,22 +1429,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1452,25 +1452,25 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1510,32 +1510,32 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1551,80 +1551,171 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Rua Alcina Coelho de Carvalho</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Rua Maria Ramos</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Bairro Novo</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>23.36</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>107.0</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -542,7 +542,7 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -550,7 +550,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 100 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -610,22 +610,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-100m-reformado-ventilado-semi-mobiliado-no-centro-da-boa-vista-9-andar-1507545093</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -732,17 +732,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -792,22 +792,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -815,20 +815,20 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1982.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -883,22 +883,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -906,30 +906,30 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OLX Imóveis, Viva Real, Zap Imóveis</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Arruda</t>
+          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua José de Barros Bezerra</t>
+          <t>Estrada de Belém</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-arruda-1529925280</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-encruzilhada-recife-com-garagem-70m2-aluguel-RS1800-id-2826948890/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -997,55 +997,55 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>105.95</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2055.95</t>
+          <t>1982.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1088,30 +1088,30 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis, Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Arruda</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua José de Barros Bezerra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1136,42 +1136,42 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-arruda-1529925280</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1197,37 +1197,37 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>105.95</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2055.95</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>32.78</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1247,22 +1247,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1361,20 +1361,20 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>32.78</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1429,22 +1429,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
         </is>
       </c>
     </row>
@@ -1452,30 +1452,30 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1520,22 +1520,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>38</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1543,20 +1543,20 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1606,27 +1606,27 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1634,88 +1634,270 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
+          <t>Portal CRECI Brasil</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Santo Amaro</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>20.83</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C15" t="n">
         <v>2</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Rua Alcina Coelho de Carvalho</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Rua Maria Ramos</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Bairro Novo</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>23.36</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>107.0</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,12 +29,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -539,93 +546,97 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>OLX Imóveis</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Apartamento · 100 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1600.0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1600.0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Encruzilhada</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-100m-reformado-ventilado-semi-mobiliado-no-centro-da-boa-vista-9-andar-1507545093</t>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>28.57</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-com-2-quartos-para-alugar-na-encruzilhada-recife-pe-1531066849</t>
         </is>
       </c>
     </row>
@@ -633,7 +644,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -641,7 +652,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -651,12 +662,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1400.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,12 +677,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1450.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -681,12 +692,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -701,22 +712,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
         </is>
       </c>
     </row>
@@ -797,7 +808,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -807,7 +818,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -815,7 +826,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -823,17 +834,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -863,17 +874,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -883,22 +894,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -906,7 +917,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -914,17 +925,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Estrada de Belém</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -959,17 +970,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -979,17 +990,17 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-encruzilhada-recife-com-garagem-70m2-aluguel-RS1800-id-2826948890/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -997,7 +1008,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1005,17 +1016,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Estrada de Belém</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1030,12 +1041,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1982.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1045,12 +1056,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1060,27 +1071,27 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-encruzilhada-recife-com-garagem-70m2-aluguel-RS1800-id-2826948890/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1088,30 +1099,30 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OLX Imóveis, Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Arruda</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua José de Barros Bezerra</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1121,12 +1132,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1982.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1136,12 +1147,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1156,22 +1167,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-arruda-1529925280</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1179,65 +1190,65 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>OLX Imóveis, Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
+          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Arruda</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua José de Barros Bezerra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>105.95</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2055.95</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1247,22 +1258,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-arruda-1529925280</t>
         </is>
       </c>
     </row>
@@ -1270,55 +1281,55 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>105.95</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2055.95</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1328,7 +1339,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1338,22 +1349,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
         </is>
       </c>
     </row>
@@ -1361,20 +1372,20 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1384,7 +1395,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1399,7 +1410,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1409,7 +1420,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>32.78</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1419,7 +1430,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1434,17 +1445,17 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1452,20 +1463,20 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1475,7 +1486,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1490,7 +1501,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1500,7 +1511,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>32.78</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1510,7 +1521,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1520,22 +1531,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
         </is>
       </c>
     </row>
@@ -1543,15 +1554,15 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1566,7 +1577,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1581,7 +1592,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1591,7 +1602,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1601,7 +1612,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1611,22 +1622,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>39</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1634,25 +1645,25 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1682,7 +1693,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1692,7 +1703,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1702,22 +1713,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1725,25 +1736,25 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1773,7 +1784,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1783,32 +1794,32 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1824,80 +1835,171 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Rua Alcina Coelho de Carvalho</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Rua Maria Ramos</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Bairro Novo</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>23.36</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>107.0</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,18 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -546,97 +539,93 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Âncora Imobiliária</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Encruzilhada</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2000.0</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>2000.0</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Arruda</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1450.0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>28.57</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-com-2-quartos-para-alugar-na-encruzilhada-recife-pe-1531066849</t>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>19.33</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
         </is>
       </c>
     </row>
@@ -644,7 +633,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -652,7 +641,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -662,12 +651,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -677,12 +666,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -692,12 +681,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,22 +701,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -808,7 +797,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -818,7 +807,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -826,7 +815,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -834,17 +823,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -874,17 +863,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -894,22 +883,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -917,25 +906,25 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Estrada de Belém</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -970,37 +959,37 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-encruzilhada-recife-com-garagem-70m2-aluguel-RS1800-id-2826948890/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1008,7 +997,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1016,17 +1005,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Estrada de Belém</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1041,12 +1030,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1982.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1056,12 +1045,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1071,27 +1060,27 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-encruzilhada-recife-com-garagem-70m2-aluguel-RS1800-id-2826948890/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1099,55 +1088,55 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>105.95</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1982.0</t>
+          <t>2055.95</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1157,7 +1146,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1167,22 +1156,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
         </is>
       </c>
     </row>
@@ -1190,30 +1179,30 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OLX Imóveis, Viva Real, Zap Imóveis</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Arruda</t>
+          <t>Apartamento · 3 quartos · 87 m² · Espinheiro</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua José de Barros Bezerra</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1228,7 +1217,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1238,17 +1227,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>25.29</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1258,7 +1247,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1268,12 +1257,12 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-arruda-1529925280</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-e-venda-com-87-metros-quadrados-com-3-quartos-em-espinheiro-recife-1530348025</t>
         </is>
       </c>
     </row>
@@ -1281,55 +1270,55 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>105.95</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2055.95</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1339,7 +1328,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1349,22 +1338,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>29</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1372,30 +1361,30 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 90 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua do Riachuelo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2317.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1410,7 +1399,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2317.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1420,42 +1409,42 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>25.74</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-vista-recife-90m2-aluguel-RS2317-id-2904925102/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1463,20 +1452,20 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1486,7 +1475,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1501,7 +1490,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1511,7 +1500,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>32.78</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1521,7 +1510,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1531,22 +1520,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>40</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1554,15 +1543,15 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1577,7 +1566,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1592,7 +1581,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1602,7 +1591,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1612,7 +1601,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1622,22 +1611,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1645,25 +1634,25 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1693,7 +1682,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1703,7 +1692,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1713,22 +1702,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1736,25 +1725,25 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1784,7 +1773,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1794,32 +1783,32 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1835,17 +1824,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1875,7 +1864,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1885,121 +1874,30 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>29</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Rua Maria Ramos</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>23.36</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,12 +29,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -539,275 +546,287 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Âncora Imobiliária</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>OLX Imóveis</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Arruda</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1450.0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 82 m² · Tamarineira</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Tamarineira</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>1577.0</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>19.33</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>19.23</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-tem-82-metros-quadrados-com-3-quartos-em-tamarineira-recife-pe-1531424449</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Camila Melo Imóveis</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>OLX Imóveis</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 96 m² · Torre</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Torre</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>24.32</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>20.83</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-excelente-apartamento-no-bairro-da-torre-proximo-a-beira-rio-3-quartos-1531394184</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Camila Melo Imóveis</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Rua João Clementino Montarroyos</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2300.0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2300.0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>24.32</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>31.94</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -815,7 +834,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -823,22 +842,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1400.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -848,12 +867,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1450.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -863,7 +882,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>19.33</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -873,7 +892,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -883,7 +902,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -898,7 +917,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
         </is>
       </c>
     </row>
@@ -906,25 +925,25 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Estrada de Belém</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -954,42 +973,42 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-encruzilhada-recife-com-garagem-70m2-aluguel-RS1800-id-2826948890/?source=ranking%2Crp</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -997,25 +1016,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1030,12 +1049,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1982.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1045,17 +1064,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1065,22 +1084,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1107,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1096,47 +1115,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>105.95</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2055.95</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1146,7 +1165,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1156,22 +1175,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -1179,30 +1198,30 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 87 m² · Espinheiro</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1212,12 +1231,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>1982.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1227,7 +1246,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>25.29</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1237,7 +1256,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1247,22 +1266,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-e-venda-com-87-metros-quadrados-com-3-quartos-em-espinheiro-recife-1530348025</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1270,30 +1289,30 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Arruda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1308,7 +1327,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1318,17 +1337,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1338,22 +1357,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-arruda-1529925280</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1380,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1369,82 +1388,82 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 90 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rua do Riachuelo</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2317.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>105.95</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2317.0</t>
+          <t>2055.95</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>25.74</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-vista-recife-90m2-aluguel-RS2317-id-2904925102/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
         </is>
       </c>
     </row>
@@ -1452,20 +1471,20 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1475,7 +1494,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1490,7 +1509,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1500,7 +1519,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>32.78</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1510,7 +1529,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1520,22 +1539,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
         </is>
       </c>
     </row>
@@ -1543,15 +1562,15 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1566,7 +1585,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1581,7 +1600,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1591,7 +1610,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1601,7 +1620,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1611,22 +1630,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>40</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1634,25 +1653,25 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1682,7 +1701,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1692,7 +1711,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1702,22 +1721,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1725,25 +1744,25 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1773,7 +1792,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1783,32 +1802,32 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1824,80 +1843,171 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Rua Alcina Coelho de Carvalho</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Rua Maria Ramos</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Bairro Novo</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>23.36</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>107.0</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -553,30 +553,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>OLX Imóveis, Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 82 m² · Tamarineira</t>
+          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida João de Barros</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Tamarineira</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1500.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>1577.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,17 +601,17 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -621,22 +621,22 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-tem-82-metros-quadrados-com-3-quartos-em-tamarineira-recife-pe-1531424449</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-com-2-quartos-para-alugar-na-encruzilhada-recife-pe-1531066849</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 96 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 65 m² · Torre</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-excelente-apartamento-no-bairro-da-torre-proximo-a-beira-rio-3-quartos-1531394184</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-alugar-2-quartos-com-65m-na-torre-1531489445</t>
         </is>
       </c>
     </row>
@@ -743,30 +743,30 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 68 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -811,22 +811,22 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/excelente-apto-torre-recife-pe-1531486408</t>
         </is>
       </c>
     </row>
@@ -1289,20 +1289,20 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Arruda</t>
+          <t>Apartamento · 2 quartos · 60 m² · Arruda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua José de Barros Bezerra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1362,17 +1362,17 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-arruda-1529925280</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-60m2-aluguel-RS2000-id-2908173232/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1471,20 +1471,20 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>32.78</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1544,17 +1544,17 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -553,11 +553,11 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>OLX Imóveis, Viva Real, Zap Imóveis</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -626,207 +626,199 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-com-2-quartos-para-alugar-na-encruzilhada-recife-pe-1531066849</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-encruzilhada-recife-com-garagem-70m2-aluguel-RS2000-id-2909004819/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Camila Melo Imóveis</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 65 m² · Torre</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Apartamento · 74 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>38.46</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-alugar-2-quartos-com-65m-na-torre-1531489445</t>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Camila Melo Imóveis</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 68 m² · 1 vaga · Torre</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Apartamento · 74 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>36.76</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/excelente-apto-torre-recife-pe-1531486408</t>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -834,7 +826,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -842,22 +834,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -867,12 +859,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -882,7 +874,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -892,7 +884,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -902,12 +894,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -917,7 +909,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -925,7 +917,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -933,17 +925,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Estrada de Belém</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -973,42 +965,42 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-encruzilhada-recife-com-garagem-70m2-aluguel-RS1800-id-2826948890/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1016,25 +1008,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1049,12 +1041,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1982.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1064,17 +1056,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1084,22 +1076,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1099,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1115,22 +1107,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Arruda</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1145,7 +1137,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1155,17 +1147,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1175,22 +1167,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-arruda-1529925280</t>
         </is>
       </c>
     </row>
@@ -1198,30 +1190,30 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1231,12 +1223,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1982.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1246,7 +1238,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1256,7 +1248,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1266,12 +1258,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1281,7 +1273,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1289,25 +1281,25 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Arruda</t>
+          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rua José de Barros Bezerra</t>
+          <t>Avenida João de Barros</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1337,7 +1329,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1347,32 +1339,32 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-60m2-aluguel-RS2000-id-2908173232/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-encruzilhada-recife-com-garagem-70m2-aluguel-RS2000-id-2908460832/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1445,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1544,7 +1536,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1562,20 +1554,20 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1585,7 +1577,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1600,7 +1592,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1610,7 +1602,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>32.78</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1620,7 +1612,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1630,22 +1622,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
         </is>
       </c>
     </row>
@@ -1653,15 +1645,15 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1676,7 +1668,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1691,7 +1683,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1701,7 +1693,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1711,7 +1703,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1721,22 +1713,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1744,25 +1736,25 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1792,7 +1784,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1802,7 +1794,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1812,22 +1804,22 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1900,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1999,7 +1991,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -553,11 +553,11 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -566,7 +566,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Avenida João de Barros</t>
+          <t>Estrada de Belém</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -626,17 +626,17 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-encruzilhada-recife-com-garagem-70m2-aluguel-RS2000-id-2909004819/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-encruzilhada-recife-com-garagem-70m2-aluguel-RS1800-id-2826948890/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -917,25 +917,25 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Estrada de Belém</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -950,12 +950,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1982.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -980,27 +980,27 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-encruzilhada-recife-com-garagem-70m2-aluguel-RS1800-id-2826948890/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1008,30 +1008,30 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1982.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1099,20 +1099,20 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Arruda</t>
+          <t>Apartamento · 2 quartos · 60 m² · Arruda</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua José de Barros Bezerra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1172,17 +1172,17 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-arruda-1529925280</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-60m2-aluguel-RS2000-id-2908173232/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1208,37 +1208,37 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>105.95</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2055.95</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
         </is>
       </c>
     </row>
@@ -1281,30 +1281,30 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Avenida João de Barros</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1349,22 +1349,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-encruzilhada-recife-com-garagem-70m2-aluguel-RS2000-id-2908460832/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1372,55 +1372,55 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>105.95</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2055.95</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1440,22 +1440,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1463,15 +1463,15 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1531,22 +1531,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1554,20 +1554,20 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>32.78</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1612,32 +1612,32 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1653,22 +1653,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1713,293 +1713,20 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Rua João Clementino Montarroyos</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>32.47</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Rua Maria Ramos</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>23.36</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -553,30 +553,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
+          <t>Apartamento · 2 quartos · 60 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Estrada de Belém</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>850.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>850.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -611,123 +611,127 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-encruzilhada-recife-com-garagem-70m2-aluguel-RS1800-id-2826948890/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-02-quartos-no-boa-vista-2-1525672775</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Camila Melo Imóveis</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real, Zap Imóveis</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 65 m² · Torre</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Rua Professora Ângela Pinto</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Torre</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>24.32</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>38.46</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torre-recife-com-garagem-65m2-aluguel-RS2500-id-2909254326/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -808,7 +812,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -818,7 +822,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -826,7 +830,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -834,17 +838,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -874,17 +878,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -894,22 +898,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -917,20 +921,20 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -950,12 +954,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1982.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -965,7 +969,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -975,7 +979,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -985,7 +989,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -995,12 +999,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -1008,30 +1012,30 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1041,12 +1045,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1982.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1056,7 +1060,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1066,7 +1070,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1076,12 +1080,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1091,7 +1095,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1099,15 +1103,15 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>OLX Imóveis, Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Arruda</t>
+          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Arruda</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1172,17 +1176,17 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-60m2-aluguel-RS2000-id-2908173232/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-arruda-1529925280</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1194,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1198,7 +1202,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1208,37 +1212,37 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>105.95</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2055.95</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1258,22 +1262,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1281,55 +1285,55 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>105.95</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2055.95</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1339,7 +1343,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1349,22 +1353,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1384,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1395,7 +1399,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1410,7 +1414,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1420,7 +1424,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1430,7 +1434,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1440,22 +1444,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1463,30 +1467,30 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Zap Imóveis</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 90 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua do Riachuelo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2317.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1501,7 +1505,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2317.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1511,42 +1515,42 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>25.74</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-cozinha-boa-vista-recife-90m2-id-2904925102/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1554,20 +1558,20 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1577,7 +1581,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1592,7 +1596,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2360.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1602,7 +1606,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>32.78</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1612,32 +1616,32 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
         </is>
       </c>
     </row>
@@ -1653,82 +1657,355 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Rua João Clementino Montarroyos</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2400.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2400.0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Rua João Clementino Montarroyos</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>32.47</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Rua Maria Ramos</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Bairro Novo</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>23.36</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>107.0</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Rua Alcina Coelho de Carvalho</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,18 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -546,192 +539,184 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Camila Melo Imóveis</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 60 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Apartamento · 74 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Boa Vista</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>850.0</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>850.0</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>14.17</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-02-quartos-no-boa-vista-2-1525672775</t>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Viva Real, Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 65 m² · Torre</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Rua Professora Ângela Pinto</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Camila Melo Imóveis</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Apartamento · 74 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>38.46</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torre-recife-com-garagem-65m2-aluguel-RS2500-id-2909254326/?source=ranking%2Crp</t>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -739,7 +724,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -747,17 +732,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -787,17 +772,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -807,22 +792,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -830,25 +815,25 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -863,12 +848,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1982.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -878,17 +863,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -898,22 +883,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -921,7 +906,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -929,22 +914,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -959,7 +944,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -969,7 +954,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -979,7 +964,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -989,22 +974,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1012,7 +997,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1020,22 +1005,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 60 m² · Arruda</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Rua José de Barros Bezerra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1045,12 +1030,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1982.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1060,12 +1045,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1080,22 +1065,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-60m2-aluguel-RS2000-id-2908173232/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1103,65 +1088,65 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OLX Imóveis, Viva Real, Zap Imóveis</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Arruda</t>
+          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua José de Barros Bezerra</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>105.95</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2055.95</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1171,22 +1156,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-arruda-1529925280</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
         </is>
       </c>
     </row>
@@ -1194,30 +1179,30 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1232,7 +1217,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1242,7 +1227,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1252,7 +1237,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1262,22 +1247,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1285,55 +1270,55 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>105.95</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2055.95</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1343,7 +1328,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1353,22 +1338,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1376,15 +1361,15 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1399,7 +1384,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1414,7 +1399,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1424,7 +1409,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1444,22 +1429,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1467,30 +1452,30 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 90 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 65 m² · Torre</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua do Riachuelo</t>
+          <t>Rua Professora Ângela Pinto</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2317.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1505,7 +1490,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2317.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1515,7 +1500,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>25.74</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1525,32 +1510,32 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-cozinha-boa-vista-recife-90m2-id-2904925102/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torre-recife-com-garagem-65m2-aluguel-RS2500-id-2909254326/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1558,20 +1543,20 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1581,7 +1566,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1596,7 +1581,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1606,7 +1591,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>32.78</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1616,32 +1601,32 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1657,22 +1642,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1687,7 +1672,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1697,7 +1682,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1707,7 +1692,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1717,295 +1702,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Rua João Clementino Montarroyos</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>32.47</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Rua Maria Ramos</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>23.36</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -615,7 +615,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1088,55 +1088,55 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>105.95</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2055.95</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1156,22 +1156,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>32</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1247,22 +1247,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>43</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1270,15 +1270,15 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1361,25 +1361,25 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 65 m² · Torre</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Professora Ângela Pinto</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1409,42 +1409,42 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torre-recife-com-garagem-65m2-aluguel-RS2500-id-2909254326/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 65 m² · Torre</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua Professora Ângela Pinto</t>
+          <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1500,42 +1500,42 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torre-recife-com-garagem-65m2-aluguel-RS2500-id-2909254326/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1551,17 +1551,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1601,121 +1601,30 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>32</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Rua Maria Ramos</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>23.36</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,12 +29,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -539,93 +546,97 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Camila Melo Imóveis</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>OLX Imóveis</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>24.32</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 70 m² · Torre</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Torre</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2387.0</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>34.1</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-aluguel-3-quartos-1-vaga-torre-recife-pe-1532343979</t>
         </is>
       </c>
     </row>
@@ -716,7 +727,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -724,7 +735,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -732,17 +743,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -772,17 +783,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -792,22 +803,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -815,20 +826,20 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -848,12 +859,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1982.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -863,7 +874,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -873,7 +884,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -883,22 +894,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -906,30 +917,30 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -939,12 +950,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1982.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -954,7 +965,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -964,7 +975,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -974,7 +985,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -989,7 +1000,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -997,25 +1008,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rua José de Barros Bezerra</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1045,17 +1056,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1065,22 +1076,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-60m2-aluguel-RS2000-id-2908173232/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1460,17 +1471,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1500,7 +1511,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1510,32 +1521,32 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>32</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1551,17 +1562,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1591,7 +1602,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1601,32 +1612,32 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -586,12 +586,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1982.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -656,7 +656,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Derby</t>
+          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -666,47 +666,47 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>105.95</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2055.95</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/9119/apartamento-3-quartos-derby-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
         </is>
       </c>
     </row>
@@ -743,30 +743,30 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 90 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua do Riachuelo</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2317.0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2317.0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -791,224 +791,232 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>25.74</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-vista-recife-90m2-aluguel-RS2317-id-2904925102/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Âncora Imobiliária</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>OLX Imóveis</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 75 m² · Arruda</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Arruda</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>1450.0</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 78 m² · 1 vaga · Casa Amarela</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Casa Amarela</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2350.0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2350.0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>19.33</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>30.13</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/432/casa-3-quartos-arruda-recife/</t>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-casa-amarela-1532718092</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Camila Melo Imóveis</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Viva Real, Zap Imóveis</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 65 m² · Torre</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Rua Professora Ângela Pinto</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Torre</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>24.32</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>38.46</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torre-recife-com-garagem-65m2-aluguel-RS2500-id-2909254326/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1097,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1099,7 +1107,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1115,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1115,17 +1123,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1155,17 +1163,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1175,22 +1183,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -1198,30 +1206,30 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1236,7 +1244,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1246,7 +1254,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1256,7 +1264,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1266,22 +1274,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -1289,30 +1297,30 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1327,7 +1335,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1337,7 +1345,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1347,7 +1355,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1357,22 +1365,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1380,30 +1388,30 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1418,7 +1426,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1428,7 +1436,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1438,7 +1446,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1448,22 +1456,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1479,7 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1479,22 +1487,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua Zeferino Agra</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1509,7 +1517,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1519,19 +1527,19 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="O12" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -1544,7 +1552,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>44</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1554,7 +1562,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-80m2-aluguel-RS2500-id-2882143782/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1562,25 +1570,25 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1610,7 +1618,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1620,7 +1628,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1630,22 +1638,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1661,80 +1669,171 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Rua Maria Ramos</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>23.36</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Casa Caiada</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>31.25</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis, OLX Imóveis Olinda</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -561,22 +561,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Arruda</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>1982.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,17 +601,17 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -621,22 +621,22 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-arruda-1529925280</t>
         </is>
       </c>
     </row>
@@ -648,15 +648,15 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>OLX Imóveis, OLX Imóveis Olinda</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
+          <t>Apartamento · 3 quartos · 96 m² · Torre</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -696,17 +696,17 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-excelente-apartamento-no-bairro-da-torre-proximo-a-beira-rio-3-quartos-1531394184</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>OLX Imóveis, OLX Imóveis Olinda</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -751,22 +751,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 90 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 87 m² · Espinheiro</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Rua do Riachuelo</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2317.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2317.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -791,27 +791,27 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25.74</t>
+          <t>25.29</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-vista-recife-90m2-aluguel-RS2317-id-2904925102/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-e-venda-com-87-metros-quadrados-com-3-quartos-em-espinheiro-recife-1530348025</t>
         </is>
       </c>
     </row>
@@ -838,15 +838,15 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>OLX Imóveis, OLX Imóveis Olinda</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 78 m² · 1 vaga · Casa Amarela</t>
+          <t>Apartamento · 3 quartos · 70 m² · Torre</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -856,37 +856,37 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2350.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2350.0</t>
+          <t>2387.0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,102 +921,98 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-casa-amarela-1532718092</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-aluguel-3-quartos-1-vaga-torre-recife-pe-1532343979</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Viva Real, Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 65 m² · Torre</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Rua Professora Ângela Pinto</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Camila Melo Imóveis</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Apartamento · 74 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>38.46</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torre-recife-com-garagem-65m2-aluguel-RS2500-id-2909254326/?source=ranking%2Crp</t>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1103,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1111,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1123,17 +1119,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1163,17 +1159,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1183,22 +1179,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -1206,20 +1202,20 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1239,12 +1235,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1982.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1254,7 +1250,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1264,7 +1260,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1274,22 +1270,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1293,7 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1305,7 +1301,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1315,7 +1311,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1345,17 +1341,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1365,22 +1361,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
         </is>
       </c>
     </row>
@@ -1388,30 +1384,30 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1426,7 +1422,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1436,7 +1432,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1446,7 +1442,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1456,22 +1452,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1483,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1502,7 +1498,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1517,7 +1513,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1527,7 +1523,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1537,7 +1533,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1547,22 +1543,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>33</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1570,30 +1566,30 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 90 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua do Riachuelo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2317.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1608,7 +1604,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2317.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1618,42 +1614,42 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>25.74</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-vista-recife-90m2-aluguel-RS2317-id-2904925102/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1657,7 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis, OLX Imóveis Olinda</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1669,22 +1665,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 78 m² · 1 vaga · Casa Amarela</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2350.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1699,7 +1695,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2350.0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1709,7 +1705,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1719,7 +1715,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1729,22 +1725,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-casa-amarela-1532718092</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1748,7 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis, OLX Imóveis Olinda</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1760,80 +1756,535 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2360.0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2360.0</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>32.78</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Rua João Clementino Montarroyos</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2400.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2400.0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Rua João Clementino Montarroyos</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>32.47</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Viva Real, Zap Imóveis</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 65 m² · Torre</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Rua Professora Ângela Pinto</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Torre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>38.46</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torre-recife-com-garagem-65m2-aluguel-RS2500-id-2909254326/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Rua Maria Ramos</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>23.36</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Casa Caiada</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>31.25</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>OLX Imóveis, OLX Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -561,12 +561,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Arruda</t>
+          <t>Apartamento · 2 quartos · 60 m² · Arruda</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua José de Barros Bezerra</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-arruda-1529925280</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-arruda-recife-com-garagem-60m2-aluguel-RS2000-id-2908173232/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -648,30 +648,30 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>OLX Imóveis, OLX Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 96 m² · Torre</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -716,212 +716,204 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-excelente-apartamento-no-bairro-da-torre-proximo-a-beira-rio-3-quartos-1531394184</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis, OLX Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 87 m² · Espinheiro</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Espinheiro</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2200.0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2200.0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Camila Melo Imóveis</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Apartamento · 74 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>25.29</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-e-venda-com-87-metros-quadrados-com-3-quartos-em-espinheiro-recife-1530348025</t>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis, OLX Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 70 m² · Torre</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2000.0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2387.0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>34.1</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-aluguel-3-quartos-1-vaga-torre-recife-pe-1532343979</t>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Camila Melo Imóveis</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Apartamento · 74 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>24.32</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -929,7 +921,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -937,17 +929,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -977,17 +969,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,22 +989,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -1020,25 +1012,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Joana Noberto Pessoa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1053,12 +1045,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1982.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1068,17 +1060,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1088,22 +1080,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1103,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1119,22 +1111,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1149,7 +1141,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1159,7 +1151,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1169,7 +1161,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1179,22 +1171,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1800/id-45733416/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -1210,22 +1202,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua Joana Noberto Pessoa</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1235,12 +1227,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1982.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1250,7 +1242,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1270,22 +1262,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>33</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-85m2-aluguel-RS1800-id-2906183668/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1293,30 +1285,30 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1331,7 +1323,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1341,19 +1333,19 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -1361,22 +1353,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1384,30 +1376,30 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 2 quartos · 65 m² · Torre</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Professora Ângela Pinto</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1422,7 +1414,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1432,17 +1424,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1452,22 +1444,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torre-recife-com-garagem-65m2-aluguel-RS2500-id-2909254326/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1475,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1498,7 +1490,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1513,7 +1505,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1523,7 +1515,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1538,27 +1530,27 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-72m2-aluguel-RS2300-id-2866390830/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1558,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1574,22 +1566,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 90 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua do Riachuelo</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2317.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1604,7 +1596,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2317.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1614,679 +1606,42 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>25.74</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-boa-vista-recife-90m2-aluguel-RS2317-id-2904925102/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>OLX Imóveis, OLX Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 78 m² · 1 vaga · Casa Amarela</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Casa Amarela</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2350.0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2350.0</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>30.13</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-casa-amarela-1532718092</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>OLX Imóveis, OLX Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2360.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2360.0</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>32.78</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Rua João Clementino Montarroyos</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2400.0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2400.0</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2400-id-2897542450/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Rua João Clementino Montarroyos</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>32.47</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Viva Real, Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 65 m² · Torre</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Rua Professora Ângela Pinto</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>38.46</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torre-recife-com-garagem-65m2-aluguel-RS2500-id-2909254326/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Rua Maria Ramos</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>23.36</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
           <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Rua Alcina Coelho de Carvalho</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS2500-id-2904821162/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S109"/>
+  <dimension ref="A1:S115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -561,7 +561,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Tamarineira</t>
+          <t>Apartamento · 1 quarto · 33 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Tamarineira</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>1750.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>1750.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>77.14</t>
+          <t>53.03</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-possui-35-metros-quadrados-com-1-quarto-em-tamarineira-recife-pe-1533482760</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/123-rua-carlos-borromeu-de-frente-para-o-mercado-da-encruzilhada/850471068-78</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · 1 vaga · Ilha do Leite</t>
+          <t>Apartamento · 3 quartos · 75 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Ilha do Leite</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2900.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2900.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>37.33</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/estudio-ilha-do-leite-no-recife-mobilado-e-equipado-por-2900-reais-mensais-1533493470</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-otimo-apartamento-com-3-quartos-no-bairro-de-casa-amarela-recife-1533578933</t>
         </is>
       </c>
     </row>
@@ -743,30 +743,30 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 34 m² · Graças</t>
+          <t>Apartamento · 1 quarto · 32 m² · Casa Forte</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Rua Dona Anunciada</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Casa Forte</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>94.12</t>
+          <t>100.12</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-gracas-recife-com-garagem-34m2-aluguel-RS3200-id-2795484813/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-1-quarto-em-casa-forte-recife-pe-1533544358</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 96 m² · Encruzilhada</t>
+          <t>Apartamento · 1 quarto · 46 m² · Graças</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -856,12 +856,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3299.0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3299.0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34.38</t>
+          <t>71.72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-apartamento-com-02-quartos-02-vagas-na-encruzilhada-recife-1533489136</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-possui-46-metros-quadrados-com-1-quarto-em-gracas-recife-pe-1533619487</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Espinheiro</t>
+          <t>Apartamento · 1 quarto · 41 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>80.49</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-apto-em-andar-alto-e-com-moveis-planejados-no-edf-saint-jaimes-espinheiro-recife-1533498731</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-1-quarto-em-boa-vista-recife-pe-1533558543</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -1036,22 +1036,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · Parnamirim</t>
+          <t>Apartamento · 1 quarto · 32 m² · Torre</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Avenida Parnamirim</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>112.12</t>
+          <t>109.38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-1-quarto-mobiliado-parnamirim-recife-pe-33m2-id-2896269848/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-1-quarto-na-torre-recife-pe-1533552220</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · Parnamirim</t>
+          <t>Apartamento · 2 quartos · 62 m² · Torre</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>115.15</t>
+          <t>61.29</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-possui-33-metros-quadrados-com-1-quarto-em-parnamirim-recife-pe-1533481808</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-2-quartos-na-torre-recife-pe-1533546992</t>
         </is>
       </c>
     </row>
@@ -1218,565 +1218,545 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 62 m² · Hipódromo</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Hipódromo</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4159.0</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>4159.0</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>67.08</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-excelente-apartamneto-3-quartos-na-estrada-de-belem-1533514055</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 53 m² · Torre</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Rua Horácio Cahu</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>3900.0</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>3900.0</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 57 m² · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Rua Pintor Manoel Bandeira</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>900.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>900.0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>73.58</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>15.79</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-olinda-com-garagem-57m2-aluguel-RS900-id-2652006870/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 58 m² · 1 vaga · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Rua Norberto Pessoa, 238</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1300.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1300.0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>22.41</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torre-recife-com-garagem-53m2-aluguel-RS3900-id-2910115353/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1300/id-46461545/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Apartamento · 1 quarto · 41 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Rua Professor Marculino Botelho, 404</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>34.15</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-olinda-bairro-novo-41m2-RS1200/id-45673360/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Âncora Imobiliária</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 48 m² · 1 vaga · Espinheiro</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Rua São Salvador</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Espinheiro</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3350.0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>650.0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4000.0</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 50 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1100.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>250.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>97.38</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1447.38</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>83.33</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>28.95</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>https://ancoraimobiliaria.com.br/imovel/224/apartamento-2-quartos-jose-mariano-boa-vista-recife/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cristina Mirele Imóveis</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 58 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>25.86</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>48.0</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-48m2-RS3350/id-44730471/</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 1 quarto · 33 m² · Rosarinho</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Rosarinho</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4000.0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4000.0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>121.21</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-tem-33-metros-quadrados-com-1-quarto-em-rosarinho-recife-pe-1533508699</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Aflitos</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Avenida Conselheiro Rosa E Silva, 801</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Aflitos</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4141.0</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4142.0</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>75.31</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-aflitos-55m2-RS4141/id-45283901/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 223 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5800.0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5800.0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>26.01</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>223.0</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-excelente-apartamento-com-3-quartos-no-bairro-da-boa-vista-recife-1533482876</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 223 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5800.0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5800.0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>26.01</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>223.0</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-excelente-apartamento-com-3-quartos-no-bairro-da-boa-vista-recife-1533481096</t>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>https://www.cristinamireleimoveis.com.br/imovel/4314734/apartamento-locacao-olinda-pe-bairro-novo-edf-estacao-verde</t>
         </is>
       </c>
     </row>
@@ -1784,30 +1764,30 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 57 m² · Arruda</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rua Pintor Manoel Bandeira</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>900.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1822,7 +1802,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>900.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1832,7 +1812,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1842,7 +1822,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1867,7 +1847,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-olinda-com-garagem-57m2-aluguel-RS900-id-2652006870/?source=ranking%2Crp</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850301025-80</t>
         </is>
       </c>
     </row>
@@ -1883,12 +1863,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 58 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rua Norberto Pessoa, 238</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1898,7 +1878,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1913,7 +1893,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1923,7 +1903,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1933,7 +1913,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1943,7 +1923,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1958,7 +1938,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1300/id-46461545/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1700/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -1966,55 +1946,55 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 41 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 30 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rua Professor Marculino Botelho, 404</t>
+          <t>Rua Carlos Nigro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>1799.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>1799.0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>59.97</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2029,27 +2009,27 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-olinda-bairro-novo-41m2-RS1200/id-45673360/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-olinda-com-garagem-30m2-aluguel-RS1799-id-2906429133/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2037,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2065,7 +2045,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Boa Vista</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2080,37 +2060,37 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1100.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>97.38</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1447.38</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2125,22 +2105,22 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/224/apartamento-2-quartos-jose-mariano-boa-vista-recife/</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2128,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cristina Mirele Imóveis</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2156,7 +2136,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 58 m² · Bairro Novo</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2166,12 +2146,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1500.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2186,7 +2166,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1500.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2196,12 +2176,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2216,22 +2196,22 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://www.cristinamireleimoveis.com.br/imovel/4314734/apartamento-locacao-olinda-pe-bairro-novo-edf-estacao-verde</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2219,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2247,57 +2227,57 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · Arruda</t>
+          <t>Apartamento · 30 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Coronel Alberto Lundgren, 604</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2307,7 +2287,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2322,7 +2302,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850301025-80</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2310,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2338,22 +2318,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 38 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2368,7 +2348,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2378,42 +2358,42 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1700/id-45733416/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/flat-quatro-rodas-1526587978</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2401,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2429,7 +2409,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2439,17 +2419,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2459,22 +2439,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2489,22 +2469,22 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -2512,30 +2492,30 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 1 quarto · 35 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Carlos Nigro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2550,7 +2530,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2560,17 +2540,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2580,22 +2560,22 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-casa-caiada-olinda-35m2-aluguel-RS2000-id-2582783099/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2611,57 +2591,57 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Apartamento · 30 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 50 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rua Coronel Alberto Lundgren, 604</t>
+          <t>Rua Gildo Branco, 2</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2671,7 +2651,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2686,7 +2666,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS2200/id-44016902/</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2674,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2702,17 +2682,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Coronel Alberto Lundgren, 604</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2722,27 +2702,27 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2752,7 +2732,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2762,7 +2742,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2777,7 +2757,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/flat-quatro-rodas-1526587978</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2765,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2793,17 +2773,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Espinheiro</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Barão De Itamaracá</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2813,17 +2793,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>307.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2389.0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2833,17 +2813,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>74.66</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2853,22 +2833,22 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-espinheiro-2117m2-RS2000/id-9788603/</t>
         </is>
       </c>
     </row>
@@ -2876,20 +2856,20 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 50 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 31 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rua Gildo Branco, 2</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2899,7 +2879,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2914,7 +2894,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2924,34 +2904,34 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>80.65</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R27" t="inlineStr">
         <is>
           <t>2026-09-05</t>
@@ -2959,7 +2939,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS2200/id-44016902/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-31m2-RS2500/id-45418272/</t>
         </is>
       </c>
     </row>
@@ -2975,59 +2955,59 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rua Coronel Alberto Lundgren, 604</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O28" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -3035,22 +3015,22 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3038,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3066,47 +3046,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Espinheiro</t>
+          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rua Barão De Itamaracá</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>307.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2389.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>74.66</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3116,7 +3096,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3131,17 +3111,17 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-espinheiro-2117m2-RS2000/id-9788603/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/flat-empresarial-jam-1523997215</t>
         </is>
       </c>
     </row>
@@ -3149,90 +3129,90 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 50 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua da Glória</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2425.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>67.36</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/flat-para-alugar-em-bairro-novo-olinda-pe-1525650735</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-olinda-com-garagem-50m2-aluguel-RS2500-id-2904799000/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3220,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -3253,7 +3233,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Presidente Getúlio Vargas, 1748</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3263,22 +3243,22 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>683.0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2425.0</t>
+          <t>2576.0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3288,7 +3268,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>67.36</t>
+          <t>71.56</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3298,7 +3278,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3313,17 +3293,17 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/flat-para-alugar-em-bairro-novo-olinda-pe-1525650750</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-36m2-RS1800/id-45673358/</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3311,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -3344,7 +3324,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3354,22 +3334,22 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>684.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2425.0</t>
+          <t>2577.0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3379,7 +3359,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>67.36</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3389,7 +3369,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3404,17 +3384,17 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/flat-para-alugar-em-bairro-novo-olinda-pe-1525650807</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-720m2-RS1800/id-43805924/</t>
         </is>
       </c>
     </row>
@@ -3422,25 +3402,25 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 31 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · Aflitos</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3450,7 +3430,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3460,27 +3440,27 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2691.0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>80.65</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3490,7 +3470,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3505,7 +3485,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-31m2-RS2500/id-45418272/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-aflitos-recife--pe_33374631</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3493,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3521,22 +3501,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 35 m² · Tamarineira</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Tamarineira</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3551,7 +3531,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3561,17 +3541,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>77.14</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3581,22 +3561,22 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-possui-35-metros-quadrados-com-1-quarto-em-tamarineira-recife-pe-1533482760</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3584,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3612,12 +3592,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa Monteiro, 93</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3627,12 +3607,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>1526.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1178.0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3642,29 +3622,29 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2704.0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>78.12</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -3672,7 +3652,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3687,7 +3667,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/flat-empresarial-jam-1523997215</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1526/id-45586419/</t>
         </is>
       </c>
     </row>
@@ -3695,30 +3675,30 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 90 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rua da Glória</t>
+          <t>Rua Doutor Manoel de Almeida Belo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2750.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3733,7 +3713,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2750.0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3743,27 +3723,27 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3778,7 +3758,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-olinda-com-garagem-50m2-aluguel-RS2500-id-2904799000/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-bairro-novo-1492211765</t>
         </is>
       </c>
     </row>
@@ -3786,30 +3766,30 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3824,7 +3804,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3834,7 +3814,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>69.44</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3844,17 +3824,17 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3869,7 +3849,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-olinda-com-garagem-36m2-aluguel-RS2500-id-2881114874/?source=ranking%2Crp</t>
+          <t>https://www.rogeriocorretor.com/imovel/apartamento-1-quarto-boa-vista-recife-1-vaga-38m2-code-707</t>
         </is>
       </c>
     </row>
@@ -3877,45 +3857,45 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>CTI Imobiliária, Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Avenida Presidente Getúlio Vargas, 1748</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2450.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>683.0</t>
+          <t>365.0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>161.22</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2576.0</t>
+          <t>2895.6099999999997</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3925,17 +3905,17 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>71.56</t>
+          <t>64.35</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3945,7 +3925,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3960,7 +3940,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-36m2-RS1800/id-45673358/</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
         </is>
       </c>
     </row>
@@ -3968,7 +3948,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3976,47 +3956,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 35 m² · 1 vaga · Ilha do Leite</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rua Professor José Cândido Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Ilha do Leite</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2900.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>684.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2577.0</t>
+          <t>2900.0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4026,7 +4006,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4036,22 +4016,22 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-720m2-RS1800/id-43805924/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/estudio-ilha-do-leite-no-recife-mobilado-e-equipado-por-2900-reais-mensais-1533493470</t>
         </is>
       </c>
     </row>
@@ -4059,45 +4039,45 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>CTI Imobiliária, Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Aflitos</t>
+          <t>Apartamento · 2 quartos · 80 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Da Amizade, 223</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>1850.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>953.0</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2691.0</t>
+          <t>2997.0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4107,17 +4087,17 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>37.46</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4127,22 +4107,22 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>47</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-aflitos-recife--pe_33374631</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4138,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro, 93</t>
+          <t>Avenida Doutor José Augusto Moreira, 900</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4173,12 +4153,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1526.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1178.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4188,22 +4168,22 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2704.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4218,7 +4198,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -4233,7 +4213,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1526/id-45586419/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
         </is>
       </c>
     </row>
@@ -4241,30 +4221,30 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OLX Imóveis, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 90 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 92 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rua Doutor Manoel de Almeida Belo</t>
+          <t>Avenida Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2750.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4279,7 +4259,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2750.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4289,7 +4269,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4299,7 +4279,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4309,7 +4289,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4324,7 +4304,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-bairro-novo-1492211765</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS3000/id-42437394/</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4312,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -4340,27 +4320,27 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa Monteiro, 93</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>1822.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1178.0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4370,29 +4350,29 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O43" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -4400,7 +4380,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -4415,7 +4395,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-1-quarto-boa-vista-recife-1-vaga-38m2-code-707</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1822/id-45585830/</t>
         </is>
       </c>
     </row>
@@ -4423,65 +4403,65 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CTI Imobiliária, Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
+          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante, 2595</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2450.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>365.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>161.22</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2895.6099999999997</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>64.35</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4491,7 +4471,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -4506,7 +4486,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-40m2-RS3000/id-45710865/</t>
         </is>
       </c>
     </row>
@@ -4514,55 +4494,55 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CTI Imobiliária, Chaves na Mão Recife</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 2 quartos · 47 m² · 1 vaga · Tamarineira</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rua Da Amizade, 223</t>
+          <t>Rua Goianésia, 106</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Tamarineira</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1850.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>953.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2997.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>37.46</t>
+          <t>63.83</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4582,22 +4562,22 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-tamarineira-47m2-RS3000/id-44941964/</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4585,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4613,17 +4593,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Avenida Doutor José Augusto Moreira, 900</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4653,7 +4633,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4663,7 +4643,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4673,7 +4653,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4688,7 +4668,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-alugar-ou-vender-nas-gracas-recife-pe-1516957301</t>
         </is>
       </c>
     </row>
@@ -4696,7 +4676,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4704,17 +4684,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 92 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 33 m² · Graças</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Avenida Carlos De Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4724,7 +4704,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4739,39 +4719,39 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R47" t="inlineStr">
         <is>
           <t>2026-09-05</t>
@@ -4779,7 +4759,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS3000/id-42437394/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-33m2-gracas-recife--pe_33286759</t>
         </is>
       </c>
     </row>
@@ -4787,35 +4767,35 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 35 m² · Paissandu</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro, 93</t>
+          <t>Rua Estácio Coimbra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Paissandu</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1822.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1178.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4830,17 +4810,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4850,27 +4830,27 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>23</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1822/id-45585830/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-paissandu-recife-com-garagem-35m2-aluguel-RS3000-id-2902097797/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4878,20 +4858,20 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 92 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante, 2595</t>
+          <t>Rua Edmar Moury Fernandes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4926,27 +4906,27 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4961,7 +4941,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-40m2-RS3000/id-45710865/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-92m2-aluguel-RS3000-id-2773332517/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4969,25 +4949,25 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 47 m² · 1 vaga · Tamarineira</t>
+          <t>Apartamento · 3 quartos · 81 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rua Goianésia, 106</t>
+          <t>Rua Professor Francisco Xavier Paes Barreto</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tamarineira</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4997,62 +4977,62 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3002.0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>63.83</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>47.0</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-tamarineira-47m2-RS3000/id-44941964/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-81m2-aluguel-RS3000-id-2908569699/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5040,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Josinildo Imóveis</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -5068,7 +5048,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 2 quartos · 42 m² · Torre</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5078,12 +5058,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5098,7 +5078,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5108,12 +5088,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5128,7 +5108,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -5143,7 +5123,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-alugar-ou-vender-nas-gracas-recife-pe-1516957301</t>
+          <t>https://josinildoimoveis.com.br/imovel/edf-green-life-torre/320</t>
         </is>
       </c>
     </row>
@@ -5151,35 +5131,35 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · Graças</t>
+          <t>Apartamento · 2 quartos · 48 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua da Glória</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>650.0</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5189,7 +5169,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3150.0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5199,19 +5179,19 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>65.62</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O52" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -5219,22 +5199,22 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-33m2-gracas-recife--pe_33286759</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-olinda-com-garagem-48m2-aluguel-RS2500-id-2910114900/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5250,12 +5230,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 92 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rua Edmar Moury Fernandes</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5265,7 +5245,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5280,7 +5260,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5290,34 +5270,34 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R53" t="inlineStr">
         <is>
           <t>2026-09-05</t>
@@ -5325,7 +5305,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-92m2-aluguel-RS3000-id-2773332517/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-olinda-com-garagem-60m2-aluguel-RS3200-id-2686319323/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5333,30 +5313,30 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Josinildo Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 42 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5371,7 +5351,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5381,7 +5361,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5391,17 +5371,17 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -5416,7 +5396,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://josinildoimoveis.com.br/imovel/edf-green-life-torre/320</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-olinda-com-garagem-60m2-aluguel-RS3200-id-2906163316/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5432,27 +5412,27 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 48 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 57 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rua da Glória</t>
+          <t>Rua Pereira Simões</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>650.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5462,17 +5442,17 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>3150.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>65.62</t>
+          <t>56.14</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5482,32 +5462,32 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-olinda-com-garagem-48m2-aluguel-RS2500-id-2910114900/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-olinda-com-garagem-57m2-aluguel-RS3200-id-2901326206/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5515,55 +5495,55 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>237.0</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3202.0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5583,7 +5563,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -5598,7 +5578,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-olinda-com-garagem-60m2-aluguel-RS3200-id-2686319323/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
         </is>
       </c>
     </row>
@@ -5606,30 +5586,30 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Rua Barão De Vera Cruz</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Campo Grande</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5644,7 +5624,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5654,12 +5634,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5669,12 +5649,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -5689,7 +5669,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-olinda-com-garagem-60m2-aluguel-RS3200-id-2906163316/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5677,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -5705,7 +5685,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
+          <t>Apartamento · 2 quartos · 96 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5715,37 +5695,37 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>237.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>3202.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>34.38</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5755,7 +5735,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5765,22 +5745,22 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-apartamento-com-02-quartos-02-vagas-na-encruzilhada-recife-1533489136</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5768,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5796,22 +5776,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
+          <t>Apartamento · 2 quartos · 50 m² · Torre</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rua Barão De Vera Cruz</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Campo Grande</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3400.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5826,7 +5806,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3400.0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5836,34 +5816,34 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R59" t="inlineStr">
         <is>
           <t>2026-09-05</t>
@@ -5871,7 +5851,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
+          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-torre-recife-1-vaga-50m2-code-88</t>
         </is>
       </c>
     </row>
@@ -5879,25 +5859,25 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 95 m² · 1 vaga · Aflitos</t>
+          <t>Apartamento · 2 quartos · 59 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Dois de Julho</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5927,17 +5907,17 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>57.63</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5947,22 +5927,22 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/edf-araras-1532381063</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-santo-amaro-recife-com-garagem-59m2-aluguel-RS3400-id-2910116626/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5950,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -5978,27 +5958,27 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Torre</t>
+          <t>Apartamento · 3 quartos · 84 m² · 2 vagas · Santana</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Sant'anna, 171</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Santana</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1219.0</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6008,27 +5988,27 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>3419.0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6038,22 +6018,22 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-torre-recife-1-vaga-50m2-code-88</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-santana-RS2200/id-46016126/</t>
         </is>
       </c>
     </row>
@@ -6061,35 +6041,35 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · 2 vagas · Santana</t>
+          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rua Sant'anna, 171</t>
+          <t>Rua Pereira Simões</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Santana</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1219.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6099,52 +6079,52 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>3419.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>59.32</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-santana-RS2200/id-46016126/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-45711136/</t>
         </is>
       </c>
     </row>
@@ -6152,20 +6132,20 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões</t>
+          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6200,7 +6180,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>59.32</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6210,7 +6190,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6220,7 +6200,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -6235,7 +6215,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-45711136/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6223,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -6251,17 +6231,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Casa Amarela</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
+          <t>Rua Doutor Genaro Guimarães, 210</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6291,7 +6271,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>59.32</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6311,22 +6291,22 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-59m2-RS3500/id-45862927/</t>
         </is>
       </c>
     </row>
@@ -6342,17 +6322,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Casa Amarela</t>
+          <t>Apartamento · 3 quartos · 87 m² · 2 vagas · Encruzilhada</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rua Doutor Genaro Guimarães, 210</t>
+          <t>Rua Castro Alves, 175</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -6382,19 +6362,19 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>59.32</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O65" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -6402,7 +6382,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -6417,7 +6397,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-59m2-RS3500/id-45862927/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-encruzilhada-RS3500/id-46232694/</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6405,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -6433,17 +6413,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 87 m² · 2 vagas · Encruzilhada</t>
+          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Espinheiro</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rua Castro Alves, 175</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -6473,17 +6453,17 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6493,7 +6473,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -6508,7 +6488,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-encruzilhada-RS3500/id-46232694/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-apto-em-andar-alto-e-com-moveis-planejados-no-edf-saint-jaimes-espinheiro-recife-1533498731</t>
         </is>
       </c>
     </row>
@@ -6971,20 +6951,20 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
+          <t>Apartamento · 1 quarto · 40 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Agamenon Magalhães</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -7019,7 +6999,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>92.18</t>
+          <t>87.58</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7029,7 +7009,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7039,22 +7019,22 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-aluguel-predio-novo-de-luxo-primeiro-dono-1-quarto-mobiliado-com-lazer-co-1532892785</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-boa-vista-recife-com-garagem-40m2-aluguel-RS3500-id-2910206116/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -7062,65 +7042,65 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · Boa Vista</t>
+          <t>Apartamento · 62 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Avenida Governador Agamenon Magalhães</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>3503.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>87.58</t>
+          <t>58.06</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7130,22 +7110,22 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-boa-vista-recife-com-garagem-40m2-aluguel-RS3500-id-2910206116/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/edificio-trindade-family-class-direto-com-a-proprietaria-1532638263</t>
         </is>
       </c>
     </row>
@@ -7517,20 +7497,20 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Newville</t>
+          <t>Newville, Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · Santo Amaro</t>
+          <t>Apartamento · 2 quartos · 56 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Dois de Julho</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -7565,7 +7545,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>64.47</t>
+          <t>66.07</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -7575,17 +7555,17 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>57.39</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -7608,7 +7588,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -7616,7 +7596,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Parnamirim</t>
+          <t>Apartamento · 3 quartos · Encruzilhada</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7626,7 +7606,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -7636,7 +7616,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7651,17 +7631,17 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>105.71</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -7676,22 +7656,22 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-tem-30-metros-quadrados-com-1-quarto-em-parnamirim-recife-pe-1531883717</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-encruzilhada-recife--pe_33362592</t>
         </is>
       </c>
     </row>
@@ -7699,7 +7679,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -7707,7 +7687,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Encruzilhada</t>
+          <t>Apartamento · 3 quartos · 84 m² · Santana</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7717,27 +7697,27 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Santana</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1219.86</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>340.89</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>3760.7499999999995</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7747,7 +7727,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7767,7 +7747,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -7782,7 +7762,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-encruzilhada-recife--pe_33362592</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/6793/apartamento-3-quartos-agave-santana-recife/</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7770,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -7798,7 +7778,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Santana</t>
+          <t>Apartamento · 1 quarto · 33 m² · Parnamirim</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7808,42 +7788,42 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Santana</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1219.86</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>340.89</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>3760.7499999999995</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>115.15</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -7858,22 +7838,22 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/6793/apartamento-3-quartos-agave-santana-recife/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-possui-33-metros-quadrados-com-1-quarto-em-parnamirim-recife-pe-1533481808</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8043,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -8071,57 +8051,57 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Graças</t>
+          <t>Apartamento · 2 quartos · 48 m² · 1 vaga · Espinheiro</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua São Salvador</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
+          <t>3350.0</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>650.0</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
           <t>4000.0</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>4000.0</t>
-        </is>
-      </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -8131,22 +8111,22 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-80m2-gracas-recife--pe_33287785</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-48m2-RS3350/id-44730471/</t>
         </is>
       </c>
     </row>
@@ -8154,25 +8134,25 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 160 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 33 m² · Rosarinho</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Rosarinho</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -8202,42 +8182,42 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>121.21</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-casa-caiada-olinda-com-garagem-160m2-aluguel-RS4000-id-2909290334/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-tem-33-metros-quadrados-com-1-quarto-em-rosarinho-recife-pe-1533508699</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8225,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -8253,17 +8233,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 80 m² · Graças</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rua Joana D'arc Sampaio, --</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -8273,7 +8253,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8283,27 +8263,27 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>4010.0</t>
+          <t>4000.0</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>71.61</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -8313,7 +8293,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -8328,7 +8308,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-56m2-RS4000/id-45802268/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-80m2-gracas-recife--pe_33287785</t>
         </is>
       </c>
     </row>
@@ -8336,30 +8316,30 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Graças</t>
+          <t>Apartamento · 4 quartos · 160 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>4100.0</t>
+          <t>4000.0</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -8374,7 +8354,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>4100.0</t>
+          <t>4000.0</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8384,42 +8364,42 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apto-2-quartos-com-suite-na-rua-amelia-1533421604</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-casa-caiada-olinda-com-garagem-160m2-aluguel-RS4000-id-2909290334/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -8427,7 +8407,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -8435,37 +8415,37 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Casa Forte</t>
+          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Avenida Dezessete De Agosto, 1536</t>
+          <t>Rua Joana D'arc Sampaio, --</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2900.0</t>
+          <t>4000.0</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1100.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>4104.0</t>
+          <t>4010.0</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -8475,7 +8455,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>93.27</t>
+          <t>71.61</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -8495,22 +8475,22 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-forte-44m2-RS2900/id-45261230/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-56m2-RS4000/id-45802268/</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8498,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -8526,37 +8506,37 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
+          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Casa Forte</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Dezessete De Agosto, 1536</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Casa Forte</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>2900.0</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1100.0</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>4104.0</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -8566,7 +8546,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>97.67</t>
+          <t>93.27</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -8576,7 +8556,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -8586,22 +8566,22 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-forte-44m2-RS2900/id-45261230/</t>
         </is>
       </c>
     </row>
@@ -8609,7 +8589,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -8617,12 +8597,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
+          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Aflitos</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Conselheiro Rosa E Silva, 801</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -8632,12 +8612,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4141.0</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8647,17 +8627,17 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>4250.0</t>
+          <t>4142.0</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>53.12</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -8667,7 +8647,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -8677,22 +8657,22 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-aflitos-55m2-RS4141/id-45283901/</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8688,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 102 m² · Ilha do Leite</t>
+          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8718,12 +8698,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ilha do Leite</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>4300.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8738,7 +8718,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>4300.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8748,7 +8728,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>97.67</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8768,22 +8748,22 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-102m2-ilha-do-leite-recife--pe_33316621</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8771,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -8799,37 +8779,37 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · 2 vagas · Casa Forte</t>
+          <t>Apartamento · 3 quartos · 103 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rua Alfredo Fernandes, 320</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1500.0</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>428.0</t>
+          <t>1435.0</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>4328.0</t>
+          <t>4235.0</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -8839,7 +8819,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>41.12</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -8849,7 +8829,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -8859,22 +8839,22 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-casa-forte-84m2-RS2400/id-45585272/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-103-metros-quadrados-com-3-quartos-em-boa-vista-recife-pe-1530041789</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8862,7 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -8890,27 +8870,27 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1195.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8920,7 +8900,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>4395.0</t>
+          <t>4250.0</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -8930,7 +8910,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>79.91</t>
+          <t>53.12</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -8940,7 +8920,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -8950,7 +8930,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -8965,7 +8945,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-55m2-RS3200/id-46174975/</t>
+          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
         </is>
       </c>
     </row>
@@ -8973,7 +8953,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -8981,27 +8961,27 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 98 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 102 m² · Ilha do Leite</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire, 3291</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Ilha do Leite</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>4499.0</t>
+          <t>4300.0</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9011,44 +8991,44 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>4499.0</t>
+          <t>4300.0</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>98.0</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R94" t="inlineStr">
         <is>
           <t>2026-09-05</t>
@@ -9056,7 +9036,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4499/id-46461488/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-102m2-ilha-do-leite-recife--pe_33316621</t>
         </is>
       </c>
     </row>
@@ -9064,55 +9044,55 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 98 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 84 m² · 2 vagas · Casa Forte</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire</t>
+          <t>Rua Alfredo Fernandes, 320</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Casa Forte</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>4499.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>428.0</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>4499.0</t>
+          <t>4328.0</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -9122,7 +9102,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -9132,22 +9112,22 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4500/id-46421413/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-casa-forte-84m2-RS2400/id-45585272/</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9143,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -9178,12 +9158,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1195.0</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9193,44 +9173,44 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>4395.0</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>79.91</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R96" t="inlineStr">
         <is>
           <t>2026-09-05</t>
@@ -9238,7 +9218,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-110m2-RS4500/id-42417501/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-55m2-RS3200/id-46174975/</t>
         </is>
       </c>
     </row>
@@ -9246,20 +9226,20 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 92 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 98 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Ministro Marcos Freire</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -9269,7 +9249,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>4499.0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9284,7 +9264,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>4499.0</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -9294,7 +9274,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>48.91</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -9304,7 +9284,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -9314,7 +9294,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -9329,7 +9309,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1529307796</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4499/id-46461488/</t>
         </is>
       </c>
     </row>
@@ -9337,7 +9317,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -9345,17 +9325,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 90 m² · Torre</t>
+          <t>Apartamento · 3 quartos · 85 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Ministro Marcos Freire</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -9385,17 +9365,17 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -9405,7 +9385,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -9420,7 +9400,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/casa-4-quartos-torre-recife-90m2-code-736</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-110m2-RS4500/id-42417501/</t>
         </is>
       </c>
     </row>
@@ -9428,20 +9408,20 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 145 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 97 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire</t>
+          <t>Avenida Ministro Marcos Freire, 3291</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -9476,12 +9456,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>46.39</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -9496,22 +9476,22 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-olinda-com-garagem-145m2-aluguel-RS4500-id-2910117413/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4500/id-46421413/</t>
         </is>
       </c>
     </row>
@@ -9527,7 +9507,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 54 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 3 quartos · 130 m² · 2 vagas · Espinheiro</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9537,12 +9517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>4900.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9557,7 +9537,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>4900.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -9567,12 +9547,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>90.74</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -9587,7 +9567,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -9602,7 +9582,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/oportunidade-de-morar-com-o-requinte-e-sofisticacao-da-renomada-construtora-ferreira-pinto-1521757938</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/na-agamenon-alugo-exc-apt-3qts-130m-2-vagas-so-r-4-500-1349050999</t>
         </is>
       </c>
     </row>
@@ -9610,7 +9590,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -9618,12 +9598,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 118 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 92 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire, 2505</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -9633,7 +9613,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>5000.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -9648,7 +9628,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>5000.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -9658,7 +9638,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>42.37</t>
+          <t>48.91</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -9668,7 +9648,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -9678,7 +9658,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -9693,7 +9673,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS5000/id-42812242/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1529307796</t>
         </is>
       </c>
     </row>
@@ -9701,7 +9681,7 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -9709,22 +9689,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 4 quartos · 90 m² · Torre</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Avenida Parnamirim</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>5000.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -9739,7 +9719,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>5000.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -9749,17 +9729,17 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>113.64</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -9769,22 +9749,22 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-parnamirim-44m2-RS5000/id-37849980/</t>
+          <t>https://www.rogeriocorretor.com/imovel/casa-4-quartos-torre-recife-90m2-code-736</t>
         </is>
       </c>
     </row>
@@ -9792,30 +9772,30 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife, Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 90 m² · 2 vagas · Tamarineira</t>
+          <t>Apartamento · 2 quartos · 145 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Rua Isaac Salazar</t>
+          <t>Avenida Ministro Marcos Freire</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tamarineira</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>5000.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9830,7 +9810,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>5000.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -9840,19 +9820,19 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="O103" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -9860,22 +9840,22 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-tamarineira-RS5000/id-45230721/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-olinda-com-garagem-145m2-aluguel-RS4500-id-2910117413/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9863,7 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -9891,7 +9871,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 33 m² · Parnamirim</t>
+          <t>Apartamento · 2 quartos · 54 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9901,17 +9881,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>5000.0</t>
+          <t>4900.0</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -9921,17 +9901,17 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>5000.0</t>
+          <t>4900.0</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>151.52</t>
+          <t>90.74</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -9951,7 +9931,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -9966,7 +9946,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-33m2-parnamirim-recife--pe_33352285</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/oportunidade-de-morar-com-o-requinte-e-sofisticacao-da-renomada-construtora-ferreira-pinto-1521757938</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9962,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 148 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 118 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire, 3455</t>
+          <t>Avenida Ministro Marcos Freire, 2505</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -9997,44 +9977,44 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>1388.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>5388.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>36.41</t>
+          <t>42.37</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O105" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -10042,7 +10022,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -10057,7 +10037,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-148m2-RS3500/id-45673363/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS5000/id-42812242/</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10045,7 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -10073,47 +10053,47 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 148 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire</t>
+          <t>Avenida Parnamirim</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>1389.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>5389.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>36.41</t>
+          <t>113.64</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -10123,7 +10103,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -10133,22 +10113,22 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-1008m2-RS3500/id-8950438/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-parnamirim-44m2-RS5000/id-37849980/</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10136,7 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -10164,22 +10144,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Apartamento · 100 m² · Espinheiro</t>
+          <t>Apartamento · 3 quartos · 90 m² · 2 vagas · Tamarineira</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Isaac Salazar, 1</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Tamarineira</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>5500.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -10194,7 +10174,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>5500.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -10204,17 +10184,17 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -10224,22 +10204,22 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141436/lindo-apartamento-para-venda-ou-aluguel-mobiliado-no-espinheiro</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-tamarineira-RS5000/id-45230721/</t>
         </is>
       </c>
     </row>
@@ -10247,7 +10227,7 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -10255,7 +10235,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Apartamento · 100 m² · Espinheiro</t>
+          <t>Apartamento · 2 quartos · 33 m² · Parnamirim</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10265,17 +10245,17 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>5500.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -10285,22 +10265,22 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>5500.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>151.52</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -10315,7 +10295,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -10330,7 +10310,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141436</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-33m2-parnamirim-recife--pe_33352285</t>
         </is>
       </c>
     </row>
@@ -10338,7 +10318,7 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -10346,80 +10326,626 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t>Apartamento · 2 quartos · 148 m² · 1 vaga · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Avenida Ministro Marcos Freire, 3455</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>3500.0</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>1388.0</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>5388.0</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>36.41</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-148m2-RS3500/id-45673363/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 148 m² · 1 vaga · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Avenida Ministro Marcos Freire</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>3500.0</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>1389.0</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>5389.0</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>36.41</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-1008m2-RS3500/id-8950438/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Camila Melo Imóveis</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Apartamento · 100 m² · Espinheiro</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Espinheiro</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>5500.0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>5500.0</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>https://camilameloimoveis.com.br/imovel/141436/lindo-apartamento-para-venda-ou-aluguel-mobiliado-no-espinheiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Camila Melo Imóveis</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Apartamento · 100 m² · Espinheiro</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Espinheiro</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>5500.0</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>5500.0</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141436</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>OLX Imóveis</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 223 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>5800.0</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>5800.0</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>26.01</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>223.0</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-excelente-apartamento-com-3-quartos-no-bairro-da-boa-vista-recife-1533482876</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>OLX Imóveis</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 223 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>5800.0</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>5800.0</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>26.01</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>223.0</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-excelente-apartamento-com-3-quartos-no-bairro-da-boa-vista-recife-1533481096</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Camila Melo Imóveis</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
           <t>Apartamento · 88 m² · Torre</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>Torre</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t>6000.0</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
         <is>
           <t>6000.0</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="K115" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t>68.18</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr">
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
         <is>
           <t>88.0</t>
         </is>
       </c>
-      <c r="Q109" t="inlineStr">
+      <c r="Q115" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr">
+      <c r="R115" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr">
+      <c r="S115" t="inlineStr">
         <is>
           <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/112619</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S115"/>
+  <dimension ref="A1:S119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -561,7 +561,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · Encruzilhada</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Jaqueira</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Jaqueira</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1750.0</t>
+          <t>2350.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>1750.0</t>
+          <t>2350.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>53.03</t>
+          <t>78.33</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -631,12 +631,12 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/123-rua-carlos-borromeu-de-frente-para-o-mercado-da-encruzilhada/850471068-78</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-no-puerto-bilbao-residence-jaqueira-recife-pe-1533639364</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 75 m² · Casa Amarela</t>
+          <t>Apartamento · 40 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>37.33</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-otimo-apartamento-com-3-quartos-no-bairro-de-casa-amarela-recife-1533578933</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-no-edificio-luar-da-praca-casa-caiada-olinda-pe-1533638962</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · Casa Forte</t>
+          <t>Apartamento · 3 quartos · 90 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3204.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100.12</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -821,12 +821,12 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-1-quarto-em-casa-forte-recife-pe-1533544358</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-no-nossa-sra-do-carmo-gracas-recife-pe-1533638766</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 46 m² · Graças</t>
+          <t>Apartamento · 3 quartos · 59 m² · 1 vaga · Casa Amarela</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -856,12 +856,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3299.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3299.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71.72</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-possui-46-metros-quadrados-com-1-quarto-em-gracas-recife-pe-1533619487</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-casa-amarela-recife-pe-1533641842</t>
         </is>
       </c>
     </row>
@@ -933,90 +933,90 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Newville, OLX Imóveis, Viva Real</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 41 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 57 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Dois de Julho</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3700.0</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3700.0</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>80.49</t>
+          <t>64.91</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-1-quarto-em-boa-vista-recife-pe-1533558543</t>
+          <t>https://newville.com.br/imovel/apartamento_2_quartos--santo_amaro--recife--pe--locacao--cod-6847</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · Torre</t>
+          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3700.0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3700.0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>109.38</t>
+          <t>108.82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-1-quarto-na-torre-recife-pe-1533552220</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-no-beach-class-jaqueira-parnamirim-recife-pe-1532378567</t>
         </is>
       </c>
     </row>
@@ -1123,30 +1123,30 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 62 m² · Torre</t>
+          <t>Apartamento · 3 quartos · 70 m² · Tamarineira</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Coronel Uriel Sérgio Cardim</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Tamarineira</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>5200.0</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>5200.0</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1171,19 +1171,19 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61.29</t>
+          <t>74.29</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1201,107 +1201,103 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-2-quartos-na-torre-recife-pe-1533546992</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-tamarineira-recife-com-garagem-70m2-aluguel-RS5200-id-2910117516/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 62 m² · Hipódromo</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Hipódromo</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>4159.0</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>4159.0</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 57 m² · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Rua Pintor Manoel Bandeira</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>900.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>900.0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>67.08</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-excelente-apartamneto-3-quartos-na-estrada-de-belem-1533514055</t>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>15.79</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-olinda-com-garagem-57m2-aluguel-RS900-id-2652006870/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1309,30 +1305,30 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 58 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rua Pintor Manoel Bandeira</t>
+          <t>Rua Norberto Pessoa, 238</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>900.0</t>
+          <t>1300.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1347,7 +1343,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>900.0</t>
+          <t>1300.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1357,12 +1353,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1377,7 +1373,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1387,12 +1383,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-olinda-com-garagem-57m2-aluguel-RS900-id-2652006870/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1300/id-46461545/</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1404,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 58 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 41 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rua Norberto Pessoa, 238</t>
+          <t>Rua Professor Marculino Botelho, 404</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1423,37 +1419,37 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>1200.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>1400.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>34.15</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1468,22 +1464,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1300/id-46461545/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-olinda-bairro-novo-41m2-RS1200/id-45673360/</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1487,7 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1499,37 +1495,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 41 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 50 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua Professor Marculino Botelho, 404</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>1100.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>97.38</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>1447.38</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1539,17 +1535,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1559,12 +1555,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1574,7 +1570,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-olinda-bairro-novo-41m2-RS1200/id-45673360/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/224/apartamento-2-quartos-jose-mariano-boa-vista-recife/</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1578,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Cristina Mirele Imóveis</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1590,7 +1586,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 58 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1600,37 +1596,37 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1100.0</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>97.38</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1447.38</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1650,12 +1646,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1665,7 +1661,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/224/apartamento-2-quartos-jose-mariano-boa-vista-recife/</t>
+          <t>https://www.cristinamireleimoveis.com.br/imovel/4314734/apartamento-locacao-olinda-pe-bairro-novo-edf-estacao-verde</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1669,7 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cristina Mirele Imóveis</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1681,7 +1677,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 58 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 57 m² · Arruda</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1691,12 +1687,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1500.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1711,7 +1707,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1500.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1721,7 +1717,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1741,12 +1737,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1756,7 +1752,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.cristinamireleimoveis.com.br/imovel/4314734/apartamento-locacao-olinda-pe-bairro-novo-edf-estacao-verde</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850301025-80</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1760,7 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1772,22 +1768,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · Arruda</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1802,7 +1798,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1812,19 +1808,19 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -1832,7 +1828,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1842,12 +1838,12 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850301025-80</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1700/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1851,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1863,22 +1859,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 33 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1750.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1893,7 +1889,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1750.0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1903,17 +1899,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>53.03</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1923,22 +1919,22 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1700/id-45733416/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/123-rua-carlos-borromeu-de-frente-para-o-mercado-da-encruzilhada/850471068-78</t>
         </is>
       </c>
     </row>
@@ -1946,30 +1942,30 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Camila Melo Imóveis</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · Casa Caiada</t>
+          <t>Apartamento · 74 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rua Carlos Nigro</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1799.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1984,7 +1980,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1799.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1994,42 +1990,42 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>59.97</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-olinda-com-garagem-30m2-aluguel-RS1799-id-2906429133/?source=ranking%2Crp</t>
+          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2106,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2120,7 +2116,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/141772/apartamento-semi-mobiliado-para-locacao-na-boa-vista-no-edf-basbel</t>
+          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2124,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Camila Melo Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2136,17 +2132,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Apartamento · 74 m² · Boa Vista</t>
+          <t>Apartamento · 30 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Coronel Alberto Lundgren, 604</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2156,27 +2152,27 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2186,7 +2182,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2196,22 +2192,22 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://camilameloimoveis.com.br/imovel/viewFichaImovel/141772</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2215,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2227,32 +2223,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Apartamento · 30 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 38 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rua Coronel Alberto Lundgren, 604</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2262,22 +2258,22 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2287,12 +2283,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2302,7 +2298,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/flat-quatro-rodas-1526587978</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2306,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2318,7 +2314,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2328,7 +2324,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2338,7 +2334,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2353,17 +2349,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2378,22 +2374,22 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/flat-quatro-rodas-1526587978</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -2401,25 +2397,25 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 1 quarto · 35 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Carlos Nigro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2429,7 +2425,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2444,22 +2440,22 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2469,22 +2465,22 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-casa-caiada-olinda-35m2-aluguel-RS2000-id-2582783099/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2492,20 +2488,20 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 50 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rua Carlos Nigro</t>
+          <t>Rua Gildo Branco, 2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2515,7 +2511,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2530,7 +2526,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2540,17 +2536,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2560,22 +2556,22 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-casa-caiada-olinda-35m2-aluguel-RS2000-id-2582783099/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS2200/id-44016902/</t>
         </is>
       </c>
     </row>
@@ -2591,57 +2587,57 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 50 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rua Gildo Branco, 2</t>
+          <t>Rua Coronel Alberto Lundgren, 604</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>2200.0</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2200.0</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2651,12 +2647,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2666,7 +2662,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS2200/id-44016902/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
         </is>
       </c>
     </row>
@@ -2674,67 +2670,67 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 71 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rua Coronel Alberto Lundgren, 604</t>
+          <t>Rua Alcina Coelho de Carvalho</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2350.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2350.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -2742,12 +2738,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2757,7 +2753,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-olinda-com-garagem-71m2-aluguel-RS2350-id-2889467882/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2834,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2929,7 +2925,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3020,7 +3016,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3111,7 +3107,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3202,7 +3198,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3293,7 +3289,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3384,7 +3380,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3475,7 +3471,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3566,7 +3562,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3657,7 +3653,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3748,7 +3744,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3766,7 +3762,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3774,7 +3770,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 75 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3784,7 +3780,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3814,42 +3810,42 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>37.33</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-1-quarto-boa-vista-recife-1-vaga-38m2-code-707</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-otimo-apartamento-com-3-quartos-no-bairro-de-casa-amarela-recife-1533578933</t>
         </is>
       </c>
     </row>
@@ -3857,15 +3853,15 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CTI Imobiliária, Âncora Imobiliária</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
+          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3875,42 +3871,42 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2450.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>365.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>161.22</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2895.6099999999997</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>64.35</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3925,12 +3921,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3940,7 +3936,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
+          <t>https://www.rogeriocorretor.com/imovel/apartamento-1-quarto-boa-vista-recife-1-vaga-38m2-code-707</t>
         </is>
       </c>
     </row>
@@ -3948,15 +3944,15 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>CTI Imobiliária, Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · 1 vaga · Ilha do Leite</t>
+          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3966,42 +3962,42 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ilha do Leite</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2900.0</t>
+          <t>2450.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>365.0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>161.22</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2900.0</t>
+          <t>2895.6099999999997</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>64.35</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4016,22 +4012,22 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/estudio-ilha-do-leite-no-recife-mobilado-e-equipado-por-2900-reais-mensais-1533493470</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
         </is>
       </c>
     </row>
@@ -4039,65 +4035,65 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CTI Imobiliária, Chaves na Mão Recife</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 1 quarto · 35 m² · 1 vaga · Ilha do Leite</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rua Da Amizade, 223</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Ilha do Leite</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1850.0</t>
+          <t>2900.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>953.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2997.0</t>
+          <t>2900.0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>37.46</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4107,22 +4103,22 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/estudio-ilha-do-leite-no-recife-mobilado-e-equipado-por-2900-reais-mensais-1533493470</t>
         </is>
       </c>
     </row>
@@ -4130,65 +4126,65 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>CTI Imobiliária, Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 80 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Avenida Doutor José Augusto Moreira, 900</t>
+          <t>Rua Da Amizade, 223</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>1850.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>953.0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2997.0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>37.46</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4198,22 +4194,22 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>48</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
         </is>
       </c>
     </row>
@@ -4229,12 +4225,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 92 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Avenida Carlos De Lima Cavalcante</t>
+          <t>Avenida Doutor José Augusto Moreira, 900</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4269,17 +4265,17 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4289,12 +4285,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4304,7 +4300,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS3000/id-42437394/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
         </is>
       </c>
     </row>
@@ -4320,12 +4316,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 92 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro, 93</t>
+          <t>Avenida Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4335,12 +4331,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1822.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1178.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4355,24 +4351,24 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O43" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -4380,12 +4376,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4395,7 +4391,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1822/id-45585830/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS3000/id-42437394/</t>
         </is>
       </c>
     </row>
@@ -4411,12 +4407,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante, 2595</t>
+          <t>Rua Otaviano Pessoa Monteiro, 93</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4426,44 +4422,44 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
+          <t>1822.0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1178.0</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
           <t>3000.0</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O44" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -4471,12 +4467,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4486,7 +4482,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-40m2-RS3000/id-45710865/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1822/id-45585830/</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4490,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -4502,17 +4498,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 47 m² · 1 vaga · Tamarineira</t>
+          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rua Goianésia, 106</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante, 2595</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tamarineira</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4542,17 +4538,17 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>63.83</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4562,22 +4558,22 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-tamarineira-47m2-RS3000/id-44941964/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-40m2-RS3000/id-45710865/</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4581,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4593,17 +4589,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 2 quartos · 47 m² · 1 vaga · Tamarineira</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Goianésia, 106</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Tamarineira</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4633,42 +4629,42 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>63.83</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>34.0</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-alugar-ou-vender-nas-gracas-recife-pe-1516957301</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-tamarineira-47m2-RS3000/id-44941964/</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4745,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4767,7 +4763,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4775,17 +4771,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Paissandu</t>
+          <t>Apartamento · 3 quartos · 92 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rua Estácio Coimbra</t>
+          <t>Rua Edmar Moury Fernandes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Paissandu</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4815,42 +4811,42 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-paissandu-recife-com-garagem-35m2-aluguel-RS3000-id-2902097797/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-92m2-aluguel-RS3000-id-2773332517/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4866,12 +4862,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 92 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 81 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rua Edmar Moury Fernandes</t>
+          <t>Rua Professor Francisco Xavier Paes Barreto</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4886,27 +4882,27 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3002.0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4916,17 +4912,17 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4936,12 +4932,12 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-92m2-aluguel-RS3000-id-2773332517/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-81m2-aluguel-RS3000-id-2908569699/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4949,90 +4945,90 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Josinildo Imóveis</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 81 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 42 m² · Torre</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rua Professor Francisco Xavier Paes Barreto</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>3002.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-81m2-aluguel-RS3000-id-2908569699/?source=ranking%2Crp</t>
+          <t>https://josinildoimoveis.com.br/imovel/edf-green-life-torre/320</t>
         </is>
       </c>
     </row>
@@ -5040,35 +5036,35 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Josinildo Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 42 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 48 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua da Glória</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>650.0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5078,17 +5074,17 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>3150.0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>65.62</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5098,7 +5094,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5108,22 +5104,22 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://josinildoimoveis.com.br/imovel/edf-green-life-torre/320</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-olinda-com-garagem-48m2-aluguel-RS2500-id-2910114900/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5127,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -5139,27 +5135,27 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 48 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 34 m² · Graças</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rua da Glória</t>
+          <t>Rua Dona Anunciada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>650.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5169,22 +5165,22 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>3150.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>65.62</t>
+          <t>94.12</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5199,7 +5195,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -5209,12 +5205,12 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-olinda-com-garagem-48m2-aluguel-RS2500-id-2910114900/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-gracas-recife-com-garagem-34m2-aluguel-RS3200-id-2795484813/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5295,7 +5291,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -5386,7 +5382,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5404,55 +5400,55 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>237.0</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3202.0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>56.14</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5467,17 +5463,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5487,7 +5483,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-olinda-com-garagem-57m2-aluguel-RS3200-id-2901326206/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5491,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -5503,7 +5499,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
+          <t>Apartamento · 1 quarto · 32 m² · Casa Forte</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5513,47 +5509,47 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Casa Forte</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>237.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>3202.0</t>
+          <t>3204.0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>100.12</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5563,22 +5559,22 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-1-quarto-em-casa-forte-recife-pe-1533544358</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5582,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -5594,22 +5590,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
+          <t>Apartamento · 1 quarto · 46 m² · Graças</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rua Barão De Vera Cruz</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Campo Grande</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3299.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5624,7 +5620,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3299.0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5634,42 +5630,42 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>71.72</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>46.0</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-possui-46-metros-quadrados-com-1-quarto-em-gracas-recife-pe-1533619487</t>
         </is>
       </c>
     </row>
@@ -5677,7 +5673,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -5685,17 +5681,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 96 m² · Encruzilhada</t>
+          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Barão De Vera Cruz</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Campo Grande</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5725,17 +5721,17 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>34.38</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5745,22 +5741,22 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-apartamento-com-02-quartos-02-vagas-na-encruzilhada-recife-1533489136</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5764,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5776,7 +5772,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Torre</t>
+          <t>Apartamento · 1 quarto · 41 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5786,12 +5782,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5806,7 +5802,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5816,12 +5812,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>80.49</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -5836,22 +5832,22 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-torre-recife-1-vaga-50m2-code-88</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-1-quarto-em-boa-vista-recife-pe-1533558543</t>
         </is>
       </c>
     </row>
@@ -5859,30 +5855,30 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 59 m² · Santo Amaro</t>
+          <t>Apartamento · 2 quartos · 96 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rua Dois de Julho</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5897,7 +5893,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5907,7 +5903,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>57.63</t>
+          <t>34.38</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5917,7 +5913,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5927,12 +5923,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5942,7 +5938,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-santo-amaro-recife-com-garagem-59m2-aluguel-RS3400-id-2910116626/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-apartamento-com-02-quartos-02-vagas-na-encruzilhada-recife-1533489136</t>
         </is>
       </c>
     </row>
@@ -5950,7 +5946,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -5958,27 +5954,27 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · 2 vagas · Santana</t>
+          <t>Apartamento · 2 quartos · 50 m² · Torre</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rua Sant'anna, 171</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Santana</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>3400.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1219.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5988,27 +5984,27 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>3419.0</t>
+          <t>3400.0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6018,22 +6014,22 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-santana-RS2200/id-46016126/</t>
+          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-torre-recife-1-vaga-50m2-code-88</t>
         </is>
       </c>
     </row>
@@ -6041,35 +6037,35 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 84 m² · 2 vagas · Santana</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões</t>
+          <t>Rua Sant'anna, 171</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Santana</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1219.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6079,27 +6075,27 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3419.0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>59.32</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6109,22 +6105,22 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-45711136/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-santana-RS2200/id-46016126/</t>
         </is>
       </c>
     </row>
@@ -6132,20 +6128,20 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
+          <t>Rua Pereira Simões</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6180,7 +6176,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>59.32</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6190,7 +6186,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6200,12 +6196,12 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -6215,7 +6211,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-45711136/</t>
         </is>
       </c>
     </row>
@@ -6223,7 +6219,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -6231,17 +6227,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Casa Amarela</t>
+          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rua Doutor Genaro Guimarães, 210</t>
+          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6271,7 +6267,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>59.32</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6291,22 +6287,22 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-59m2-RS3500/id-45862927/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
         </is>
       </c>
     </row>
@@ -6322,17 +6318,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 87 m² · 2 vagas · Encruzilhada</t>
+          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Casa Amarela</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rua Castro Alves, 175</t>
+          <t>Rua Doutor Genaro Guimarães, 210</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -6362,17 +6358,17 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>59.32</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6382,12 +6378,12 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6397,7 +6393,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-encruzilhada-RS3500/id-46232694/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-59m2-RS3500/id-45862927/</t>
         </is>
       </c>
     </row>
@@ -6405,7 +6401,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -6413,17 +6409,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Espinheiro</t>
+          <t>Apartamento · 3 quartos · 87 m² · 2 vagas · Encruzilhada</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Castro Alves, 175</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -6453,19 +6449,19 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O66" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -6473,12 +6469,12 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6488,7 +6484,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-apto-em-andar-alto-e-com-moveis-planejados-no-edf-saint-jaimes-espinheiro-recife-1533498731</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-encruzilhada-RS3500/id-46232694/</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6500,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Espinheiro</t>
+          <t>Apartamento · 1 quarto · 32 m² · Torre</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6514,7 +6510,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6544,12 +6540,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>109.38</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -6564,12 +6560,12 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6579,7 +6575,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-apto-em-andar-alto-e-com-moveis-planejados-no-edf-saint-jaimes-espinheiro-recife-1533436267</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-1-quarto-na-torre-recife-pe-1533552220</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6583,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -6595,7 +6591,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 82 m² · Casa Forte</t>
+          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Espinheiro</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6605,7 +6601,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6615,7 +6611,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6630,12 +6626,12 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>42.68</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6655,22 +6651,22 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-82m2-casa-forte-recife--pe_33364920</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-apto-em-andar-alto-e-com-moveis-planejados-no-edf-saint-jaimes-espinheiro-recife-1533498731</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6682,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Tamarineira</t>
+          <t>Apartamento · 2 quartos · 82 m² · Casa Forte</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6696,7 +6692,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tamarineira</t>
+          <t>Casa Forte</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6726,7 +6722,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>42.68</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6746,12 +6742,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6761,7 +6757,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-70m2-tamarineira-recife--pe_33364198</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-82m2-casa-forte-recife--pe_33364920</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6765,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -6777,7 +6773,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 34 m² · Graças</t>
+          <t>Apartamento · 2 quartos · 70 m² · Tamarineira</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6787,7 +6783,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Tamarineira</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6797,7 +6793,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6812,17 +6808,17 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>102.94</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -6837,12 +6833,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6852,7 +6848,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-1-quarto-gracas-recife-1-vaga-34m2-code-726</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-70m2-tamarineira-recife--pe_33364198</t>
         </is>
       </c>
     </row>
@@ -6860,25 +6856,25 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 103 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 34 m² · Graças</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rua Professor Francisco Xavier Paes Barreto</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6908,34 +6904,34 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>102.94</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R71" t="inlineStr">
         <is>
           <t>2026-09-05</t>
@@ -6943,7 +6939,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-casa-caiada-olinda-com-garagem-103m2-aluguel-RS3500-id-2909202314/?source=ranking%2Crp</t>
+          <t>https://www.rogeriocorretor.com/imovel/apartamento-1-quarto-gracas-recife-1-vaga-34m2-code-726</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6947,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -6959,17 +6955,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · Boa Vista</t>
+          <t>Apartamento · 4 quartos · 103 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Avenida Governador Agamenon Magalhães</t>
+          <t>Rua Professor Francisco Xavier Paes Barreto</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6979,62 +6975,62 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>3503.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>87.58</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-boa-vista-recife-com-garagem-40m2-aluguel-RS3500-id-2910206116/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-casa-caiada-olinda-com-garagem-103m2-aluguel-RS3500-id-2909202314/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -7042,65 +7038,65 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Apartamento · 62 m² · Casa Amarela</t>
+          <t>Apartamento · 1 quarto · 40 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Agamenon Magalhães</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3503.0</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>58.06</t>
+          <t>87.58</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7110,22 +7106,22 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/edificio-trindade-family-class-direto-com-a-proprietaria-1532638263</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-boa-vista-recife-com-garagem-40m2-aluguel-RS3500-id-2910206116/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -7133,25 +7129,25 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 75 m² · Espinheiro</t>
+          <t>Apartamento · 62 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rua Quarenta e Oito</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -7181,17 +7177,17 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>58.06</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7201,22 +7197,22 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-espinheiro-recife-com-garagem-75m2-aluguel-RS3600-id-2910115354/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/edificio-trindade-family-class-direto-com-a-proprietaria-1532638263</t>
         </is>
       </c>
     </row>
@@ -7224,55 +7220,55 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 2 quartos · 75 m² · Espinheiro</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Avenida Parnamirim, 58</t>
+          <t>Rua Quarenta e Oito</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>995.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>435.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>3630.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7282,7 +7278,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7292,22 +7288,22 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-parnamirim-70m2-RS2200/id-45505315/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-espinheiro-recife-com-garagem-75m2-aluguel-RS3600-id-2910115354/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -7323,47 +7319,47 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · 1 vaga · Tamarineira</t>
+          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rua São Vicente, 255</t>
+          <t>Avenida Parnamirim, 58</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tamarineira</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>995.0</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>435.0</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>3630.0</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7373,7 +7369,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7383,12 +7379,12 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -7398,7 +7394,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-tamarineira-RS3700/id-42017736/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-parnamirim-70m2-RS2200/id-45505315/</t>
         </is>
       </c>
     </row>
@@ -7406,25 +7402,25 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Recife, OLX Imóveis</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · 1 vaga · Casa Forte</t>
+          <t>Apartamento · 2 quartos · 50 m² · 1 vaga · Tamarineira</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rua Alfredo Fernandes, 278</t>
+          <t>Rua São Vicente, 255</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Tamarineira</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -7454,17 +7450,17 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>105.71</t>
+          <t>73.27</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -7474,22 +7470,22 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-casa-forte-RS3700/id-45922055/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-tamarineira-RS3700/id-42017736/</t>
         </is>
       </c>
     </row>
@@ -7497,25 +7493,25 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Newville, Viva Real, Zap Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 56 m² · Santo Amaro</t>
+          <t>Apartamento · 1 quarto · 35 m² · 1 vaga · Casa Forte</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rua Dois de Julho</t>
+          <t>Rua Alfredo Fernandes, 278</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Forte</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -7545,12 +7541,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>66.07</t>
+          <t>105.71</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -7560,27 +7556,27 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://newville.com.br/imovel/apartamento_2_quartos--santo_amaro--recife--pe--locacao--cod-6847</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-casa-forte-RS3700/id-45922055/</t>
         </is>
       </c>
     </row>
@@ -7661,7 +7657,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7752,7 +7748,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7778,7 +7774,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · Parnamirim</t>
+          <t>Apartamento · 2 quartos · 62 m² · Torre</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7788,7 +7784,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -7818,34 +7814,34 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>115.15</t>
+          <t>61.29</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="R81" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -7853,7 +7849,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-possui-33-metros-quadrados-com-1-quarto-em-parnamirim-recife-pe-1533481808</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-2-quartos-na-torre-recife-pe-1533546992</t>
         </is>
       </c>
     </row>
@@ -7861,25 +7857,25 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 67 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 33 m² · Parnamirim</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -7909,17 +7905,17 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>56.72</t>
+          <t>115.15</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -7929,22 +7925,22 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-olinda-com-garagem-67m2-aluguel-RS3800-id-2906555835/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-possui-33-metros-quadrados-com-1-quarto-em-parnamirim-recife-pe-1533481808</t>
         </is>
       </c>
     </row>
@@ -7952,7 +7948,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -7960,17 +7956,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 53 m² · Torre</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire</t>
+          <t>Rua Horácio Cahu</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -8000,12 +7996,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -8015,12 +8011,12 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -8030,12 +8026,12 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS3900-id-2910365714/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torre-recife-com-garagem-53m2-aluguel-RS3900-id-2910115353/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -8043,35 +8039,35 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 48 m² · 1 vaga · Espinheiro</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rua São Salvador</t>
+          <t>Avenida Ministro Marcos Freire</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>3350.0</t>
+          <t>3900.0</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>650.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8081,52 +8077,52 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>4000.0</t>
+          <t>3900.0</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>48.0</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-48m2-RS3350/id-44730471/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-olinda-com-garagem-80m2-aluguel-RS3900-id-2910365714/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8130,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -8142,74 +8138,74 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · Rosarinho</t>
+          <t>Apartamento · 2 quartos · 48 m² · 1 vaga · Espinheiro</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua São Salvador</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosarinho</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
+          <t>3350.0</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>650.0</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
           <t>4000.0</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>4000.0</t>
-        </is>
-      </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>121.21</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="R85" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -8217,7 +8213,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-tem-33-metros-quadrados-com-1-quarto-em-rosarinho-recife-pe-1533508699</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-48m2-RS3350/id-44730471/</t>
         </is>
       </c>
     </row>
@@ -8225,7 +8221,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -8233,7 +8229,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Graças</t>
+          <t>Apartamento · 1 quarto · 33 m² · Rosarinho</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8243,7 +8239,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Rosarinho</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -8273,12 +8269,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>121.21</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -8293,22 +8289,22 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-80m2-gracas-recife--pe_33287785</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-tem-33-metros-quadrados-com-1-quarto-em-rosarinho-recife-pe-1533508699</t>
         </is>
       </c>
     </row>
@@ -8389,7 +8385,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -8480,7 +8476,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -8571,7 +8567,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8662,7 +8658,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8680,7 +8676,7 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -8688,7 +8684,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
+          <t>Apartamento · 3 quartos · 62 m² · Hipódromo</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8698,17 +8694,17 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Hipódromo</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>4159.0</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8718,22 +8714,22 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>4159.0</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>97.67</t>
+          <t>67.08</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -8748,22 +8744,22 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-excelente-apartamneto-3-quartos-na-estrada-de-belem-1533514055</t>
         </is>
       </c>
     </row>
@@ -8779,7 +8775,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 103 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 48 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8789,42 +8785,42 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1435.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>4235.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>41.12</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -8839,22 +8835,22 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-103-metros-quadrados-com-3-quartos-em-boa-vista-recife-pe-1530041789</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-no-torre-recife-pe-torre-recife-pe-1533184010</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8858,7 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -8870,7 +8866,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
+          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8880,17 +8876,17 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8900,7 +8896,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>4250.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -8910,7 +8906,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>53.12</t>
+          <t>97.67</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -8930,7 +8926,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -8940,12 +8936,12 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
         </is>
       </c>
     </row>
@@ -8953,7 +8949,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -8961,7 +8957,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 102 m² · Ilha do Leite